--- a/database/event/4979/event_4979_evp_summary.xlsx
+++ b/database/event/4979/event_4979_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.2217</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4687</v>
+        <v>3.3925</v>
       </c>
       <c r="E2" t="n">
         <v>9.6295</v>
@@ -548,7 +548,7 @@
         <v>1.5432</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2807</v>
+        <v>2.2209</v>
       </c>
       <c r="E3" t="n">
         <v>6.6887</v>
@@ -594,7 +594,7 @@
         <v>1.2057</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6897</v>
+        <v>1.638</v>
       </c>
       <c r="E4" t="n">
         <v>5.2258</v>
@@ -640,7 +640,7 @@
         <v>1.1363</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5683</v>
+        <v>1.5183</v>
       </c>
       <c r="E5" t="n">
         <v>4.9251</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0798</v>
+        <v>4.0611</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9413</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2268</v>
+        <v>1.174</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0798</v>
+        <v>4.0611</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5129</v>
+        <v>2.4942</v>
       </c>
       <c r="G6" t="n">
         <v>1.5669</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5129</v>
+        <v>2.4942</v>
       </c>
       <c r="I6" t="n">
         <v>2.5364</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.474</v>
+        <v>3.4376</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8015</v>
+        <v>0.7931</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9821</v>
+        <v>0.9256</v>
       </c>
       <c r="E7" t="n">
-        <v>3.474</v>
+        <v>3.4376</v>
       </c>
       <c r="F7" t="n">
-        <v>3.264</v>
+        <v>3.2276</v>
       </c>
       <c r="G7" t="n">
         <v>0.21</v>
       </c>
       <c r="H7" t="n">
-        <v>3.264</v>
+        <v>3.2276</v>
       </c>
       <c r="I7" t="n">
         <v>3.3098</v>
@@ -778,7 +778,7 @@
         <v>0.7853</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9536</v>
+        <v>0.9121</v>
       </c>
       <c r="E8" t="n">
         <v>3.4036</v>
@@ -824,7 +824,7 @@
         <v>0.6923</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7907</v>
+        <v>0.7514</v>
       </c>
       <c r="E9" t="n">
         <v>3.0004</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8186</v>
+        <v>2.7784</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6503</v>
+        <v>0.641</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7173</v>
+        <v>0.663</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8186</v>
+        <v>2.7784</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7042</v>
+        <v>2.664</v>
       </c>
       <c r="G10" t="n">
         <v>0.1144</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7042</v>
+        <v>2.664</v>
       </c>
       <c r="I10" t="n">
         <v>2.7549</v>
@@ -916,7 +916,7 @@
         <v>0.6094000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>2.6414</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6317</v>
+        <v>2.5952</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6072</v>
+        <v>0.5988</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6418</v>
+        <v>0.59</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6317</v>
+        <v>2.5952</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4591</v>
+        <v>2.4226</v>
       </c>
       <c r="G12" t="n">
         <v>0.1726</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4591</v>
+        <v>2.4226</v>
       </c>
       <c r="I12" t="n">
         <v>2.5052</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1141</v>
+        <v>2.091</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4878</v>
+        <v>0.4824</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4327</v>
+        <v>0.3891</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1141</v>
+        <v>2.091</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5564</v>
+        <v>1.5333</v>
       </c>
       <c r="G13" t="n">
         <v>0.5577</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5564</v>
+        <v>1.5333</v>
       </c>
       <c r="I13" t="n">
         <v>1.5856</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.976</v>
+        <v>1.9788</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4559</v>
+        <v>0.4565</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3769</v>
+        <v>0.3444</v>
       </c>
       <c r="E14" t="n">
-        <v>1.976</v>
+        <v>1.9788</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3765</v>
+        <v>-0.3737</v>
       </c>
       <c r="G14" t="n">
         <v>2.3525</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3765</v>
+        <v>-0.3737</v>
       </c>
       <c r="I14" t="n">
         <v>-0.38</v>
@@ -1100,7 +1100,7 @@
         <v>0.4461</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3597</v>
+        <v>0.3264</v>
       </c>
       <c r="E15" t="n">
         <v>1.9335</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8697</v>
+        <v>1.8524</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4314</v>
+        <v>0.4274</v>
       </c>
       <c r="D16" t="n">
-        <v>0.334</v>
+        <v>0.2941</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8697</v>
+        <v>1.8524</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5499</v>
+        <v>1.5326</v>
       </c>
       <c r="G16" t="n">
         <v>0.3198</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5499</v>
+        <v>1.5326</v>
       </c>
       <c r="I16" t="n">
         <v>1.5716</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8524</v>
+        <v>1.849</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4274</v>
+        <v>0.4266</v>
       </c>
       <c r="D17" t="n">
-        <v>0.327</v>
+        <v>0.2927</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8524</v>
+        <v>1.849</v>
       </c>
       <c r="F17" t="n">
-        <v>0.458</v>
+        <v>0.4546</v>
       </c>
       <c r="G17" t="n">
         <v>1.3944</v>
       </c>
       <c r="H17" t="n">
-        <v>0.458</v>
+        <v>0.4546</v>
       </c>
       <c r="I17" t="n">
         <v>0.4623</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8021</v>
+        <v>1.771</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4158</v>
+        <v>0.4086</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3066</v>
+        <v>0.2617</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8021</v>
+        <v>1.771</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7906</v>
+        <v>2.7595</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9885</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7906</v>
+        <v>2.7595</v>
       </c>
       <c r="I18" t="n">
         <v>2.8297</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7692</v>
+        <v>1.765</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4082</v>
+        <v>0.4072</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2934</v>
+        <v>0.2593</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7692</v>
+        <v>1.765</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5656</v>
+        <v>0.5614</v>
       </c>
       <c r="G19" t="n">
         <v>1.2036</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5656</v>
+        <v>0.5614</v>
       </c>
       <c r="I19" t="n">
         <v>0.5709</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7508</v>
+        <v>1.7296</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4039</v>
+        <v>0.3991</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2859</v>
+        <v>0.2452</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7508</v>
+        <v>1.7296</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9083</v>
+        <v>1.8871</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1575</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9083</v>
+        <v>1.8871</v>
       </c>
       <c r="I20" t="n">
         <v>1.9351</v>
@@ -1376,7 +1376,7 @@
         <v>0.3742</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2338</v>
+        <v>0.2022</v>
       </c>
       <c r="E21" t="n">
         <v>1.6217</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.247</v>
+        <v>1.2342</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2877</v>
+        <v>0.2848</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0824</v>
+        <v>0.0478</v>
       </c>
       <c r="E22" t="n">
-        <v>1.247</v>
+        <v>1.2342</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7159</v>
+        <v>1.7031</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4689</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7159</v>
+        <v>1.7031</v>
       </c>
       <c r="I22" t="n">
         <v>1.7319</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1929</v>
+        <v>1.1631</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2752</v>
+        <v>0.2683</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0605</v>
+        <v>0.0195</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1929</v>
+        <v>1.1631</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0098</v>
+        <v>1.98</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8169</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0098</v>
+        <v>1.98</v>
       </c>
       <c r="I23" t="n">
         <v>2.0475</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1194</v>
+        <v>1.122</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2583</v>
+        <v>0.2589</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0309</v>
+        <v>0.0031</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1194</v>
+        <v>1.122</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3442</v>
+        <v>-0.3416</v>
       </c>
       <c r="G24" t="n">
         <v>1.4636</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3442</v>
+        <v>-0.3416</v>
       </c>
       <c r="I24" t="n">
         <v>-0.3474</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0651</v>
+        <v>1.0475</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2457</v>
+        <v>0.2417</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0089</v>
+        <v>-0.0266</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0651</v>
+        <v>1.0475</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5766</v>
+        <v>1.559</v>
       </c>
       <c r="G25" t="n">
         <v>-0.5115</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5766</v>
+        <v>1.559</v>
       </c>
       <c r="I25" t="n">
         <v>1.5987</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8973</v>
+        <v>0.894</v>
       </c>
       <c r="C26" t="n">
-        <v>0.207</v>
+        <v>0.2063</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0589</v>
+        <v>-0.0877</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8973</v>
+        <v>0.894</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8973</v>
+        <v>0.894</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8973</v>
+        <v>0.894</v>
       </c>
       <c r="I26" t="n">
         <v>0.9015</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1725</v>
+        <v>0.1676</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0398</v>
+        <v>0.0387</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3517</v>
+        <v>-0.3771</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1725</v>
+        <v>0.1676</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6586</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>-0.4861</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6586</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="I27" t="n">
         <v>0.6647</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1365</v>
+        <v>0.136</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0315</v>
+        <v>0.0314</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3662</v>
+        <v>-0.3897</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1365</v>
+        <v>0.136</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1365</v>
+        <v>0.136</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1365</v>
+        <v>0.136</v>
       </c>
       <c r="I28" t="n">
         <v>0.1371</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3556</v>
+        <v>-0.3543</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.082</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5851</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3556</v>
+        <v>-0.3543</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3556</v>
+        <v>-0.3543</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3556</v>
+        <v>-0.3543</v>
       </c>
       <c r="I29" t="n">
         <v>-0.3573</v>
@@ -1790,7 +1790,7 @@
         <v>-0.1601</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7016</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="E30" t="n">
         <v>-0.6938</v>
@@ -1836,7 +1836,7 @@
         <v>-0.2355</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8337</v>
+        <v>-0.8506</v>
       </c>
       <c r="E31" t="n">
         <v>-1.0208</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.0488</v>
+        <v>-1.0449</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.242</v>
+        <v>-0.2411</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8451</v>
+        <v>-0.8602</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.0488</v>
+        <v>-1.0449</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.0488</v>
+        <v>-1.0449</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.0488</v>
+        <v>-1.0449</v>
       </c>
       <c r="I32" t="n">
         <v>-1.0537</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2449</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8501</v>
+        <v>-0.8667</v>
       </c>
       <c r="E33" t="n">
         <v>-1.0613</v>
@@ -1974,7 +1974,7 @@
         <v>-0.2723</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8981</v>
+        <v>-0.9141</v>
       </c>
       <c r="E34" t="n">
         <v>-1.1801</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.2032</v>
+        <v>-1.1987</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2776</v>
+        <v>-0.2766</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9074</v>
+        <v>-0.9215</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.2032</v>
+        <v>-1.1987</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.2032</v>
+        <v>-1.1987</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.2032</v>
+        <v>-1.1987</v>
       </c>
       <c r="I35" t="n">
         <v>-1.2088</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3069</v>
+        <v>-1.2978</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3015</v>
+        <v>-0.2994</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9493</v>
+        <v>-0.961</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3069</v>
+        <v>-1.2978</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.222</v>
+        <v>-1.2129</v>
       </c>
       <c r="G36" t="n">
         <v>-0.0849</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.222</v>
+        <v>-1.2129</v>
       </c>
       <c r="I36" t="n">
         <v>-1.2334</v>
@@ -2112,7 +2112,7 @@
         <v>-0.3091</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9626</v>
+        <v>-0.9777</v>
       </c>
       <c r="E37" t="n">
         <v>-1.3398</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4464</v>
+        <v>-1.441</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3337</v>
+        <v>-0.3325</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0057</v>
+        <v>-1.018</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4464</v>
+        <v>-1.441</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4464</v>
+        <v>-1.441</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4464</v>
+        <v>-1.441</v>
       </c>
       <c r="I38" t="n">
         <v>-1.4531</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4017</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1247</v>
+        <v>-1.1376</v>
       </c>
       <c r="E39" t="n">
         <v>-1.7411</v>
@@ -2250,7 +2250,7 @@
         <v>-0.4132</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1449</v>
+        <v>-1.1575</v>
       </c>
       <c r="E40" t="n">
         <v>-1.7911</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.0496</v>
+        <v>-2.0325</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4729</v>
+        <v>-0.4689</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2494</v>
+        <v>-1.2537</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.0496</v>
+        <v>-2.0325</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.1491</v>
+        <v>-1.132</v>
       </c>
       <c r="G41" t="n">
         <v>-0.9005</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.1491</v>
+        <v>-1.132</v>
       </c>
       <c r="I41" t="n">
         <v>-1.1706</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.1334</v>
+        <v>-2.1322</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.4922</v>
+        <v>-0.4919</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.2832</v>
+        <v>-1.2934</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.1334</v>
+        <v>-2.1322</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1684</v>
+        <v>-0.1672</v>
       </c>
       <c r="G42" t="n">
         <v>-1.965</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1684</v>
+        <v>-0.1672</v>
       </c>
       <c r="I42" t="n">
         <v>-0.17</v>

--- a/database/event/4979/event_4979_evp_summary.xlsx
+++ b/database/event/4979/event_4979_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.6295</v>
+        <v>8.6462</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2217</v>
+        <v>1.9948</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3925</v>
+        <v>3.2653</v>
       </c>
       <c r="E2" t="n">
-        <v>9.6295</v>
+        <v>8.6462</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7679</v>
+        <v>4.4518</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8616</v>
+        <v>4.1944</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6219</v>
+        <v>11.9778</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3672</v>
+        <v>6.2279</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8616</v>
+        <v>4.1944</v>
       </c>
       <c r="K2" t="n">
         <v>103</v>
@@ -529,7 +529,7 @@
         <v>144</v>
       </c>
       <c r="M2" t="n">
-        <v>10.2288</v>
+        <v>10.4223</v>
       </c>
       <c r="N2" t="n">
         <v>247</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6887</v>
+        <v>6.1905</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5432</v>
+        <v>1.4283</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2209</v>
+        <v>2.1567</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6887</v>
+        <v>6.1905</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8207</v>
+        <v>2.9659</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8679</v>
+        <v>3.2246</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8207</v>
+        <v>4.9635</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2863</v>
+        <v>2.5808</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8679</v>
+        <v>3.2246</v>
       </c>
       <c r="K3" t="n">
         <v>103</v>
@@ -575,7 +575,7 @@
         <v>144</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1542</v>
+        <v>5.805400000000001</v>
       </c>
       <c r="N3" t="n">
         <v>247</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2258</v>
+        <v>4.6707</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2057</v>
+        <v>1.0776</v>
       </c>
       <c r="D4" t="n">
-        <v>1.638</v>
+        <v>1.4706</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2258</v>
+        <v>4.6707</v>
       </c>
       <c r="F4" t="n">
-        <v>4.254</v>
+        <v>2.85</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9718</v>
+        <v>1.8207</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5542</v>
+        <v>4.5552</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6913</v>
+        <v>2.3685</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9718</v>
+        <v>1.8207</v>
       </c>
       <c r="K4" t="n">
         <v>142</v>
@@ -621,7 +621,7 @@
         <v>146</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6631</v>
+        <v>4.1892</v>
       </c>
       <c r="N4" t="n">
         <v>288</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9251</v>
+        <v>4.5652</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1363</v>
+        <v>1.0533</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5183</v>
+        <v>1.4229</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9251</v>
+        <v>4.5652</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9737</v>
+        <v>3.7203</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9514</v>
+        <v>0.8449</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9737</v>
+        <v>7.6218</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4103</v>
+        <v>3.963</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9514</v>
+        <v>0.8449</v>
       </c>
       <c r="K5" t="n">
         <v>142</v>
@@ -667,7 +667,7 @@
         <v>146</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3617</v>
+        <v>4.8079</v>
       </c>
       <c r="N5" t="n">
         <v>288</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0611</v>
+        <v>4.1886</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9664</v>
       </c>
       <c r="D6" t="n">
-        <v>1.174</v>
+        <v>1.2529</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0611</v>
+        <v>4.1886</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4942</v>
+        <v>2.8253</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5669</v>
+        <v>1.3633</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4942</v>
+        <v>2.8441</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5364</v>
+        <v>3.0829</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5669</v>
+        <v>1.3633</v>
       </c>
       <c r="K6" t="n">
         <v>155</v>
@@ -713,7 +713,7 @@
         <v>106</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1033</v>
+        <v>4.4462</v>
       </c>
       <c r="N6" t="n">
         <v>261</v>
@@ -722,725 +722,725 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xsepower</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4376</v>
+        <v>3.7229</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7931</v>
+        <v>0.8589</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9256</v>
+        <v>1.0427</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4376</v>
+        <v>3.7229</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2276</v>
+        <v>2.7752</v>
       </c>
       <c r="G7" t="n">
-        <v>0.21</v>
+        <v>0.9477</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2276</v>
+        <v>4.2917</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3098</v>
+        <v>2.2315</v>
       </c>
       <c r="J7" t="n">
-        <v>0.21</v>
+        <v>0.9477</v>
       </c>
       <c r="K7" t="n">
-        <v>189</v>
+        <v>103</v>
       </c>
       <c r="L7" t="n">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5198</v>
+        <v>3.1792</v>
       </c>
       <c r="N7" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4036</v>
+        <v>3.3678</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7853</v>
+        <v>0.777</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9121</v>
+        <v>0.8824</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4036</v>
+        <v>3.3678</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6493</v>
+        <v>3.1154</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2457</v>
+        <v>0.2524</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6493</v>
+        <v>3.4811</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9579</v>
+        <v>4.0901</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2457</v>
+        <v>0.2524</v>
       </c>
       <c r="K8" t="n">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="L8" t="n">
-        <v>144</v>
+        <v>56</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7122</v>
+        <v>4.342499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>247</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0004</v>
+        <v>3.3584</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6923</v>
+        <v>0.7748</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7514</v>
+        <v>0.8781</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0004</v>
+        <v>3.3584</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2141</v>
+        <v>3.2389</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7863</v>
+        <v>0.1195</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2141</v>
+        <v>3.7524</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7946</v>
+        <v>4.4088</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7863</v>
+        <v>0.1195</v>
       </c>
       <c r="K9" t="n">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="L9" t="n">
-        <v>144</v>
+        <v>56</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5809</v>
+        <v>4.528300000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>247</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>xsepower</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7784</v>
+        <v>3.3193</v>
       </c>
       <c r="C10" t="n">
-        <v>0.641</v>
+        <v>0.7658</v>
       </c>
       <c r="D10" t="n">
-        <v>0.663</v>
+        <v>0.8605</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7784</v>
+        <v>3.3193</v>
       </c>
       <c r="F10" t="n">
-        <v>2.664</v>
+        <v>3.0505</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1144</v>
+        <v>0.2688</v>
       </c>
       <c r="H10" t="n">
-        <v>2.664</v>
+        <v>3.3385</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7549</v>
+        <v>3.7676</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1144</v>
+        <v>0.2688</v>
       </c>
       <c r="K10" t="n">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="L10" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8693</v>
+        <v>4.0364</v>
       </c>
       <c r="N10" t="n">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6414</v>
+        <v>3.2436</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.7484</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.8263</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6414</v>
+        <v>3.2436</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2672</v>
+        <v>3.3392</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3742</v>
+        <v>-0.0956</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2672</v>
+        <v>6.279</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2672</v>
+        <v>3.2648</v>
       </c>
       <c r="J11" t="n">
-        <v>2.3742</v>
+        <v>-0.0956</v>
       </c>
       <c r="K11" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="L11" t="n">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6414</v>
+        <v>3.1692</v>
       </c>
       <c r="N11" t="n">
-        <v>179</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5952</v>
+        <v>2.774</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5988</v>
+        <v>0.64</v>
       </c>
       <c r="D12" t="n">
-        <v>0.59</v>
+        <v>0.6143</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5952</v>
+        <v>2.774</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4226</v>
+        <v>1.6801</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1726</v>
+        <v>1.0939</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4226</v>
+        <v>1.6801</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5052</v>
+        <v>1.8211</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1726</v>
+        <v>1.0939</v>
       </c>
       <c r="K12" t="n">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="L12" t="n">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6778</v>
+        <v>2.915</v>
       </c>
       <c r="N12" t="n">
-        <v>231</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.091</v>
+        <v>2.7371</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4824</v>
+        <v>0.6315</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3891</v>
+        <v>0.5977</v>
       </c>
       <c r="E13" t="n">
-        <v>2.091</v>
+        <v>2.7371</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5333</v>
+        <v>2.2384</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5577</v>
+        <v>0.4987</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5333</v>
+        <v>2.4004</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5856</v>
+        <v>1.2481</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5577</v>
+        <v>0.4987</v>
       </c>
       <c r="K13" t="n">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="L13" t="n">
-        <v>56</v>
+        <v>146</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1433</v>
+        <v>1.7468</v>
       </c>
       <c r="N13" t="n">
-        <v>231</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9788</v>
+        <v>2.6462</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4565</v>
+        <v>0.6105</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3444</v>
+        <v>0.5566</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9788</v>
+        <v>2.6462</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3737</v>
+        <v>2.5147</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3525</v>
+        <v>0.1315</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3737</v>
+        <v>3.374</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.38</v>
+        <v>1.7543</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3525</v>
+        <v>0.1315</v>
       </c>
       <c r="K14" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="L14" t="n">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9725</v>
+        <v>1.8858</v>
       </c>
       <c r="N14" t="n">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Jerry</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9335</v>
+        <v>2.585</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4461</v>
+        <v>0.5964</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3264</v>
+        <v>0.529</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9335</v>
+        <v>2.585</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0775</v>
+        <v>3.2264</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.144</v>
+        <v>-0.6414</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0775</v>
+        <v>3.7249</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6839</v>
+        <v>4.2036</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.144</v>
+        <v>-0.6414</v>
       </c>
       <c r="K15" t="n">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="L15" t="n">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5399</v>
+        <v>3.5622</v>
       </c>
       <c r="N15" t="n">
-        <v>288</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>facecrack</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8524</v>
+        <v>2.4644</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4274</v>
+        <v>0.5686</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2941</v>
+        <v>0.4745</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8524</v>
+        <v>2.4644</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5326</v>
+        <v>0.3826</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3198</v>
+        <v>2.0818</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5326</v>
+        <v>0.3826</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5716</v>
+        <v>0.3826</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3198</v>
+        <v>2.0818</v>
       </c>
       <c r="K16" t="n">
-        <v>189</v>
+        <v>65</v>
       </c>
       <c r="L16" t="n">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8914</v>
+        <v>2.4644</v>
       </c>
       <c r="N16" t="n">
-        <v>239</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>facecrack</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.849</v>
+        <v>2.3367</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4266</v>
+        <v>0.5391</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2927</v>
+        <v>0.4169</v>
       </c>
       <c r="E17" t="n">
-        <v>1.849</v>
+        <v>2.3367</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4546</v>
+        <v>1.9763</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3944</v>
+        <v>0.3604</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4546</v>
+        <v>1.9763</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4623</v>
+        <v>2.2303</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3944</v>
+        <v>0.3604</v>
       </c>
       <c r="K17" t="n">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="L17" t="n">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8567</v>
+        <v>2.5907</v>
       </c>
       <c r="N17" t="n">
-        <v>261</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jerry</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.771</v>
+        <v>2.3205</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4086</v>
+        <v>0.5354</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2617</v>
+        <v>0.4096</v>
       </c>
       <c r="E18" t="n">
-        <v>1.771</v>
+        <v>2.3205</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7595</v>
+        <v>1.7557</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9885</v>
+        <v>0.5648</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7595</v>
+        <v>1.7557</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8297</v>
+        <v>2.0628</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9885</v>
+        <v>0.5648</v>
       </c>
       <c r="K18" t="n">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="L18" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8412</v>
+        <v>2.6276</v>
       </c>
       <c r="N18" t="n">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>almazer</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.765</v>
+        <v>2.1867</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4072</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2593</v>
+        <v>0.3492</v>
       </c>
       <c r="E19" t="n">
-        <v>1.765</v>
+        <v>2.1867</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5614</v>
+        <v>2.2437</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2036</v>
+        <v>-0.057</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5614</v>
+        <v>2.2437</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5709</v>
+        <v>2.5321</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2036</v>
+        <v>-0.057</v>
       </c>
       <c r="K19" t="n">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="L19" t="n">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7745</v>
+        <v>2.4751</v>
       </c>
       <c r="N19" t="n">
-        <v>261</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>almazer</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7296</v>
+        <v>2.1141</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3991</v>
+        <v>0.4878</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2452</v>
+        <v>0.3164</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7296</v>
+        <v>2.1141</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8871</v>
+        <v>1.2198</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1575</v>
+        <v>0.8943</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8871</v>
+        <v>1.2198</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9351</v>
+        <v>1.3222</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1575</v>
+        <v>0.8943</v>
       </c>
       <c r="K20" t="n">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="L20" t="n">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7776</v>
+        <v>2.2165</v>
       </c>
       <c r="N20" t="n">
-        <v>239</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6217</v>
+        <v>2.0722</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3742</v>
+        <v>0.4781</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2022</v>
+        <v>0.2975</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6217</v>
+        <v>2.0722</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3029</v>
+        <v>2.3462</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3188</v>
+        <v>-0.274</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3029</v>
+        <v>2.3462</v>
       </c>
       <c r="I21" t="n">
-        <v>1.056</v>
+        <v>2.6477</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3188</v>
+        <v>-0.274</v>
       </c>
       <c r="K21" t="n">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="L21" t="n">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3748</v>
+        <v>2.3737</v>
       </c>
       <c r="N21" t="n">
-        <v>288</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2342</v>
+        <v>1.8818</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2848</v>
+        <v>0.4342</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0478</v>
+        <v>0.2115</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2342</v>
+        <v>1.8818</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7031</v>
+        <v>0.0436</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4689</v>
+        <v>1.8382</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7031</v>
+        <v>0.0436</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7319</v>
+        <v>0.0473</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4689</v>
+        <v>1.8382</v>
       </c>
       <c r="K22" t="n">
         <v>162</v>
@@ -1449,7 +1449,7 @@
         <v>114</v>
       </c>
       <c r="M22" t="n">
-        <v>1.263</v>
+        <v>1.8855</v>
       </c>
       <c r="N22" t="n">
         <v>276</v>
@@ -1458,81 +1458,81 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1631</v>
+        <v>1.8685</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2683</v>
+        <v>0.4311</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0195</v>
+        <v>0.2055</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1631</v>
+        <v>1.8685</v>
       </c>
       <c r="F23" t="n">
-        <v>1.98</v>
+        <v>2.2829</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8169</v>
+        <v>-0.4144</v>
       </c>
       <c r="H23" t="n">
-        <v>1.98</v>
+        <v>2.2829</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0475</v>
+        <v>2.4745</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8169</v>
+        <v>-0.4144</v>
       </c>
       <c r="K23" t="n">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="L23" t="n">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2306</v>
+        <v>2.0601</v>
       </c>
       <c r="N23" t="n">
-        <v>231</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.122</v>
+        <v>1.8425</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2589</v>
+        <v>0.4251</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0031</v>
+        <v>0.1938</v>
       </c>
       <c r="E24" t="n">
-        <v>1.122</v>
+        <v>1.8425</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3416</v>
+        <v>2.1016</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4636</v>
+        <v>-0.2591</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3416</v>
+        <v>2.1016</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3474</v>
+        <v>2.278</v>
       </c>
       <c r="J24" t="n">
-        <v>1.4636</v>
+        <v>-0.2591</v>
       </c>
       <c r="K24" t="n">
         <v>155</v>
@@ -1541,7 +1541,7 @@
         <v>106</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1162</v>
+        <v>2.0189</v>
       </c>
       <c r="N24" t="n">
         <v>261</v>
@@ -1550,139 +1550,139 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0475</v>
+        <v>1.7065</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2417</v>
+        <v>0.3937</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0266</v>
+        <v>0.1324</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0475</v>
+        <v>1.7065</v>
       </c>
       <c r="F25" t="n">
-        <v>1.559</v>
+        <v>2.2276</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5115</v>
+        <v>-0.5211</v>
       </c>
       <c r="H25" t="n">
-        <v>1.559</v>
+        <v>2.2276</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5987</v>
+        <v>2.6173</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5115</v>
+        <v>-0.5211</v>
       </c>
       <c r="K25" t="n">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="L25" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0872</v>
+        <v>2.0962</v>
       </c>
       <c r="N25" t="n">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.894</v>
+        <v>1.5296</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2063</v>
+        <v>0.3529</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0877</v>
+        <v>0.0525</v>
       </c>
       <c r="E26" t="n">
-        <v>0.894</v>
+        <v>1.5296</v>
       </c>
       <c r="F26" t="n">
-        <v>0.894</v>
+        <v>0.3437</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.1859</v>
       </c>
       <c r="H26" t="n">
-        <v>0.894</v>
+        <v>0.3437</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9015</v>
+        <v>0.3726</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1.1859</v>
       </c>
       <c r="K26" t="n">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M26" t="n">
-        <v>0.9015</v>
+        <v>1.5585</v>
       </c>
       <c r="N26" t="n">
-        <v>169</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1676</v>
+        <v>0.7947</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0387</v>
+        <v>0.1834</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3771</v>
+        <v>-0.2792</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1676</v>
+        <v>0.7947</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.7947</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4861</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.7947</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6647</v>
+        <v>0.8274</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4861</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="L27" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1786</v>
+        <v>0.8274</v>
       </c>
       <c r="N27" t="n">
-        <v>261</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.136</v>
+        <v>0.425</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0314</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3897</v>
+        <v>-0.4461</v>
       </c>
       <c r="E28" t="n">
-        <v>0.136</v>
+        <v>0.425</v>
       </c>
       <c r="F28" t="n">
-        <v>0.136</v>
+        <v>0.425</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.136</v>
+        <v>0.425</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1371</v>
+        <v>0.4425</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1371</v>
+        <v>0.4425</v>
       </c>
       <c r="N28" t="n">
         <v>169</v>
@@ -1734,139 +1734,139 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3543</v>
+        <v>0.3165</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.08169999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5851</v>
+        <v>-0.4951</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3543</v>
+        <v>0.3165</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3543</v>
+        <v>2.3165</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3543</v>
+        <v>2.6754</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3573</v>
+        <v>1.3911</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="K29" t="n">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3573</v>
+        <v>-0.6089</v>
       </c>
       <c r="N29" t="n">
-        <v>169</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DeStRoYeR</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6938</v>
+        <v>0.0165</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1601</v>
+        <v>0.0038</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.6306</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6938</v>
+        <v>0.0165</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6938</v>
+        <v>0.0165</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6938</v>
+        <v>0.0165</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6938</v>
+        <v>0.0172</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>83</v>
+        <v>169</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6938</v>
+        <v>0.0172</v>
       </c>
       <c r="N30" t="n">
-        <v>83</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>DeStRoYeR</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.0208</v>
+        <v>-0.4408</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2355</v>
+        <v>-0.1017</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8506</v>
+        <v>-0.837</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.0208</v>
+        <v>-0.4408</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9792</v>
+        <v>-0.4408</v>
       </c>
       <c r="G31" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9792</v>
+        <v>-0.4408</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7937</v>
+        <v>-0.4408</v>
       </c>
       <c r="J31" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="L31" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.2063</v>
+        <v>-0.4408</v>
       </c>
       <c r="N31" t="n">
-        <v>247</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.0449</v>
+        <v>-0.5837</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2411</v>
+        <v>-0.1347</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8602</v>
+        <v>-0.9015</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.0449</v>
+        <v>-0.5837</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.0449</v>
+        <v>-0.5837</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.0449</v>
+        <v>-0.5837</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.0537</v>
+        <v>-0.6077</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.0537</v>
+        <v>-0.6077</v>
       </c>
       <c r="N32" t="n">
         <v>169</v>
@@ -1918,461 +1918,461 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0613</v>
+        <v>-0.7248</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2449</v>
+        <v>-0.1672</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8667</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0613</v>
+        <v>-0.7248</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6193</v>
+        <v>-0.7248</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.442</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6193</v>
+        <v>-0.7248</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.502</v>
+        <v>-0.7546</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.442</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="L33" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.944</v>
+        <v>-0.7546</v>
       </c>
       <c r="N33" t="n">
-        <v>288</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SLOWLY</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.1801</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2723</v>
+        <v>-0.1859</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9141</v>
+        <v>-1.0018</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.1801</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.1801</v>
+        <v>-0.7598</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.0461</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.1801</v>
+        <v>-0.7598</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.1801</v>
+        <v>-0.8236</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.0461</v>
       </c>
       <c r="K34" t="n">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.1801</v>
+        <v>-0.8697</v>
       </c>
       <c r="N34" t="n">
-        <v>83</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>SLOWLY</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1987</v>
+        <v>-0.8861</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2766</v>
+        <v>-0.2044</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9215</v>
+        <v>-1.038</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1987</v>
+        <v>-0.8861</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1987</v>
+        <v>-0.8861</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1987</v>
+        <v>-0.8861</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.2088</v>
+        <v>-0.8861</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>169</v>
+        <v>83</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2088</v>
+        <v>-0.8861</v>
       </c>
       <c r="N35" t="n">
-        <v>169</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2978</v>
+        <v>-0.93</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2994</v>
+        <v>-0.2146</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.961</v>
+        <v>-1.0579</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2978</v>
+        <v>-0.93</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2129</v>
+        <v>-0.7181</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0849</v>
+        <v>-0.2119</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2129</v>
+        <v>-0.7181</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.2334</v>
+        <v>-0.3734</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.0849</v>
+        <v>-0.2119</v>
       </c>
       <c r="K36" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="L36" t="n">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.3183</v>
+        <v>-0.5853</v>
       </c>
       <c r="N36" t="n">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B1NGO</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3398</v>
+        <v>-0.977</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3091</v>
+        <v>-0.2254</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9777</v>
+        <v>-1.0791</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3398</v>
+        <v>-0.977</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.3398</v>
+        <v>-0.4001</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.5769</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3398</v>
+        <v>-0.4001</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.3398</v>
+        <v>-0.4701</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.5769</v>
       </c>
       <c r="K37" t="n">
-        <v>83</v>
+        <v>175</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3398</v>
+        <v>-1.047</v>
       </c>
       <c r="N37" t="n">
-        <v>83</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>crush</t>
+          <t>B1NGO</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.441</v>
+        <v>-0.984</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3325</v>
+        <v>-0.227</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.018</v>
+        <v>-1.0822</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.441</v>
+        <v>-0.984</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.441</v>
+        <v>-0.984</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.441</v>
+        <v>-0.984</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.4531</v>
+        <v>-0.984</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4531</v>
+        <v>-0.984</v>
       </c>
       <c r="N38" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>crush</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7411</v>
+        <v>-1.0922</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4017</v>
+        <v>-0.252</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1376</v>
+        <v>-1.1311</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7411</v>
+        <v>-1.0922</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.7411</v>
+        <v>-1.0922</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.7411</v>
+        <v>-1.0922</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.7411</v>
+        <v>-1.1371</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7411</v>
+        <v>-1.1371</v>
       </c>
       <c r="N39" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FIOURN</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7911</v>
+        <v>-1.3572</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4132</v>
+        <v>-0.3131</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1575</v>
+        <v>-1.2507</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7911</v>
+        <v>-1.3572</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7911</v>
+        <v>0.2666</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-1.6238</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7911</v>
+        <v>0.2666</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7911</v>
+        <v>0.289</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-1.6238</v>
       </c>
       <c r="K40" t="n">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7911</v>
+        <v>-1.3348</v>
       </c>
       <c r="N40" t="n">
-        <v>83</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.0325</v>
+        <v>-1.4214</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4689</v>
+        <v>-0.3279</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2537</v>
+        <v>-1.2797</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.0325</v>
+        <v>-1.4214</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.132</v>
+        <v>-1.4214</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9005</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.132</v>
+        <v>-1.4214</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.1706</v>
+        <v>-1.4214</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9005</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>175</v>
+        <v>83</v>
       </c>
       <c r="L41" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.0711</v>
+        <v>-1.4214</v>
       </c>
       <c r="N41" t="n">
-        <v>231</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>FIOURN</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.1322</v>
+        <v>-1.5066</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.4919</v>
+        <v>-0.3476</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.2934</v>
+        <v>-1.3182</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.1322</v>
+        <v>-1.5066</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1672</v>
+        <v>-1.5066</v>
       </c>
       <c r="G42" t="n">
-        <v>-1.965</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1672</v>
+        <v>-1.5066</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.17</v>
+        <v>-1.5066</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.965</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="L42" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.135</v>
+        <v>-1.5066</v>
       </c>
       <c r="N42" t="n">
-        <v>276</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2475,10 +2475,10 @@
         <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8315</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>29.1025</v>
+        <v>28.1015</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>1.02</v>
       </c>
       <c r="I3" t="n">
-        <v>0.041</v>
+        <v>0.0475</v>
       </c>
       <c r="J3" t="n">
-        <v>1.435</v>
+        <v>1.6625</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.022</v>
+        <v>-0.0025</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.77</v>
+        <v>-0.08749999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1671</v>
+        <v>-0.0917</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.8485</v>
+        <v>-3.2095</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.64</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6018</v>
+        <v>-0.396</v>
       </c>
       <c r="J6" t="n">
-        <v>-21.063</v>
+        <v>-13.86</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5219</v>
+        <v>0.4428</v>
       </c>
       <c r="J7" t="n">
-        <v>18.2665</v>
+        <v>15.498</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.26</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4558</v>
+        <v>0.3812</v>
       </c>
       <c r="J8" t="n">
-        <v>15.953</v>
+        <v>13.342</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.12</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2484</v>
+        <v>0.1981</v>
       </c>
       <c r="J9" t="n">
-        <v>8.694000000000001</v>
+        <v>6.9335</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>0.74</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4737</v>
+        <v>-0.3018</v>
       </c>
       <c r="J10" t="n">
-        <v>-16.5795</v>
+        <v>-10.563</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>0.74</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4737</v>
+        <v>-0.3018</v>
       </c>
       <c r="J11" t="n">
-        <v>-16.5795</v>
+        <v>-10.563</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.87</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9237</v>
+        <v>1.6227</v>
       </c>
       <c r="J12" t="n">
-        <v>53.8636</v>
+        <v>45.4356</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>1.01</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0407</v>
+        <v>0.021</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1396</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.99</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.159</v>
+        <v>-0.0887</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.452</v>
+        <v>-2.4836</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.93</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3705</v>
+        <v>-0.299</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.374</v>
+        <v>-8.372</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4294</v>
+        <v>-0.3593</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.0232</v>
+        <v>-10.0604</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.13</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2975</v>
+        <v>0.3226</v>
       </c>
       <c r="J17" t="n">
-        <v>8.33</v>
+        <v>9.0328</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2485</v>
+        <v>0.2615</v>
       </c>
       <c r="J18" t="n">
-        <v>6.958</v>
+        <v>7.322</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>0.89</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2259</v>
+        <v>-0.1393</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.3252</v>
+        <v>-3.9004</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>0.83</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3245</v>
+        <v>-0.2022</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.086</v>
+        <v>-5.6616</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3991</v>
+        <v>-0.2525</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.1748</v>
+        <v>-7.07</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.59</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3856</v>
+        <v>1.2485</v>
       </c>
       <c r="J22" t="n">
-        <v>34.64</v>
+        <v>31.2125</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.42</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0447</v>
+        <v>1.0302</v>
       </c>
       <c r="J23" t="n">
-        <v>26.1175</v>
+        <v>25.755</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>1.3</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7764</v>
+        <v>0.7867</v>
       </c>
       <c r="J24" t="n">
-        <v>19.41</v>
+        <v>19.6675</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>1.12</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2804</v>
+        <v>0.3519</v>
       </c>
       <c r="J25" t="n">
-        <v>7.01</v>
+        <v>8.797499999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9605</v>
+        <v>-0.9302</v>
       </c>
       <c r="J26" t="n">
-        <v>-24.0125</v>
+        <v>-23.255</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.11</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3116</v>
+        <v>0.3305</v>
       </c>
       <c r="J27" t="n">
-        <v>7.79</v>
+        <v>8.262499999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>0.78</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3578</v>
+        <v>-0.2373</v>
       </c>
       <c r="J28" t="n">
-        <v>-8.945</v>
+        <v>-5.9325</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3738</v>
+        <v>-0.247</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.345000000000001</v>
+        <v>-6.175</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>0.74</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4201</v>
+        <v>-0.2759</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.5025</v>
+        <v>-6.8975</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.73</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4351</v>
+        <v>-0.2855</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.8775</v>
+        <v>-7.1375</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.24</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6997</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>19.5916</v>
+        <v>15.0304</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5191</v>
+        <v>0.4341</v>
       </c>
       <c r="J33" t="n">
-        <v>14.5348</v>
+        <v>12.1548</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.14</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4334</v>
+        <v>0.3886</v>
       </c>
       <c r="J34" t="n">
-        <v>12.1352</v>
+        <v>10.8808</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>1.06</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1616</v>
+        <v>0.2053</v>
       </c>
       <c r="J35" t="n">
-        <v>4.5248</v>
+        <v>5.7484</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2957</v>
+        <v>-0.2275</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.2796</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.32</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5763</v>
+        <v>0.5441</v>
       </c>
       <c r="J37" t="n">
-        <v>16.1364</v>
+        <v>15.2348</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>0.9</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1915</v>
+        <v>-0.1253</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.362</v>
+        <v>-3.5084</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>0.82</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3296</v>
+        <v>-0.2085</v>
       </c>
       <c r="J39" t="n">
-        <v>-9.2288</v>
+        <v>-5.838</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.79</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3754</v>
+        <v>-0.2386</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.5112</v>
+        <v>-6.6808</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4476</v>
+        <v>-0.2876</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.5328</v>
+        <v>-8.0528</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.37</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.7025</v>
       </c>
       <c r="J42" t="n">
-        <v>28.836</v>
+        <v>21.075</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.28</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7562</v>
+        <v>0.5807</v>
       </c>
       <c r="J43" t="n">
-        <v>22.686</v>
+        <v>17.421</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.11</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2758</v>
+        <v>0.3314</v>
       </c>
       <c r="J44" t="n">
-        <v>8.273999999999999</v>
+        <v>9.942</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.08</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1868</v>
+        <v>0.2496</v>
       </c>
       <c r="J45" t="n">
-        <v>5.604</v>
+        <v>7.488</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>1.06</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1246</v>
+        <v>0.189</v>
       </c>
       <c r="J46" t="n">
-        <v>3.738</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.26</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4953</v>
+        <v>0.4787</v>
       </c>
       <c r="J47" t="n">
-        <v>14.859</v>
+        <v>14.361</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>1.24</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4681</v>
+        <v>0.4571</v>
       </c>
       <c r="J48" t="n">
-        <v>14.043</v>
+        <v>13.713</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.75</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4351</v>
+        <v>-0.2786</v>
       </c>
       <c r="J49" t="n">
-        <v>-13.053</v>
+        <v>-8.358000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5174</v>
+        <v>-0.3362</v>
       </c>
       <c r="J50" t="n">
-        <v>-15.522</v>
+        <v>-10.086</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.66</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5568</v>
+        <v>-0.3646</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.704</v>
+        <v>-10.938</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.54</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3243</v>
+        <v>0.9314</v>
       </c>
       <c r="J52" t="n">
-        <v>37.0804</v>
+        <v>26.0792</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.383</v>
+        <v>0.3848</v>
       </c>
       <c r="J53" t="n">
-        <v>10.724</v>
+        <v>10.7744</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>1.08</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2006</v>
+        <v>0.2558</v>
       </c>
       <c r="J54" t="n">
-        <v>5.6168</v>
+        <v>7.1624</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>1.01</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0461</v>
+        <v>0.018</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.2908</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1051</v>
+        <v>-0.0369</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.9428</v>
+        <v>-1.0332</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5916</v>
+        <v>0.5566</v>
       </c>
       <c r="J57" t="n">
-        <v>16.5648</v>
+        <v>15.5848</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.02</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0955</v>
+        <v>0.078</v>
       </c>
       <c r="J58" t="n">
-        <v>2.674</v>
+        <v>2.184</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>0.98</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0271</v>
+        <v>-0.0314</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.7588</v>
+        <v>-0.8792</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5221</v>
+        <v>-0.3389</v>
       </c>
       <c r="J60" t="n">
-        <v>-14.6188</v>
+        <v>-9.4892</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.68</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5352</v>
+        <v>-0.3484</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.9856</v>
+        <v>-9.7552</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.56</v>
       </c>
       <c r="I62" t="n">
-        <v>1.3955</v>
+        <v>0.9771</v>
       </c>
       <c r="J62" t="n">
-        <v>39.074</v>
+        <v>27.3588</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.55</v>
       </c>
       <c r="I63" t="n">
-        <v>1.3761</v>
+        <v>0.9641</v>
       </c>
       <c r="J63" t="n">
-        <v>38.5308</v>
+        <v>26.9948</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>1.14</v>
       </c>
       <c r="I64" t="n">
-        <v>0.449</v>
+        <v>0.3914</v>
       </c>
       <c r="J64" t="n">
-        <v>12.572</v>
+        <v>10.9592</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.65</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0396</v>
+        <v>-1.0198</v>
       </c>
       <c r="J65" t="n">
-        <v>-29.1088</v>
+        <v>-28.5544</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.226</v>
+        <v>-1.2318</v>
       </c>
       <c r="J66" t="n">
-        <v>-34.328</v>
+        <v>-34.4904</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.09</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2008</v>
+        <v>0.2204</v>
       </c>
       <c r="J67" t="n">
-        <v>5.6224</v>
+        <v>6.1712</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.08</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1827</v>
+        <v>0.1997</v>
       </c>
       <c r="J68" t="n">
-        <v>5.1156</v>
+        <v>5.5916</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1239</v>
+        <v>0.1349</v>
       </c>
       <c r="J69" t="n">
-        <v>3.4692</v>
+        <v>3.7772</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>1.04</v>
       </c>
       <c r="I70" t="n">
-        <v>0.102</v>
+        <v>0.112</v>
       </c>
       <c r="J70" t="n">
-        <v>2.856</v>
+        <v>3.136</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2998</v>
+        <v>-0.1802</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.394399999999999</v>
+        <v>-5.0456</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.05</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1956</v>
+        <v>0.1835</v>
       </c>
       <c r="J72" t="n">
-        <v>5.0856</v>
+        <v>4.771</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>0.95</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0513</v>
+        <v>-0.0599</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.3338</v>
+        <v>-1.5574</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>0.85</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2466</v>
+        <v>-0.1716</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.4116</v>
+        <v>-4.4616</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>0.75</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4146</v>
+        <v>-0.2698</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.7796</v>
+        <v>-7.0148</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.66</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5413</v>
+        <v>-0.3557</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.0738</v>
+        <v>-9.248200000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.46</v>
       </c>
       <c r="I77" t="n">
-        <v>1.1512</v>
+        <v>0.821</v>
       </c>
       <c r="J77" t="n">
-        <v>29.9312</v>
+        <v>21.346</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.4</v>
       </c>
       <c r="I78" t="n">
-        <v>1.0259</v>
+        <v>0.7423</v>
       </c>
       <c r="J78" t="n">
-        <v>26.6734</v>
+        <v>19.2998</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>1.29</v>
       </c>
       <c r="I79" t="n">
-        <v>0.78</v>
+        <v>0.5944</v>
       </c>
       <c r="J79" t="n">
-        <v>20.28</v>
+        <v>15.4544</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.92</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4133</v>
+        <v>-0.3394</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.7458</v>
+        <v>-8.824400000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.83</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6523</v>
+        <v>-0.5918</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.9598</v>
+        <v>-15.3868</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.23</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4192</v>
+        <v>0.424</v>
       </c>
       <c r="J82" t="n">
-        <v>12.576</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.19</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3621</v>
+        <v>0.3813</v>
       </c>
       <c r="J83" t="n">
-        <v>10.863</v>
+        <v>11.439</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1.07</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1657</v>
+        <v>0.1794</v>
       </c>
       <c r="J84" t="n">
-        <v>4.971</v>
+        <v>5.382</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3592</v>
+        <v>-0.2212</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.776</v>
+        <v>-6.636</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4023</v>
+        <v>-0.2513</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.069</v>
+        <v>-7.539</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.52</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2963</v>
+        <v>0.912</v>
       </c>
       <c r="J87" t="n">
-        <v>38.889</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.42</v>
       </c>
       <c r="I88" t="n">
-        <v>1.0931</v>
+        <v>0.7804</v>
       </c>
       <c r="J88" t="n">
-        <v>32.793</v>
+        <v>23.412</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>1.1</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2767</v>
+        <v>0.3167</v>
       </c>
       <c r="J89" t="n">
-        <v>8.301</v>
+        <v>9.500999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6879</v>
+        <v>-0.6322</v>
       </c>
       <c r="J90" t="n">
-        <v>-20.637</v>
+        <v>-18.966</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6879</v>
+        <v>-0.6322</v>
       </c>
       <c r="J91" t="n">
-        <v>-20.637</v>
+        <v>-18.966</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.55</v>
       </c>
       <c r="I92" t="n">
-        <v>1.2234</v>
+        <v>0.8897</v>
       </c>
       <c r="J92" t="n">
-        <v>26.9148</v>
+        <v>19.5734</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.45</v>
       </c>
       <c r="I93" t="n">
-        <v>1.0128</v>
+        <v>0.7691</v>
       </c>
       <c r="J93" t="n">
-        <v>22.2816</v>
+        <v>16.9202</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>1.44</v>
       </c>
       <c r="I94" t="n">
-        <v>0.99</v>
+        <v>0.757</v>
       </c>
       <c r="J94" t="n">
-        <v>21.78</v>
+        <v>16.654</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>1.33</v>
       </c>
       <c r="I95" t="n">
-        <v>0.716</v>
+        <v>0.6213</v>
       </c>
       <c r="J95" t="n">
-        <v>15.752</v>
+        <v>13.6686</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>1.26</v>
       </c>
       <c r="I96" t="n">
-        <v>0.5554</v>
+        <v>0.5278</v>
       </c>
       <c r="J96" t="n">
-        <v>12.2188</v>
+        <v>11.6116</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2907</v>
+        <v>0.3019</v>
       </c>
       <c r="J97" t="n">
-        <v>6.3954</v>
+        <v>6.6418</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>0.78</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.3041</v>
+        <v>-0.2301</v>
       </c>
       <c r="J98" t="n">
-        <v>-6.6902</v>
+        <v>-5.0622</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>0.78</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3041</v>
+        <v>-0.2301</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.6902</v>
+        <v>-5.0622</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>0.57</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.4262</v>
       </c>
       <c r="J100" t="n">
-        <v>-13.9832</v>
+        <v>-9.3764</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.57</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.4262</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.9832</v>
+        <v>-9.3764</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.29</v>
       </c>
       <c r="I102" t="n">
-        <v>0.849</v>
+        <v>0.6208</v>
       </c>
       <c r="J102" t="n">
-        <v>23.772</v>
+        <v>17.3824</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.24</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7313</v>
+        <v>0.5485</v>
       </c>
       <c r="J103" t="n">
-        <v>20.4764</v>
+        <v>15.358</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>1.17</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5546</v>
+        <v>0.4436</v>
       </c>
       <c r="J104" t="n">
-        <v>15.5288</v>
+        <v>12.4208</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>0.8</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.6382</v>
       </c>
       <c r="J105" t="n">
-        <v>-19.292</v>
+        <v>-17.8696</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.79</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7134</v>
+        <v>-0.664</v>
       </c>
       <c r="J106" t="n">
-        <v>-19.9752</v>
+        <v>-18.592</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.31</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5141</v>
+        <v>0.4989</v>
       </c>
       <c r="J107" t="n">
-        <v>14.3948</v>
+        <v>13.9692</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.07</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1466</v>
+        <v>0.1731</v>
       </c>
       <c r="J108" t="n">
-        <v>4.1048</v>
+        <v>4.8468</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>1.06</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1241</v>
+        <v>0.1522</v>
       </c>
       <c r="J109" t="n">
-        <v>3.4748</v>
+        <v>4.2616</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0291</v>
+        <v>0.0585</v>
       </c>
       <c r="J110" t="n">
-        <v>0.8148</v>
+        <v>1.638</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.83</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3529</v>
+        <v>-0.2152</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.8812</v>
+        <v>-6.0256</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.75</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9396</v>
+        <v>0.8591</v>
       </c>
       <c r="J112" t="n">
-        <v>20.6712</v>
+        <v>18.9002</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.46</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6191</v>
+        <v>0.5587</v>
       </c>
       <c r="J113" t="n">
-        <v>13.6202</v>
+        <v>12.2914</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.41</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5572</v>
+        <v>0.5053</v>
       </c>
       <c r="J114" t="n">
-        <v>12.2584</v>
+        <v>11.1166</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>1.15</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1827</v>
+        <v>0.2055</v>
       </c>
       <c r="J115" t="n">
-        <v>4.0194</v>
+        <v>4.521</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.87</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3378</v>
+        <v>-0.1992</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.4316</v>
+        <v>-4.3824</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.12</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3435</v>
+        <v>0.2849</v>
       </c>
       <c r="J117" t="n">
-        <v>7.557</v>
+        <v>6.2678</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.03</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1816</v>
+        <v>0.1232</v>
       </c>
       <c r="J118" t="n">
-        <v>3.9952</v>
+        <v>2.7104</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.73</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4197</v>
+        <v>-0.2804</v>
       </c>
       <c r="J119" t="n">
-        <v>-9.2334</v>
+        <v>-6.1688</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.57</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.6438</v>
+        <v>-0.431</v>
       </c>
       <c r="J120" t="n">
-        <v>-14.1636</v>
+        <v>-9.481999999999999</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.49</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.505</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.379</v>
+        <v>-11.11</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>0.66</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.309</v>
+        <v>-0.2648</v>
       </c>
       <c r="J122" t="n">
-        <v>-5.253</v>
+        <v>-4.5016</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>0.5</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.5597</v>
+        <v>-0.4367</v>
       </c>
       <c r="J123" t="n">
-        <v>-9.514900000000001</v>
+        <v>-7.4239</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>0.42</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.7215</v>
+        <v>-0.5094</v>
       </c>
       <c r="J124" t="n">
-        <v>-12.2655</v>
+        <v>-8.659800000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>0.36</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.8168</v>
+        <v>-0.5679</v>
       </c>
       <c r="J125" t="n">
-        <v>-13.8856</v>
+        <v>-9.654299999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.34</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.5879</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.3871</v>
+        <v>-9.994300000000001</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>2.06</v>
       </c>
       <c r="I127" t="n">
-        <v>1.9804</v>
+        <v>1.693</v>
       </c>
       <c r="J127" t="n">
-        <v>33.6668</v>
+        <v>28.781</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.74</v>
       </c>
       <c r="I128" t="n">
-        <v>1.4637</v>
+        <v>1.3476</v>
       </c>
       <c r="J128" t="n">
-        <v>24.8829</v>
+        <v>22.9092</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>1.68</v>
       </c>
       <c r="I129" t="n">
-        <v>1.3319</v>
+        <v>1.2829</v>
       </c>
       <c r="J129" t="n">
-        <v>22.6423</v>
+        <v>21.8093</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>1.48</v>
       </c>
       <c r="I130" t="n">
-        <v>0.9274</v>
+        <v>1.0528</v>
       </c>
       <c r="J130" t="n">
-        <v>15.7658</v>
+        <v>17.8976</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>1.45</v>
       </c>
       <c r="I131" t="n">
-        <v>0.8682</v>
+        <v>1.0113</v>
       </c>
       <c r="J131" t="n">
-        <v>14.7594</v>
+        <v>17.1921</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.18</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3935</v>
+        <v>0.4419</v>
       </c>
       <c r="J132" t="n">
-        <v>10.231</v>
+        <v>11.4894</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>0.86</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2544</v>
+        <v>-0.1652</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.6144</v>
+        <v>-4.2952</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>0.83</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3054</v>
+        <v>-0.1958</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.9404</v>
+        <v>-5.0908</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3374</v>
+        <v>-0.2159</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.772399999999999</v>
+        <v>-5.6134</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.78</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3834</v>
+        <v>-0.2457</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.968400000000001</v>
+        <v>-6.3882</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.51</v>
       </c>
       <c r="I137" t="n">
-        <v>1.2551</v>
+        <v>1.1609</v>
       </c>
       <c r="J137" t="n">
-        <v>32.6326</v>
+        <v>30.1834</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.31</v>
       </c>
       <c r="I138" t="n">
-        <v>0.83</v>
+        <v>0.8243</v>
       </c>
       <c r="J138" t="n">
-        <v>21.58</v>
+        <v>21.4318</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1.18</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4964</v>
+        <v>0.5159</v>
       </c>
       <c r="J139" t="n">
-        <v>12.9064</v>
+        <v>13.4134</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>1.12</v>
       </c>
       <c r="I140" t="n">
-        <v>0.3085</v>
+        <v>0.3636</v>
       </c>
       <c r="J140" t="n">
-        <v>8.021000000000001</v>
+        <v>9.4536</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.75</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.8393</v>
+        <v>-0.7957</v>
       </c>
       <c r="J141" t="n">
-        <v>-21.8218</v>
+        <v>-20.6882</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.11</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3091</v>
+        <v>0.2506</v>
       </c>
       <c r="J142" t="n">
-        <v>7.7275</v>
+        <v>6.265</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.88</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1723</v>
+        <v>-0.1387</v>
       </c>
       <c r="J143" t="n">
-        <v>-4.3075</v>
+        <v>-3.4675</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.83</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.271</v>
+        <v>-0.1896</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.775</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.77</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3765</v>
+        <v>-0.2478</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.4125</v>
+        <v>-6.195</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.57</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6538</v>
+        <v>-0.4371</v>
       </c>
       <c r="J146" t="n">
-        <v>-16.345</v>
+        <v>-10.9275</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.57</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7821</v>
+        <v>0.7</v>
       </c>
       <c r="J147" t="n">
-        <v>19.5525</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5215</v>
+        <v>0.4568</v>
       </c>
       <c r="J148" t="n">
-        <v>13.0375</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.21</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3236</v>
+        <v>0.2936</v>
       </c>
       <c r="J149" t="n">
-        <v>8.09</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.03</v>
       </c>
       <c r="I150" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0427</v>
       </c>
       <c r="J150" t="n">
-        <v>0.225</v>
+        <v>1.0675</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.83</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3776</v>
+        <v>-0.2294</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.44</v>
+        <v>-5.735</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.8</v>
       </c>
       <c r="I152" t="n">
-        <v>1.6711</v>
+        <v>1.448</v>
       </c>
       <c r="J152" t="n">
-        <v>36.7642</v>
+        <v>31.856</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.76</v>
       </c>
       <c r="I153" t="n">
-        <v>1.5999</v>
+        <v>1.4021</v>
       </c>
       <c r="J153" t="n">
-        <v>35.1978</v>
+        <v>30.8462</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>1.31</v>
       </c>
       <c r="I154" t="n">
-        <v>0.6511</v>
+        <v>0.7683</v>
       </c>
       <c r="J154" t="n">
-        <v>14.3242</v>
+        <v>16.9026</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>1.25</v>
       </c>
       <c r="I155" t="n">
-        <v>0.5159</v>
+        <v>0.6299</v>
       </c>
       <c r="J155" t="n">
-        <v>11.3498</v>
+        <v>13.8578</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>1.14</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2537</v>
+        <v>0.3554</v>
       </c>
       <c r="J156" t="n">
-        <v>5.5814</v>
+        <v>7.8188</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>0.77</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.2745</v>
+        <v>-0.2259</v>
       </c>
       <c r="J157" t="n">
-        <v>-6.039</v>
+        <v>-4.9698</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>0.73</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.3386</v>
+        <v>-0.2661</v>
       </c>
       <c r="J158" t="n">
-        <v>-7.4492</v>
+        <v>-5.8542</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>0.67</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.4516</v>
+        <v>-0.3213</v>
       </c>
       <c r="J159" t="n">
-        <v>-9.9352</v>
+        <v>-7.0686</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>0.64</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.3483</v>
       </c>
       <c r="J160" t="n">
-        <v>-11.099</v>
+        <v>-7.6626</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.57</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6096</v>
+        <v>-0.4132</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.4112</v>
+        <v>-9.090400000000001</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.42</v>
       </c>
       <c r="I162" t="n">
-        <v>1.0222</v>
+        <v>1.0208</v>
       </c>
       <c r="J162" t="n">
-        <v>25.555</v>
+        <v>25.52</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.41</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0007</v>
+        <v>1.005</v>
       </c>
       <c r="J163" t="n">
-        <v>25.0175</v>
+        <v>25.125</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.34</v>
       </c>
       <c r="I164" t="n">
-        <v>0.8442</v>
+        <v>0.866</v>
       </c>
       <c r="J164" t="n">
-        <v>21.105</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.27</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.7109</v>
       </c>
       <c r="J165" t="n">
-        <v>16.545</v>
+        <v>17.7725</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>0.91</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4679</v>
+        <v>-0.3911</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.6975</v>
+        <v>-9.7775</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.04</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1981</v>
+        <v>0.1824</v>
       </c>
       <c r="J167" t="n">
-        <v>4.9525</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>0.9</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1203</v>
+        <v>-0.1109</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.0075</v>
+        <v>-2.7725</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1727</v>
+        <v>-0.1444</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.3175</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.7</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.469</v>
+        <v>-0.3102</v>
       </c>
       <c r="J170" t="n">
-        <v>-11.725</v>
+        <v>-7.755</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.48</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-0.5155</v>
       </c>
       <c r="J171" t="n">
-        <v>-18.965</v>
+        <v>-12.8875</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.84</v>
       </c>
       <c r="I172" t="n">
-        <v>1.7355</v>
+        <v>1.4908</v>
       </c>
       <c r="J172" t="n">
-        <v>32.9745</v>
+        <v>28.3252</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.61</v>
       </c>
       <c r="I173" t="n">
-        <v>1.3139</v>
+        <v>1.2258</v>
       </c>
       <c r="J173" t="n">
-        <v>24.9641</v>
+        <v>23.2902</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>1.33</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8102</v>
       </c>
       <c r="J174" t="n">
-        <v>13.11</v>
+        <v>15.3938</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>1.29</v>
       </c>
       <c r="I175" t="n">
-        <v>0.6014</v>
+        <v>0.7201</v>
       </c>
       <c r="J175" t="n">
-        <v>11.4266</v>
+        <v>13.6819</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>1.26</v>
       </c>
       <c r="I176" t="n">
-        <v>0.5341</v>
+        <v>0.6506</v>
       </c>
       <c r="J176" t="n">
-        <v>10.1479</v>
+        <v>12.3614</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>0.8</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1993</v>
+        <v>-0.1796</v>
       </c>
       <c r="J177" t="n">
-        <v>-3.7867</v>
+        <v>-3.4124</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>0.75</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2774</v>
+        <v>-0.2336</v>
       </c>
       <c r="J178" t="n">
-        <v>-5.2706</v>
+        <v>-4.4384</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.73</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3085</v>
+        <v>-0.2544</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.8615</v>
+        <v>-4.8336</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.55</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.6163</v>
+        <v>-0.4227</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.7097</v>
+        <v>-8.0313</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.29</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.9571</v>
+        <v>-0.6691</v>
       </c>
       <c r="J181" t="n">
-        <v>-18.1849</v>
+        <v>-12.7129</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.33</v>
       </c>
       <c r="I182" t="n">
-        <v>0.545</v>
+        <v>0.4998</v>
       </c>
       <c r="J182" t="n">
-        <v>15.805</v>
+        <v>14.4942</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.14</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2779</v>
+        <v>0.241</v>
       </c>
       <c r="J183" t="n">
-        <v>8.059100000000001</v>
+        <v>6.989</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.11</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2283</v>
+        <v>0.1965</v>
       </c>
       <c r="J184" t="n">
-        <v>6.6207</v>
+        <v>5.6985</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>0.84</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3346</v>
+        <v>-0.2031</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.7034</v>
+        <v>-5.8899</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.79</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4069</v>
+        <v>-0.2538</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.8001</v>
+        <v>-7.3602</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3888</v>
+        <v>0.324</v>
       </c>
       <c r="J187" t="n">
-        <v>11.2752</v>
+        <v>9.396000000000001</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.19</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3452</v>
+        <v>0.2858</v>
       </c>
       <c r="J188" t="n">
-        <v>10.0108</v>
+        <v>8.2882</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>1.16</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2997</v>
+        <v>0.2467</v>
       </c>
       <c r="J189" t="n">
-        <v>8.6913</v>
+        <v>7.1543</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.96</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1386</v>
+        <v>-0.0701</v>
       </c>
       <c r="J190" t="n">
-        <v>-4.0194</v>
+        <v>-2.0329</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3838</v>
+        <v>-0.2366</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.1302</v>
+        <v>-6.8614</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.71</v>
       </c>
       <c r="I192" t="n">
-        <v>1.6045</v>
+        <v>1.3939</v>
       </c>
       <c r="J192" t="n">
-        <v>41.717</v>
+        <v>36.2414</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>1.29</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7458</v>
+        <v>0.7617</v>
       </c>
       <c r="J193" t="n">
-        <v>19.3908</v>
+        <v>19.8042</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>1.11</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2479</v>
+        <v>0.3221</v>
       </c>
       <c r="J194" t="n">
-        <v>6.4454</v>
+        <v>8.374599999999999</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>1.07</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1317</v>
+        <v>0.2062</v>
       </c>
       <c r="J195" t="n">
-        <v>3.4242</v>
+        <v>5.3612</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>1</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.136</v>
+        <v>-0.0575</v>
       </c>
       <c r="J196" t="n">
-        <v>-3.536</v>
+        <v>-1.495</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.14</v>
       </c>
       <c r="I197" t="n">
-        <v>0.348</v>
+        <v>0.3797</v>
       </c>
       <c r="J197" t="n">
-        <v>9.048</v>
+        <v>9.872199999999999</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.08</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2498</v>
+        <v>0.2521</v>
       </c>
       <c r="J198" t="n">
-        <v>6.4948</v>
+        <v>6.5546</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>0.93</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0912</v>
+        <v>-0.0851</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.3712</v>
+        <v>-2.2126</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.6707</v>
+        <v>-0.4492</v>
       </c>
       <c r="J200" t="n">
-        <v>-17.4382</v>
+        <v>-11.6792</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6707</v>
+        <v>-0.4492</v>
       </c>
       <c r="J201" t="n">
-        <v>-17.4382</v>
+        <v>-11.6792</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>0.93</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0032</v>
+        <v>-0.0381</v>
       </c>
       <c r="J202" t="n">
-        <v>-0.0672</v>
+        <v>-0.8001</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.91</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0391</v>
+        <v>-0.0639</v>
       </c>
       <c r="J203" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-1.3419</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.59</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.5756</v>
+        <v>-0.3925</v>
       </c>
       <c r="J204" t="n">
-        <v>-12.0876</v>
+        <v>-8.2425</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.49</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.7149</v>
+        <v>-0.4861</v>
       </c>
       <c r="J205" t="n">
-        <v>-15.0129</v>
+        <v>-10.2081</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.4</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.8303</v>
+        <v>-0.5708</v>
       </c>
       <c r="J206" t="n">
-        <v>-17.4363</v>
+        <v>-11.9868</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.72</v>
       </c>
       <c r="I207" t="n">
-        <v>1.524</v>
+        <v>1.3546</v>
       </c>
       <c r="J207" t="n">
-        <v>32.004</v>
+        <v>28.4466</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.53</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1553</v>
+        <v>1.1325</v>
       </c>
       <c r="J208" t="n">
-        <v>24.2613</v>
+        <v>23.7825</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>1.44</v>
       </c>
       <c r="I209" t="n">
-        <v>0.9388</v>
+        <v>1.0237</v>
       </c>
       <c r="J209" t="n">
-        <v>19.7148</v>
+        <v>21.4977</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>1.35</v>
       </c>
       <c r="I210" t="n">
-        <v>0.7365</v>
+        <v>0.8555</v>
       </c>
       <c r="J210" t="n">
-        <v>15.4665</v>
+        <v>17.9655</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>1.26</v>
       </c>
       <c r="I211" t="n">
-        <v>0.536</v>
+        <v>0.6518</v>
       </c>
       <c r="J211" t="n">
-        <v>11.256</v>
+        <v>13.6878</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>0.73</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.2566</v>
+        <v>-0.2246</v>
       </c>
       <c r="J212" t="n">
-        <v>-4.3622</v>
+        <v>-3.8182</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>0.65</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.3788</v>
+        <v>-0.3109</v>
       </c>
       <c r="J213" t="n">
-        <v>-6.4396</v>
+        <v>-5.2853</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.47</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.6921</v>
+        <v>-0.4802</v>
       </c>
       <c r="J214" t="n">
-        <v>-11.7657</v>
+        <v>-8.163399999999999</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.43</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.7513</v>
+        <v>-0.5183</v>
       </c>
       <c r="J215" t="n">
-        <v>-12.7721</v>
+        <v>-8.8111</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.4</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7937</v>
+        <v>-0.5473</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.4929</v>
+        <v>-9.3041</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>2.27</v>
       </c>
       <c r="I217" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J217" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.84</v>
       </c>
       <c r="I218" t="n">
-        <v>1.6227</v>
+        <v>1.4493</v>
       </c>
       <c r="J218" t="n">
-        <v>27.5859</v>
+        <v>24.6381</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>1.59</v>
       </c>
       <c r="I219" t="n">
-        <v>1.1201</v>
+        <v>1.1768</v>
       </c>
       <c r="J219" t="n">
-        <v>19.0417</v>
+        <v>20.0056</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>1.54</v>
       </c>
       <c r="I220" t="n">
-        <v>1.0246</v>
+        <v>1.1185</v>
       </c>
       <c r="J220" t="n">
-        <v>17.4182</v>
+        <v>19.0145</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>1.49</v>
       </c>
       <c r="I221" t="n">
-        <v>0.9286</v>
+        <v>1.0586</v>
       </c>
       <c r="J221" t="n">
-        <v>15.7862</v>
+        <v>17.9962</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.04</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1734</v>
+        <v>0.1565</v>
       </c>
       <c r="J222" t="n">
-        <v>4.6818</v>
+        <v>4.2255</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>0.95</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.054</v>
+        <v>-0.0609</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.458</v>
+        <v>-1.6443</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>0.93</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0931</v>
+        <v>-0.0857</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.5137</v>
+        <v>-2.3139</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.73</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4458</v>
+        <v>-0.2899</v>
       </c>
       <c r="J225" t="n">
-        <v>-12.0366</v>
+        <v>-7.8273</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.64</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5693</v>
+        <v>-0.3753</v>
       </c>
       <c r="J226" t="n">
-        <v>-15.3711</v>
+        <v>-10.1331</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.6</v>
       </c>
       <c r="I227" t="n">
-        <v>1.4038</v>
+        <v>1.2606</v>
       </c>
       <c r="J227" t="n">
-        <v>37.9026</v>
+        <v>34.0362</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>1.47</v>
       </c>
       <c r="I228" t="n">
-        <v>1.1477</v>
+        <v>1.0966</v>
       </c>
       <c r="J228" t="n">
-        <v>30.9879</v>
+        <v>29.6082</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>1.14</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3346</v>
+        <v>0.405</v>
       </c>
       <c r="J229" t="n">
-        <v>9.0342</v>
+        <v>10.935</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.97</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2703</v>
+        <v>-0.189</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.2981</v>
+        <v>-5.103</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.96</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3048</v>
+        <v>-0.224</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.2296</v>
+        <v>-6.048</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>1.05</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2817</v>
+        <v>0.2968</v>
       </c>
       <c r="J232" t="n">
-        <v>5.634</v>
+        <v>5.936</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>0.88</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.0887</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.774</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>0.53</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.6596</v>
+        <v>-0.4479</v>
       </c>
       <c r="J234" t="n">
-        <v>-13.192</v>
+        <v>-8.958</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>0.47</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.7401</v>
+        <v>-0.5042</v>
       </c>
       <c r="J235" t="n">
-        <v>-14.802</v>
+        <v>-10.084</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.37</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.8666</v>
+        <v>-0.5984</v>
       </c>
       <c r="J236" t="n">
-        <v>-17.332</v>
+        <v>-11.968</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.72</v>
       </c>
       <c r="I237" t="n">
-        <v>1.524</v>
+        <v>1.3546</v>
       </c>
       <c r="J237" t="n">
-        <v>30.48</v>
+        <v>27.092</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.71</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5057</v>
+        <v>1.343</v>
       </c>
       <c r="J238" t="n">
-        <v>30.114</v>
+        <v>26.86</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>1.53</v>
       </c>
       <c r="I239" t="n">
-        <v>1.1553</v>
+        <v>1.1325</v>
       </c>
       <c r="J239" t="n">
-        <v>23.106</v>
+        <v>22.65</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>1.35</v>
       </c>
       <c r="I240" t="n">
-        <v>0.7365</v>
+        <v>0.8555</v>
       </c>
       <c r="J240" t="n">
-        <v>14.73</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.99</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2521</v>
+        <v>-0.162</v>
       </c>
       <c r="J241" t="n">
-        <v>-5.042</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.31</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4834</v>
+        <v>0.4178</v>
       </c>
       <c r="J242" t="n">
-        <v>13.0518</v>
+        <v>11.2806</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4296</v>
+        <v>0.3706</v>
       </c>
       <c r="J243" t="n">
-        <v>11.5992</v>
+        <v>10.0062</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>1.21</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3434</v>
+        <v>0.2981</v>
       </c>
       <c r="J244" t="n">
-        <v>9.271800000000001</v>
+        <v>8.0487</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>1.08</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1153</v>
+        <v>0.1286</v>
       </c>
       <c r="J245" t="n">
-        <v>3.1131</v>
+        <v>3.4722</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.9</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2654</v>
+        <v>-0.1507</v>
       </c>
       <c r="J246" t="n">
-        <v>-7.1658</v>
+        <v>-4.0689</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>1.07</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2022</v>
+        <v>0.1547</v>
       </c>
       <c r="J247" t="n">
-        <v>5.4594</v>
+        <v>4.1769</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1</v>
       </c>
       <c r="I248" t="n">
-        <v>0.04</v>
+        <v>0.0098</v>
       </c>
       <c r="J248" t="n">
-        <v>1.08</v>
+        <v>0.2646</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.88</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2368</v>
+        <v>-0.1483</v>
       </c>
       <c r="J249" t="n">
-        <v>-6.3936</v>
+        <v>-4.0041</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.86</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2709</v>
+        <v>-0.1694</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.3143</v>
+        <v>-4.5738</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.84</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3035</v>
+        <v>-0.1901</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.1945</v>
+        <v>-5.1327</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.16</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3541</v>
+        <v>0.3921</v>
       </c>
       <c r="J252" t="n">
-        <v>9.560700000000001</v>
+        <v>10.5867</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.11</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2757</v>
+        <v>0.2916</v>
       </c>
       <c r="J253" t="n">
-        <v>7.4439</v>
+        <v>7.8732</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>0.96</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0612</v>
+        <v>-0.0563</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.6524</v>
+        <v>-1.5201</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>0.84</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2992</v>
+        <v>-0.1887</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.0784</v>
+        <v>-5.0949</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.52</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.73</v>
+        <v>-0.4933</v>
       </c>
       <c r="J256" t="n">
-        <v>-19.71</v>
+        <v>-13.3191</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.27</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7649</v>
+        <v>0.7466</v>
       </c>
       <c r="J257" t="n">
-        <v>20.6523</v>
+        <v>20.1582</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>1.27</v>
       </c>
       <c r="I258" t="n">
-        <v>0.7649</v>
+        <v>0.7466</v>
       </c>
       <c r="J258" t="n">
-        <v>20.6523</v>
+        <v>20.1582</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>1.19</v>
       </c>
       <c r="I259" t="n">
-        <v>0.5649</v>
+        <v>0.5511</v>
       </c>
       <c r="J259" t="n">
-        <v>15.2523</v>
+        <v>14.8797</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>1.15</v>
       </c>
       <c r="I260" t="n">
-        <v>0.4532</v>
+        <v>0.45</v>
       </c>
       <c r="J260" t="n">
-        <v>12.2364</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.8498</v>
+        <v>-0.8084</v>
       </c>
       <c r="J261" t="n">
-        <v>-22.9446</v>
+        <v>-21.8268</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.19</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3558</v>
+        <v>0.4091</v>
       </c>
       <c r="J262" t="n">
-        <v>14.5878</v>
+        <v>16.7731</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.06</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1374</v>
+        <v>0.1548</v>
       </c>
       <c r="J263" t="n">
-        <v>5.6334</v>
+        <v>6.3468</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.01</v>
       </c>
       <c r="I264" t="n">
-        <v>0.012</v>
+        <v>0.0331</v>
       </c>
       <c r="J264" t="n">
-        <v>0.492</v>
+        <v>1.3571</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.97</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1078</v>
+        <v>-0.0537</v>
       </c>
       <c r="J265" t="n">
-        <v>-4.4198</v>
+        <v>-2.2017</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.96</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.1291</v>
+        <v>-0.067</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.2931</v>
+        <v>-2.747</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.48</v>
       </c>
       <c r="I267" t="n">
-        <v>1.246</v>
+        <v>1.1508</v>
       </c>
       <c r="J267" t="n">
-        <v>51.086</v>
+        <v>47.1828</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.21</v>
       </c>
       <c r="I268" t="n">
-        <v>0.6468</v>
+        <v>0.6162</v>
       </c>
       <c r="J268" t="n">
-        <v>26.5188</v>
+        <v>25.2642</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>1.02</v>
       </c>
       <c r="I269" t="n">
-        <v>0.0382</v>
+        <v>0.0785</v>
       </c>
       <c r="J269" t="n">
-        <v>1.5662</v>
+        <v>3.2185</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.86</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5427</v>
+        <v>-0.4833</v>
       </c>
       <c r="J270" t="n">
-        <v>-22.2507</v>
+        <v>-19.8153</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6705</v>
+        <v>-0.6171</v>
       </c>
       <c r="J271" t="n">
-        <v>-27.4905</v>
+        <v>-25.3011</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>1.36</v>
       </c>
       <c r="I272" t="n">
-        <v>0.549</v>
+        <v>0.6694</v>
       </c>
       <c r="J272" t="n">
-        <v>16.47</v>
+        <v>20.082</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>1.22</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3599</v>
+        <v>0.4366</v>
       </c>
       <c r="J273" t="n">
-        <v>10.797</v>
+        <v>13.098</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>1.14</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2224</v>
+        <v>0.2972</v>
       </c>
       <c r="J274" t="n">
-        <v>6.672</v>
+        <v>8.916</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>1.12</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1867</v>
+        <v>0.2603</v>
       </c>
       <c r="J275" t="n">
-        <v>5.601</v>
+        <v>7.809</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.91</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2484</v>
+        <v>-0.1391</v>
       </c>
       <c r="J276" t="n">
-        <v>-7.452</v>
+        <v>-4.173</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.15</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6133</v>
+        <v>0.5482</v>
       </c>
       <c r="J277" t="n">
-        <v>18.399</v>
+        <v>16.446</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>0.96</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0769</v>
+        <v>-0.1339</v>
       </c>
       <c r="J278" t="n">
-        <v>-2.307</v>
+        <v>-4.017</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>0.89</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3193</v>
+        <v>-0.3472</v>
       </c>
       <c r="J279" t="n">
-        <v>-9.579000000000001</v>
+        <v>-10.416</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.83</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.524</v>
+        <v>-0.5057</v>
       </c>
       <c r="J280" t="n">
-        <v>-15.72</v>
+        <v>-15.171</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.58</v>
       </c>
       <c r="I281" t="n">
-        <v>-1.1329</v>
+        <v>-1.1285</v>
       </c>
       <c r="J281" t="n">
-        <v>-33.987</v>
+        <v>-33.855</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>0.89</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.0442</v>
+        <v>-0.0675</v>
       </c>
       <c r="J282" t="n">
-        <v>-0.884</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>0.76</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.2529</v>
+        <v>-0.2182</v>
       </c>
       <c r="J283" t="n">
-        <v>-5.058</v>
+        <v>-4.364</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.68</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3774</v>
+        <v>-0.3008</v>
       </c>
       <c r="J284" t="n">
-        <v>-7.548</v>
+        <v>-6.016</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.42</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.7907</v>
+        <v>-0.5423</v>
       </c>
       <c r="J285" t="n">
-        <v>-15.814</v>
+        <v>-10.846</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.29</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.9544</v>
+        <v>-0.6669</v>
       </c>
       <c r="J286" t="n">
-        <v>-19.088</v>
+        <v>-13.338</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.99</v>
       </c>
       <c r="I287" t="n">
-        <v>1.9356</v>
+        <v>1.6398</v>
       </c>
       <c r="J287" t="n">
-        <v>38.712</v>
+        <v>32.796</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.59</v>
       </c>
       <c r="I288" t="n">
-        <v>1.2262</v>
+        <v>1.1922</v>
       </c>
       <c r="J288" t="n">
-        <v>24.524</v>
+        <v>23.844</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.49</v>
       </c>
       <c r="I289" t="n">
-        <v>0.994</v>
+        <v>1.0778</v>
       </c>
       <c r="J289" t="n">
-        <v>19.88</v>
+        <v>21.556</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>1.38</v>
       </c>
       <c r="I290" t="n">
-        <v>0.7641</v>
+        <v>0.9019</v>
       </c>
       <c r="J290" t="n">
-        <v>15.282</v>
+        <v>18.038</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>1.34</v>
       </c>
       <c r="I291" t="n">
-        <v>0.6798</v>
+        <v>0.8146</v>
       </c>
       <c r="J291" t="n">
-        <v>13.596</v>
+        <v>16.292</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.1</v>
       </c>
       <c r="I292" t="n">
-        <v>0.373</v>
+        <v>0.3242</v>
       </c>
       <c r="J292" t="n">
-        <v>7.46</v>
+        <v>6.484</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>0.73</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.3269</v>
+        <v>-0.262</v>
       </c>
       <c r="J293" t="n">
-        <v>-6.538</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.61</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.541</v>
+        <v>-0.3727</v>
       </c>
       <c r="J294" t="n">
-        <v>-10.82</v>
+        <v>-7.454</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.54</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.6442</v>
+        <v>-0.4378</v>
       </c>
       <c r="J295" t="n">
-        <v>-12.884</v>
+        <v>-8.756</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.3</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.9503</v>
+        <v>-0.6639</v>
       </c>
       <c r="J296" t="n">
-        <v>-19.006</v>
+        <v>-13.278</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>2.27</v>
       </c>
       <c r="I297" t="n">
-        <v>1.4064</v>
+        <v>1.198</v>
       </c>
       <c r="J297" t="n">
-        <v>28.128</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.48</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6078</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="J298" t="n">
-        <v>12.156</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.31</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3764</v>
+        <v>0.3874</v>
       </c>
       <c r="J299" t="n">
-        <v>7.528</v>
+        <v>7.748</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>1.16</v>
       </c>
       <c r="I300" t="n">
-        <v>0.1761</v>
+        <v>0.2062</v>
       </c>
       <c r="J300" t="n">
-        <v>3.522</v>
+        <v>4.124</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.99</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.1427</v>
+        <v>-0.0609</v>
       </c>
       <c r="J301" t="n">
-        <v>-2.854</v>
+        <v>-1.218</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>1.87</v>
       </c>
       <c r="I302" t="n">
-        <v>1.766</v>
+        <v>1.5142</v>
       </c>
       <c r="J302" t="n">
-        <v>33.554</v>
+        <v>28.7698</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>1.6</v>
       </c>
       <c r="I303" t="n">
-        <v>1.268</v>
+        <v>1.2073</v>
       </c>
       <c r="J303" t="n">
-        <v>24.092</v>
+        <v>22.9387</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>1.41</v>
       </c>
       <c r="I304" t="n">
-        <v>0.8415</v>
+        <v>0.9678</v>
       </c>
       <c r="J304" t="n">
-        <v>15.9885</v>
+        <v>18.3882</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>1.39</v>
       </c>
       <c r="I305" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.9295</v>
       </c>
       <c r="J305" t="n">
-        <v>15.1791</v>
+        <v>17.6605</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>1.33</v>
       </c>
       <c r="I306" t="n">
-        <v>0.6706</v>
+        <v>0.7997</v>
       </c>
       <c r="J306" t="n">
-        <v>12.7414</v>
+        <v>15.1943</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>1.11</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4094</v>
+        <v>0.4831</v>
       </c>
       <c r="J307" t="n">
-        <v>7.7786</v>
+        <v>9.178900000000001</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>0.67</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.401</v>
+        <v>-0.3132</v>
       </c>
       <c r="J308" t="n">
-        <v>-7.619</v>
+        <v>-5.9508</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>0.63</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4701</v>
+        <v>-0.3503</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.931900000000001</v>
+        <v>-6.6557</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>0.35</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.8831</v>
+        <v>-0.6112</v>
       </c>
       <c r="J310" t="n">
-        <v>-16.7789</v>
+        <v>-11.6128</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.34</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.8955</v>
+        <v>-0.6208</v>
       </c>
       <c r="J311" t="n">
-        <v>-17.0145</v>
+        <v>-11.7952</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.77</v>
       </c>
       <c r="I312" t="n">
-        <v>1.5759</v>
+        <v>1.3963</v>
       </c>
       <c r="J312" t="n">
-        <v>29.9421</v>
+        <v>26.5297</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.74</v>
       </c>
       <c r="I313" t="n">
-        <v>1.5212</v>
+        <v>1.3625</v>
       </c>
       <c r="J313" t="n">
-        <v>28.9028</v>
+        <v>25.8875</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>1.62</v>
       </c>
       <c r="I314" t="n">
-        <v>1.291</v>
+        <v>1.2266</v>
       </c>
       <c r="J314" t="n">
-        <v>24.529</v>
+        <v>23.3054</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>1.42</v>
       </c>
       <c r="I315" t="n">
-        <v>0.8492</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="J315" t="n">
-        <v>16.1348</v>
+        <v>18.6257</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>1.22</v>
       </c>
       <c r="I316" t="n">
-        <v>0.4184</v>
+        <v>0.5376</v>
       </c>
       <c r="J316" t="n">
-        <v>7.9496</v>
+        <v>10.2144</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>0.82</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.1397</v>
+        <v>-0.1378</v>
       </c>
       <c r="J317" t="n">
-        <v>-2.6543</v>
+        <v>-2.6182</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>0.73</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.2796</v>
+        <v>-0.2392</v>
       </c>
       <c r="J318" t="n">
-        <v>-5.3124</v>
+        <v>-4.5448</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>0.6</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.485</v>
+        <v>-0.3701</v>
       </c>
       <c r="J319" t="n">
-        <v>-9.215</v>
+        <v>-7.0319</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>0.42</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.7799</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="J320" t="n">
-        <v>-14.8181</v>
+        <v>-10.1802</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.3</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.9357</v>
+        <v>-0.652</v>
       </c>
       <c r="J321" t="n">
-        <v>-17.7783</v>
+        <v>-12.388</v>
       </c>
     </row>
     <row r="322">
@@ -15275,10 +15275,10 @@
         <v>1.44</v>
       </c>
       <c r="I322" t="n">
-        <v>1.0958</v>
+        <v>1.0622</v>
       </c>
       <c r="J322" t="n">
-        <v>26.2992</v>
+        <v>25.4928</v>
       </c>
     </row>
     <row r="323">
@@ -15315,10 +15315,10 @@
         <v>1.37</v>
       </c>
       <c r="I323" t="n">
-        <v>0.9464</v>
+        <v>0.9474</v>
       </c>
       <c r="J323" t="n">
-        <v>22.7136</v>
+        <v>22.7376</v>
       </c>
     </row>
     <row r="324">
@@ -15355,10 +15355,10 @@
         <v>1.12</v>
       </c>
       <c r="I324" t="n">
-        <v>0.2894</v>
+        <v>0.356</v>
       </c>
       <c r="J324" t="n">
-        <v>6.9456</v>
+        <v>8.544</v>
       </c>
     </row>
     <row r="325">
@@ -15395,10 +15395,10 @@
         <v>1.08</v>
       </c>
       <c r="I325" t="n">
-        <v>0.1736</v>
+        <v>0.2429</v>
       </c>
       <c r="J325" t="n">
-        <v>4.1664</v>
+        <v>5.8296</v>
       </c>
     </row>
     <row r="326">
@@ -15435,10 +15435,10 @@
         <v>1.03</v>
       </c>
       <c r="I326" t="n">
-        <v>0.0117</v>
+        <v>0.0825</v>
       </c>
       <c r="J326" t="n">
-        <v>0.2808</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="327">
@@ -15475,10 +15475,10 @@
         <v>1.26</v>
       </c>
       <c r="I327" t="n">
-        <v>0.5171</v>
+        <v>0.6089</v>
       </c>
       <c r="J327" t="n">
-        <v>12.4104</v>
+        <v>14.6136</v>
       </c>
     </row>
     <row r="328">
@@ -15515,10 +15515,10 @@
         <v>1.03</v>
       </c>
       <c r="I328" t="n">
-        <v>0.1509</v>
+        <v>0.1294</v>
       </c>
       <c r="J328" t="n">
-        <v>3.6216</v>
+        <v>3.1056</v>
       </c>
     </row>
     <row r="329">
@@ -15555,10 +15555,10 @@
         <v>0.72</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.4613</v>
+        <v>-0.3</v>
       </c>
       <c r="J329" t="n">
-        <v>-11.0712</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="330">
@@ -15595,10 +15595,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.5032</v>
+        <v>-0.3287</v>
       </c>
       <c r="J330" t="n">
-        <v>-12.0768</v>
+        <v>-7.8888</v>
       </c>
     </row>
     <row r="331">
@@ -15635,10 +15635,10 @@
         <v>0.61</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6092</v>
+        <v>-0.4039</v>
       </c>
       <c r="J331" t="n">
-        <v>-14.6208</v>
+        <v>-9.6936</v>
       </c>
     </row>
     <row r="332">
@@ -15675,10 +15675,10 @@
         <v>1.99</v>
       </c>
       <c r="I332" t="n">
-        <v>1.9673</v>
+        <v>1.6671</v>
       </c>
       <c r="J332" t="n">
-        <v>41.3133</v>
+        <v>35.0091</v>
       </c>
     </row>
     <row r="333">
@@ -15715,10 +15715,10 @@
         <v>1.64</v>
       </c>
       <c r="I333" t="n">
-        <v>1.3852</v>
+        <v>1.2655</v>
       </c>
       <c r="J333" t="n">
-        <v>29.0892</v>
+        <v>26.5755</v>
       </c>
     </row>
     <row r="334">
@@ -15755,10 +15755,10 @@
         <v>1.44</v>
       </c>
       <c r="I334" t="n">
-        <v>0.9657</v>
+        <v>1.0254</v>
       </c>
       <c r="J334" t="n">
-        <v>20.2797</v>
+        <v>21.5334</v>
       </c>
     </row>
     <row r="335">
@@ -15795,10 +15795,10 @@
         <v>1.28</v>
       </c>
       <c r="I335" t="n">
-        <v>0.5897</v>
+        <v>0.7032</v>
       </c>
       <c r="J335" t="n">
-        <v>12.3837</v>
+        <v>14.7672</v>
       </c>
     </row>
     <row r="336">
@@ -15835,10 +15835,10 @@
         <v>0.83</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.7062</v>
+        <v>-0.6464</v>
       </c>
       <c r="J336" t="n">
-        <v>-14.8302</v>
+        <v>-13.5744</v>
       </c>
     </row>
     <row r="337">
@@ -15875,10 +15875,10 @@
         <v>1.05</v>
       </c>
       <c r="I337" t="n">
-        <v>0.2726</v>
+        <v>0.2823</v>
       </c>
       <c r="J337" t="n">
-        <v>5.7246</v>
+        <v>5.9283</v>
       </c>
     </row>
     <row r="338">
@@ -15915,10 +15915,10 @@
         <v>0.95</v>
       </c>
       <c r="I338" t="n">
-        <v>0.0277</v>
+        <v>-0.016</v>
       </c>
       <c r="J338" t="n">
-        <v>0.5817</v>
+        <v>-0.336</v>
       </c>
     </row>
     <row r="339">
@@ -15955,10 +15955,10 @@
         <v>0.49</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.719</v>
+        <v>-0.4885</v>
       </c>
       <c r="J339" t="n">
-        <v>-15.099</v>
+        <v>-10.2585</v>
       </c>
     </row>
     <row r="340">
@@ -15995,10 +15995,10 @@
         <v>0.47</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.745</v>
+        <v>-0.5073</v>
       </c>
       <c r="J340" t="n">
-        <v>-15.645</v>
+        <v>-10.6533</v>
       </c>
     </row>
     <row r="341">
@@ -16035,10 +16035,10 @@
         <v>0.43</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.5448</v>
       </c>
       <c r="J341" t="n">
-        <v>-16.7139</v>
+        <v>-11.4408</v>
       </c>
     </row>
     <row r="342">
@@ -16075,10 +16075,10 @@
         <v>1.63</v>
       </c>
       <c r="I342" t="n">
-        <v>1.5323</v>
+        <v>1.3439</v>
       </c>
       <c r="J342" t="n">
-        <v>42.9044</v>
+        <v>37.6292</v>
       </c>
     </row>
     <row r="343">
@@ -16115,10 +16115,10 @@
         <v>1.09</v>
       </c>
       <c r="I343" t="n">
-        <v>0.2951</v>
+        <v>0.2976</v>
       </c>
       <c r="J343" t="n">
-        <v>8.2628</v>
+        <v>8.332800000000001</v>
       </c>
     </row>
     <row r="344">
@@ -16155,10 +16155,10 @@
         <v>1.02</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0319</v>
+        <v>0.0761</v>
       </c>
       <c r="J344" t="n">
-        <v>0.8932</v>
+        <v>2.1308</v>
       </c>
     </row>
     <row r="345">
@@ -16195,10 +16195,10 @@
         <v>0.99</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1322</v>
+        <v>-0.074</v>
       </c>
       <c r="J345" t="n">
-        <v>-3.7016</v>
+        <v>-2.072</v>
       </c>
     </row>
     <row r="346">
@@ -16235,10 +16235,10 @@
         <v>0.7</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.9296</v>
+        <v>-0.8974</v>
       </c>
       <c r="J346" t="n">
-        <v>-26.0288</v>
+        <v>-25.1272</v>
       </c>
     </row>
     <row r="347">
@@ -16275,10 +16275,10 @@
         <v>1.14</v>
       </c>
       <c r="I347" t="n">
-        <v>0.2964</v>
+        <v>0.328</v>
       </c>
       <c r="J347" t="n">
-        <v>8.299200000000001</v>
+        <v>9.183999999999999</v>
       </c>
     </row>
     <row r="348">
@@ -16315,10 +16315,10 @@
         <v>1.05</v>
       </c>
       <c r="I348" t="n">
-        <v>0.1389</v>
+        <v>0.141</v>
       </c>
       <c r="J348" t="n">
-        <v>3.8892</v>
+        <v>3.948</v>
       </c>
     </row>
     <row r="349">
@@ -16355,10 +16355,10 @@
         <v>0.98</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.0634</v>
+        <v>-0.0354</v>
       </c>
       <c r="J349" t="n">
-        <v>-1.7752</v>
+        <v>-0.9912</v>
       </c>
     </row>
     <row r="350">
@@ -16395,10 +16395,10 @@
         <v>0.9</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2253</v>
+        <v>-0.1334</v>
       </c>
       <c r="J350" t="n">
-        <v>-6.3084</v>
+        <v>-3.7352</v>
       </c>
     </row>
     <row r="351">
@@ -16435,10 +16435,10 @@
         <v>0.89</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.2423</v>
+        <v>-0.1444</v>
       </c>
       <c r="J351" t="n">
-        <v>-6.7844</v>
+        <v>-4.0432</v>
       </c>
     </row>
     <row r="352">
@@ -16475,10 +16475,10 @@
         <v>2.03</v>
       </c>
       <c r="I352" t="n">
-        <v>1.9791</v>
+        <v>1.6845</v>
       </c>
       <c r="J352" t="n">
-        <v>33.6447</v>
+        <v>28.6365</v>
       </c>
     </row>
     <row r="353">
@@ -16515,10 +16515,10 @@
         <v>1.63</v>
       </c>
       <c r="I353" t="n">
-        <v>1.3111</v>
+        <v>1.2379</v>
       </c>
       <c r="J353" t="n">
-        <v>22.2887</v>
+        <v>21.0443</v>
       </c>
     </row>
     <row r="354">
@@ -16555,10 +16555,10 @@
         <v>1.53</v>
       </c>
       <c r="I354" t="n">
-        <v>1.0827</v>
+        <v>1.1249</v>
       </c>
       <c r="J354" t="n">
-        <v>18.4059</v>
+        <v>19.1233</v>
       </c>
     </row>
     <row r="355">
@@ -16595,10 +16595,10 @@
         <v>1.37</v>
       </c>
       <c r="I355" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.8812</v>
       </c>
       <c r="J355" t="n">
-        <v>12.6565</v>
+        <v>14.9804</v>
       </c>
     </row>
     <row r="356">
@@ -16635,10 +16635,10 @@
         <v>1.21</v>
       </c>
       <c r="I356" t="n">
-        <v>0.3955</v>
+        <v>0.5132</v>
       </c>
       <c r="J356" t="n">
-        <v>6.7235</v>
+        <v>8.724399999999999</v>
       </c>
     </row>
     <row r="357">
@@ -16675,10 +16675,10 @@
         <v>0.83</v>
       </c>
       <c r="I357" t="n">
-        <v>-0.143</v>
+        <v>-0.1399</v>
       </c>
       <c r="J357" t="n">
-        <v>-2.431</v>
+        <v>-2.3783</v>
       </c>
     </row>
     <row r="358">
@@ -16715,10 +16715,10 @@
         <v>0.74</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.2839</v>
+        <v>-0.2395</v>
       </c>
       <c r="J358" t="n">
-        <v>-4.8263</v>
+        <v>-4.0715</v>
       </c>
     </row>
     <row r="359">
@@ -16755,10 +16755,10 @@
         <v>0.61</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.4988</v>
+        <v>-0.3662</v>
       </c>
       <c r="J359" t="n">
-        <v>-8.4796</v>
+        <v>-6.2254</v>
       </c>
     </row>
     <row r="360">
@@ -16795,10 +16795,10 @@
         <v>0.55</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.6082</v>
+        <v>-0.4198</v>
       </c>
       <c r="J360" t="n">
-        <v>-10.3394</v>
+        <v>-7.1366</v>
       </c>
     </row>
     <row r="361">
@@ -16835,10 +16835,10 @@
         <v>0.31</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.93</v>
+        <v>-0.6476</v>
       </c>
       <c r="J361" t="n">
-        <v>-15.81</v>
+        <v>-11.0092</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4979/event_4979_evp_summary.xlsx
+++ b/database/event/4979/event_4979_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.6462</v>
+        <v>8.938599999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9948</v>
+        <v>2.0623</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2653</v>
+        <v>3.4448</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6462</v>
+        <v>8.938599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1944</v>
+        <v>4.3579</v>
       </c>
       <c r="H2" t="n">
-        <v>11.9778</v>
+        <v>11.4298</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2279</v>
+        <v>6.172</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1944</v>
+        <v>4.3579</v>
       </c>
       <c r="K2" t="n">
         <v>103</v>
@@ -529,7 +529,7 @@
         <v>144</v>
       </c>
       <c r="M2" t="n">
-        <v>10.4223</v>
+        <v>10.5299</v>
       </c>
       <c r="N2" t="n">
         <v>247</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.1905</v>
+        <v>6.3889</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4283</v>
+        <v>1.474</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1567</v>
+        <v>2.2842</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1905</v>
+        <v>6.3889</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9659</v>
+        <v>2.9139</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2246</v>
+        <v>3.475</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9635</v>
+        <v>4.7197</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5808</v>
+        <v>2.5486</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2246</v>
+        <v>3.475</v>
       </c>
       <c r="K3" t="n">
         <v>103</v>
@@ -575,7 +575,7 @@
         <v>144</v>
       </c>
       <c r="M3" t="n">
-        <v>5.805400000000001</v>
+        <v>6.0236</v>
       </c>
       <c r="N3" t="n">
         <v>247</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6707</v>
+        <v>4.6489</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0776</v>
+        <v>1.0726</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4706</v>
+        <v>1.4921</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6707</v>
+        <v>4.6489</v>
       </c>
       <c r="F4" t="n">
-        <v>2.85</v>
+        <v>2.7665</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8207</v>
+        <v>1.8824</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5552</v>
+        <v>4.2336</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3685</v>
+        <v>2.2861</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8207</v>
+        <v>1.8824</v>
       </c>
       <c r="K4" t="n">
         <v>142</v>
@@ -621,7 +621,7 @@
         <v>146</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1892</v>
+        <v>4.1685</v>
       </c>
       <c r="N4" t="n">
         <v>288</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5652</v>
+        <v>4.5793</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0533</v>
+        <v>1.0565</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4229</v>
+        <v>1.4604</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5652</v>
+        <v>4.5793</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7203</v>
+        <v>3.6355</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8449</v>
+        <v>0.9438</v>
       </c>
       <c r="H5" t="n">
-        <v>7.6218</v>
+        <v>7.1007</v>
       </c>
       <c r="I5" t="n">
-        <v>3.963</v>
+        <v>3.8343</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8449</v>
+        <v>0.9438</v>
       </c>
       <c r="K5" t="n">
         <v>142</v>
@@ -667,7 +667,7 @@
         <v>146</v>
       </c>
       <c r="M5" t="n">
-        <v>4.8079</v>
+        <v>4.7781</v>
       </c>
       <c r="N5" t="n">
         <v>288</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1886</v>
+        <v>4.0047</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9664</v>
+        <v>0.924</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2529</v>
+        <v>1.1988</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1886</v>
+        <v>4.0047</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8253</v>
+        <v>2.5137</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3633</v>
+        <v>1.491</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8441</v>
+        <v>2.7768</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0829</v>
+        <v>2.9218</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3633</v>
+        <v>1.491</v>
       </c>
       <c r="K6" t="n">
         <v>155</v>
@@ -713,7 +713,7 @@
         <v>106</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4462</v>
+        <v>4.412800000000001</v>
       </c>
       <c r="N6" t="n">
         <v>261</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7229</v>
+        <v>3.7031</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8589</v>
+        <v>0.8544</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0427</v>
+        <v>1.0615</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7229</v>
+        <v>3.7031</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7752</v>
+        <v>2.693</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9477</v>
+        <v>1.0101</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2917</v>
+        <v>3.991</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2315</v>
+        <v>2.1551</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9477</v>
+        <v>1.0101</v>
       </c>
       <c r="K7" t="n">
         <v>103</v>
@@ -759,7 +759,7 @@
         <v>144</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1792</v>
+        <v>3.1652</v>
       </c>
       <c r="N7" t="n">
         <v>247</v>
@@ -768,81 +768,81 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3678</v>
+        <v>3.2354</v>
       </c>
       <c r="C8" t="n">
-        <v>0.777</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8824</v>
+        <v>0.8486</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3678</v>
+        <v>3.2354</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1154</v>
+        <v>3.2652</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2524</v>
+        <v>-0.0298</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4811</v>
+        <v>5.8788</v>
       </c>
       <c r="I8" t="n">
-        <v>4.0901</v>
+        <v>3.1745</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2524</v>
+        <v>-0.0298</v>
       </c>
       <c r="K8" t="n">
-        <v>175</v>
+        <v>103</v>
       </c>
       <c r="L8" t="n">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="M8" t="n">
-        <v>4.342499999999999</v>
+        <v>3.1447</v>
       </c>
       <c r="N8" t="n">
-        <v>231</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3584</v>
+        <v>3.1574</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7748</v>
+        <v>0.7285</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8781</v>
+        <v>0.8131</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3584</v>
+        <v>3.1574</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2389</v>
+        <v>2.8777</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1195</v>
+        <v>0.2797</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7524</v>
+        <v>3.5735</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4088</v>
+        <v>3.9563</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1195</v>
+        <v>0.2797</v>
       </c>
       <c r="K9" t="n">
         <v>175</v>
@@ -851,7 +851,7 @@
         <v>56</v>
       </c>
       <c r="M9" t="n">
-        <v>4.528300000000001</v>
+        <v>4.236</v>
       </c>
       <c r="N9" t="n">
         <v>231</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>xsepower</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3193</v>
+        <v>3.1113</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7658</v>
+        <v>0.7178</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8605</v>
+        <v>0.7921</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3193</v>
+        <v>3.1113</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0505</v>
+        <v>2.9965</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2688</v>
+        <v>0.1148</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3385</v>
+        <v>3.8335</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7676</v>
+        <v>4.2442</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2688</v>
+        <v>0.1148</v>
       </c>
       <c r="K10" t="n">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="L10" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M10" t="n">
-        <v>4.0364</v>
+        <v>4.359</v>
       </c>
       <c r="N10" t="n">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>xsepower</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2436</v>
+        <v>3.1016</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7484</v>
+        <v>0.7156</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8263</v>
+        <v>0.7877</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2436</v>
+        <v>3.1016</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3392</v>
+        <v>2.795</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0956</v>
+        <v>0.3066</v>
       </c>
       <c r="H11" t="n">
-        <v>6.279</v>
+        <v>3.3924</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2648</v>
+        <v>3.6615</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0956</v>
+        <v>0.3066</v>
       </c>
       <c r="K11" t="n">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="L11" t="n">
-        <v>144</v>
+        <v>50</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1692</v>
+        <v>3.9681</v>
       </c>
       <c r="N11" t="n">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.774</v>
+        <v>2.8898</v>
       </c>
       <c r="C12" t="n">
-        <v>0.64</v>
+        <v>0.6667</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6143</v>
+        <v>0.6913</v>
       </c>
       <c r="E12" t="n">
-        <v>2.774</v>
+        <v>2.8898</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6801</v>
+        <v>1.6752</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0939</v>
+        <v>1.2146</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6801</v>
+        <v>1.6752</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8211</v>
+        <v>1.7627</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0939</v>
+        <v>1.2146</v>
       </c>
       <c r="K12" t="n">
         <v>155</v>
@@ -989,7 +989,7 @@
         <v>106</v>
       </c>
       <c r="M12" t="n">
-        <v>2.915</v>
+        <v>2.9773</v>
       </c>
       <c r="N12" t="n">
         <v>261</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7371</v>
+        <v>2.726</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6315</v>
+        <v>0.6289</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5977</v>
+        <v>0.6167</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7371</v>
+        <v>2.726</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2384</v>
+        <v>2.1827</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4987</v>
+        <v>0.5433</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4004</v>
+        <v>2.3073</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2481</v>
+        <v>1.2459</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4987</v>
+        <v>0.5433</v>
       </c>
       <c r="K13" t="n">
         <v>142</v>
@@ -1035,7 +1035,7 @@
         <v>146</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7468</v>
+        <v>1.7892</v>
       </c>
       <c r="N13" t="n">
         <v>288</v>
@@ -1044,139 +1044,139 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6462</v>
+        <v>2.6253</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6105</v>
+        <v>0.6057</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5566</v>
+        <v>0.5709</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6462</v>
+        <v>2.6253</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5147</v>
+        <v>0.357</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1315</v>
+        <v>2.2683</v>
       </c>
       <c r="H14" t="n">
-        <v>3.374</v>
+        <v>0.357</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7543</v>
+        <v>0.357</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1315</v>
+        <v>2.2683</v>
       </c>
       <c r="K14" t="n">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="L14" t="n">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8858</v>
+        <v>2.6253</v>
       </c>
       <c r="N14" t="n">
-        <v>288</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jerry</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.585</v>
+        <v>2.5632</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5964</v>
+        <v>0.5914</v>
       </c>
       <c r="D15" t="n">
-        <v>0.529</v>
+        <v>0.5426</v>
       </c>
       <c r="E15" t="n">
-        <v>2.585</v>
+        <v>2.5632</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2264</v>
+        <v>2.4434</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6414</v>
+        <v>0.1198</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7249</v>
+        <v>3.1676</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2036</v>
+        <v>1.7105</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6414</v>
+        <v>0.1198</v>
       </c>
       <c r="K15" t="n">
-        <v>189</v>
+        <v>142</v>
       </c>
       <c r="L15" t="n">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5622</v>
+        <v>1.8303</v>
       </c>
       <c r="N15" t="n">
-        <v>239</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4644</v>
+        <v>2.4059</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5686</v>
+        <v>0.5551</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4745</v>
+        <v>0.471</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4644</v>
+        <v>2.4059</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3826</v>
+        <v>1.8142</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0818</v>
+        <v>0.5917</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3826</v>
+        <v>1.8142</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3826</v>
+        <v>2.0085</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0818</v>
+        <v>0.5917</v>
       </c>
       <c r="K16" t="n">
-        <v>65</v>
+        <v>175</v>
       </c>
       <c r="L16" t="n">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4644</v>
+        <v>2.6002</v>
       </c>
       <c r="N16" t="n">
-        <v>179</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3367</v>
+        <v>2.3368</v>
       </c>
       <c r="C17" t="n">
         <v>0.5391</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4169</v>
+        <v>0.4396</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3367</v>
+        <v>2.3368</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9763</v>
+        <v>1.9851</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3604</v>
+        <v>0.3517</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9763</v>
+        <v>1.9851</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2303</v>
+        <v>2.1425</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3604</v>
+        <v>0.3517</v>
       </c>
       <c r="K17" t="n">
         <v>189</v>
@@ -1219,7 +1219,7 @@
         <v>50</v>
       </c>
       <c r="M17" t="n">
-        <v>2.5907</v>
+        <v>2.4942</v>
       </c>
       <c r="N17" t="n">
         <v>239</v>
@@ -1228,139 +1228,139 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>Jerry</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3205</v>
+        <v>2.3181</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5354</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4096</v>
+        <v>0.431</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3205</v>
+        <v>2.3181</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7557</v>
+        <v>2.9848</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5648</v>
+        <v>-0.6667</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7557</v>
+        <v>3.8078</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0628</v>
+        <v>4.1098</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5648</v>
+        <v>-0.6667</v>
       </c>
       <c r="K18" t="n">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="L18" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6276</v>
+        <v>3.4431</v>
       </c>
       <c r="N18" t="n">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>almazer</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1867</v>
+        <v>2.2574</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.5208</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3492</v>
+        <v>0.4034</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1867</v>
+        <v>2.2574</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2437</v>
+        <v>1.1532</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.057</v>
+        <v>1.1042</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2437</v>
+        <v>1.1532</v>
       </c>
       <c r="I19" t="n">
-        <v>2.5321</v>
+        <v>1.2134</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.057</v>
+        <v>1.1042</v>
       </c>
       <c r="K19" t="n">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="L19" t="n">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="M19" t="n">
-        <v>2.4751</v>
+        <v>2.3176</v>
       </c>
       <c r="N19" t="n">
-        <v>239</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>almazer</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1141</v>
+        <v>2.2095</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4878</v>
+        <v>0.5098</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3164</v>
+        <v>0.3816</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1141</v>
+        <v>2.2095</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2198</v>
+        <v>2.2752</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8943</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2198</v>
+        <v>2.2752</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3222</v>
+        <v>2.4557</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8943</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="L20" t="n">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="M20" t="n">
-        <v>2.2165</v>
+        <v>2.39</v>
       </c>
       <c r="N20" t="n">
-        <v>261</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0722</v>
+        <v>2.089</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4781</v>
+        <v>0.482</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2975</v>
+        <v>0.3268</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0722</v>
+        <v>2.089</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3462</v>
+        <v>2.365</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.274</v>
+        <v>-0.276</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3462</v>
+        <v>2.4514</v>
       </c>
       <c r="I21" t="n">
-        <v>2.6477</v>
+        <v>2.6458</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.274</v>
+        <v>-0.276</v>
       </c>
       <c r="K21" t="n">
         <v>189</v>
@@ -1403,7 +1403,7 @@
         <v>50</v>
       </c>
       <c r="M21" t="n">
-        <v>2.3737</v>
+        <v>2.3698</v>
       </c>
       <c r="N21" t="n">
         <v>239</v>
@@ -1412,81 +1412,81 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8818</v>
+        <v>2.0164</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4342</v>
+        <v>0.4652</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2115</v>
+        <v>0.2937</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8818</v>
+        <v>2.0164</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0436</v>
+        <v>2.1764</v>
       </c>
       <c r="G22" t="n">
-        <v>1.8382</v>
+        <v>-0.16</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0436</v>
+        <v>2.1764</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0473</v>
+        <v>2.29</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8382</v>
+        <v>-0.16</v>
       </c>
       <c r="K22" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="L22" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="M22" t="n">
-        <v>1.8855</v>
+        <v>2.13</v>
       </c>
       <c r="N22" t="n">
-        <v>276</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.8685</v>
+        <v>1.9998</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4311</v>
+        <v>0.4614</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2055</v>
+        <v>0.2861</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8685</v>
+        <v>1.9998</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2829</v>
+        <v>-0.0216</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4144</v>
+        <v>2.0214</v>
       </c>
       <c r="H23" t="n">
-        <v>2.2829</v>
+        <v>-0.0216</v>
       </c>
       <c r="I23" t="n">
-        <v>2.4745</v>
+        <v>-0.0227</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4144</v>
+        <v>2.0214</v>
       </c>
       <c r="K23" t="n">
         <v>162</v>
@@ -1495,7 +1495,7 @@
         <v>114</v>
       </c>
       <c r="M23" t="n">
-        <v>2.0601</v>
+        <v>1.9987</v>
       </c>
       <c r="N23" t="n">
         <v>276</v>
@@ -1504,47 +1504,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8425</v>
+        <v>1.9245</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4251</v>
+        <v>0.444</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1938</v>
+        <v>0.2519</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8425</v>
+        <v>1.9245</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1016</v>
+        <v>2.24</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2591</v>
+        <v>-0.3155</v>
       </c>
       <c r="H24" t="n">
-        <v>2.1016</v>
+        <v>2.24</v>
       </c>
       <c r="I24" t="n">
-        <v>2.278</v>
+        <v>2.3569</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2591</v>
+        <v>-0.3155</v>
       </c>
       <c r="K24" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="L24" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M24" t="n">
-        <v>2.0189</v>
+        <v>2.0414</v>
       </c>
       <c r="N24" t="n">
-        <v>261</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7065</v>
+        <v>1.7082</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3937</v>
+        <v>0.3941</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1324</v>
+        <v>0.1534</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7065</v>
+        <v>1.7082</v>
       </c>
       <c r="F25" t="n">
-        <v>2.2276</v>
+        <v>2.2588</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5211</v>
+        <v>-0.5506</v>
       </c>
       <c r="H25" t="n">
-        <v>2.2276</v>
+        <v>2.2588</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6173</v>
+        <v>2.5008</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5211</v>
+        <v>-0.5506</v>
       </c>
       <c r="K25" t="n">
         <v>175</v>
@@ -1587,7 +1587,7 @@
         <v>56</v>
       </c>
       <c r="M25" t="n">
-        <v>2.0962</v>
+        <v>1.9502</v>
       </c>
       <c r="N25" t="n">
         <v>231</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.5296</v>
+        <v>1.591</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3529</v>
+        <v>0.3671</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0525</v>
+        <v>0.1001</v>
       </c>
       <c r="E26" t="n">
-        <v>1.5296</v>
+        <v>1.591</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3437</v>
+        <v>0.258</v>
       </c>
       <c r="G26" t="n">
-        <v>1.1859</v>
+        <v>1.333</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3437</v>
+        <v>0.258</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3726</v>
+        <v>0.2715</v>
       </c>
       <c r="J26" t="n">
-        <v>1.1859</v>
+        <v>1.333</v>
       </c>
       <c r="K26" t="n">
         <v>155</v>
@@ -1633,7 +1633,7 @@
         <v>106</v>
       </c>
       <c r="M26" t="n">
-        <v>1.5585</v>
+        <v>1.6045</v>
       </c>
       <c r="N26" t="n">
         <v>261</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7947</v>
+        <v>0.8012</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1834</v>
+        <v>0.1849</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2792</v>
+        <v>-0.2595</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7947</v>
+        <v>0.8012</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7947</v>
+        <v>0.8012</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7947</v>
+        <v>0.8012</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8274</v>
+        <v>0.8218</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8274</v>
+        <v>0.8218</v>
       </c>
       <c r="N27" t="n">
         <v>169</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.425</v>
+        <v>0.4</v>
       </c>
       <c r="C28" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4461</v>
+        <v>-0.4421</v>
       </c>
       <c r="E28" t="n">
-        <v>0.425</v>
+        <v>0.4</v>
       </c>
       <c r="F28" t="n">
-        <v>0.425</v>
+        <v>0.4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.425</v>
+        <v>0.4</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4425</v>
+        <v>0.4103</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4425</v>
+        <v>0.4103</v>
       </c>
       <c r="N28" t="n">
         <v>169</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3165</v>
+        <v>0.2306</v>
       </c>
       <c r="C29" t="n">
-        <v>0.073</v>
+        <v>0.0532</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4951</v>
+        <v>-0.5192</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3165</v>
+        <v>0.2306</v>
       </c>
       <c r="F29" t="n">
-        <v>2.3165</v>
+        <v>2.2306</v>
       </c>
       <c r="G29" t="n">
         <v>-2</v>
       </c>
       <c r="H29" t="n">
-        <v>2.6754</v>
+        <v>2.4652</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3911</v>
+        <v>1.3312</v>
       </c>
       <c r="J29" t="n">
         <v>-2</v>
@@ -1771,7 +1771,7 @@
         <v>144</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6089</v>
+        <v>-0.6688000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>247</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0165</v>
+        <v>0.0065</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0038</v>
+        <v>0.0015</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6306</v>
+        <v>-0.6212</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0165</v>
+        <v>0.0065</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0165</v>
+        <v>0.0065</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0165</v>
+        <v>0.0065</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0172</v>
+        <v>0.0067</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0172</v>
+        <v>0.0067</v>
       </c>
       <c r="N30" t="n">
         <v>169</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4408</v>
+        <v>-0.5078</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1017</v>
+        <v>-0.1172</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.837</v>
+        <v>-0.8554</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4408</v>
+        <v>-0.5078</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4408</v>
+        <v>-0.5078</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4408</v>
+        <v>-0.5078</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4408</v>
+        <v>-0.5078</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4408</v>
+        <v>-0.5078</v>
       </c>
       <c r="N31" t="n">
         <v>83</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5837</v>
+        <v>-0.6117</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1347</v>
+        <v>-0.1411</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9015</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5837</v>
+        <v>-0.6117</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5837</v>
+        <v>-0.6117</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5837</v>
+        <v>-0.6117</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6077</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6077</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="N32" t="n">
         <v>169</v>
@@ -1918,185 +1918,185 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7248</v>
+        <v>-0.7758</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1672</v>
+        <v>-0.179</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-0.9774</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7248</v>
+        <v>-0.7758</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7248</v>
+        <v>-0.5652</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.2106</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7248</v>
+        <v>-0.5652</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7546</v>
+        <v>-0.3052</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.2106</v>
       </c>
       <c r="K33" t="n">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7546</v>
+        <v>-0.5158</v>
       </c>
       <c r="N33" t="n">
-        <v>169</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-0.7816</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1859</v>
+        <v>-0.1803</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0018</v>
+        <v>-0.98</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-0.7816</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7598</v>
+        <v>-0.7816</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0461</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7598</v>
+        <v>-0.7816</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8236</v>
+        <v>-0.8017</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.0461</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="L34" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8697</v>
+        <v>-0.8017</v>
       </c>
       <c r="N34" t="n">
-        <v>276</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SLOWLY</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8861</v>
+        <v>-0.8642</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2044</v>
+        <v>-0.1994</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.038</v>
+        <v>-1.0176</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8861</v>
+        <v>-0.8642</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8861</v>
+        <v>-0.8841</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.0199</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8861</v>
+        <v>-0.8841</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8861</v>
+        <v>-0.9303</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.0199</v>
       </c>
       <c r="K35" t="n">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8861</v>
+        <v>-0.9104</v>
       </c>
       <c r="N35" t="n">
-        <v>83</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>SLOWLY</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.93</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2146</v>
+        <v>-0.2204</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0579</v>
+        <v>-1.059</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.93</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7181</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.2119</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7181</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3734</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.2119</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="L36" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5853</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>288</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.977</v>
+        <v>-1.0339</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2254</v>
+        <v>-0.2385</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0791</v>
+        <v>-1.0949</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.977</v>
+        <v>-1.0339</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4001</v>
+        <v>-0.4299</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5769</v>
+        <v>-0.604</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4001</v>
+        <v>-0.4299</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4701</v>
+        <v>-0.4759</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5769</v>
+        <v>-0.604</v>
       </c>
       <c r="K37" t="n">
         <v>175</v>
@@ -2139,7 +2139,7 @@
         <v>56</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.047</v>
+        <v>-1.0799</v>
       </c>
       <c r="N37" t="n">
         <v>231</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.984</v>
+        <v>-1.0684</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.227</v>
+        <v>-0.2465</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0822</v>
+        <v>-1.1106</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.984</v>
+        <v>-1.0684</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.984</v>
+        <v>-1.0684</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.984</v>
+        <v>-1.0684</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.984</v>
+        <v>-1.0684</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.984</v>
+        <v>-1.0684</v>
       </c>
       <c r="N38" t="n">
         <v>83</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0922</v>
+        <v>-1.0724</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.252</v>
+        <v>-0.2474</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1311</v>
+        <v>-1.1124</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0922</v>
+        <v>-1.0724</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0922</v>
+        <v>-1.0724</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0922</v>
+        <v>-1.0724</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1371</v>
+        <v>-1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1371</v>
+        <v>-1.1</v>
       </c>
       <c r="N39" t="n">
         <v>97</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3572</v>
+        <v>-1.4484</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3131</v>
+        <v>-0.3342</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2507</v>
+        <v>-1.2835</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3572</v>
+        <v>-1.4484</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2666</v>
+        <v>0.2033</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.6238</v>
+        <v>-1.6517</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2666</v>
+        <v>0.2033</v>
       </c>
       <c r="I40" t="n">
-        <v>0.289</v>
+        <v>0.2139</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.6238</v>
+        <v>-1.6517</v>
       </c>
       <c r="K40" t="n">
         <v>162</v>
@@ -2277,7 +2277,7 @@
         <v>114</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3348</v>
+        <v>-1.4378</v>
       </c>
       <c r="N40" t="n">
         <v>276</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4214</v>
+        <v>-1.4855</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3279</v>
+        <v>-0.3427</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2797</v>
+        <v>-1.3004</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4214</v>
+        <v>-1.4855</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4214</v>
+        <v>-1.4855</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4214</v>
+        <v>-1.4855</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4214</v>
+        <v>-1.4855</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4214</v>
+        <v>-1.4855</v>
       </c>
       <c r="N41" t="n">
         <v>83</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-1.5066</v>
+        <v>-1.4996</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.3476</v>
+        <v>-0.346</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.3182</v>
+        <v>-1.3069</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.5066</v>
+        <v>-1.4996</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.5066</v>
+        <v>-1.4996</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.5066</v>
+        <v>-1.4996</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.5066</v>
+        <v>-1.4996</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-1.5066</v>
+        <v>-1.4996</v>
       </c>
       <c r="N42" t="n">
         <v>83</v>
@@ -2475,10 +2475,10 @@
         <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.772</v>
       </c>
       <c r="J2" t="n">
-        <v>28.1015</v>
+        <v>27.02</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>1.02</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0475</v>
+        <v>0.0553</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6625</v>
+        <v>1.9355</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0025</v>
+        <v>-0.0019</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.0665</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0917</v>
+        <v>-0.1018</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.2095</v>
+        <v>-3.563</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.64</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.396</v>
+        <v>-0.4047</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.86</v>
+        <v>-14.1645</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4428</v>
+        <v>0.4487</v>
       </c>
       <c r="J7" t="n">
-        <v>15.498</v>
+        <v>15.7045</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.26</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3812</v>
+        <v>0.39</v>
       </c>
       <c r="J8" t="n">
-        <v>13.342</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.12</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1981</v>
+        <v>0.2117</v>
       </c>
       <c r="J9" t="n">
-        <v>6.9335</v>
+        <v>7.4095</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>0.74</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3018</v>
+        <v>-0.3134</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.563</v>
+        <v>-10.969</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>0.74</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3018</v>
+        <v>-0.3134</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.563</v>
+        <v>-10.969</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.87</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6227</v>
+        <v>1.7491</v>
       </c>
       <c r="J12" t="n">
-        <v>45.4356</v>
+        <v>48.9748</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>1.01</v>
       </c>
       <c r="I13" t="n">
-        <v>0.021</v>
+        <v>0.0365</v>
       </c>
       <c r="J13" t="n">
-        <v>0.588</v>
+        <v>1.022</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.99</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0887</v>
+        <v>-0.083</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.4836</v>
+        <v>-2.324</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.93</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.299</v>
+        <v>-0.2866</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.372</v>
+        <v>-8.024800000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3593</v>
+        <v>-0.3427</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.0604</v>
+        <v>-9.595599999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.13</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3226</v>
+        <v>0.3216</v>
       </c>
       <c r="J17" t="n">
-        <v>9.0328</v>
+        <v>9.004799999999999</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2615</v>
+        <v>0.2635</v>
       </c>
       <c r="J18" t="n">
-        <v>7.322</v>
+        <v>7.378</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>0.89</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1393</v>
+        <v>-0.1536</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.9004</v>
+        <v>-4.3008</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>0.83</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2022</v>
+        <v>-0.2172</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.6616</v>
+        <v>-6.0816</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2525</v>
+        <v>-0.267</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.07</v>
+        <v>-7.476</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.59</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2485</v>
+        <v>1.2961</v>
       </c>
       <c r="J22" t="n">
-        <v>31.2125</v>
+        <v>32.4025</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.42</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0302</v>
+        <v>0.9823</v>
       </c>
       <c r="J23" t="n">
-        <v>25.755</v>
+        <v>24.5575</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>1.3</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7867</v>
+        <v>0.7483</v>
       </c>
       <c r="J24" t="n">
-        <v>19.6675</v>
+        <v>18.7075</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>1.12</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3519</v>
+        <v>0.3571</v>
       </c>
       <c r="J25" t="n">
-        <v>8.797499999999999</v>
+        <v>8.9275</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9302</v>
+        <v>-0.8489</v>
       </c>
       <c r="J26" t="n">
-        <v>-23.255</v>
+        <v>-21.2225</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.11</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3305</v>
+        <v>0.3187</v>
       </c>
       <c r="J27" t="n">
-        <v>8.262499999999999</v>
+        <v>7.9675</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>0.78</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2373</v>
+        <v>-0.2553</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.9325</v>
+        <v>-6.3825</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.247</v>
+        <v>-0.2648</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.175</v>
+        <v>-6.62</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>0.74</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2759</v>
+        <v>-0.2932</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.8975</v>
+        <v>-7.33</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.73</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2855</v>
+        <v>-0.3026</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.1375</v>
+        <v>-7.565</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.24</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5921</v>
       </c>
       <c r="J32" t="n">
-        <v>15.0304</v>
+        <v>16.5788</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4341</v>
+        <v>0.4769</v>
       </c>
       <c r="J33" t="n">
-        <v>12.1548</v>
+        <v>13.3532</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.14</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3886</v>
+        <v>0.4195</v>
       </c>
       <c r="J34" t="n">
-        <v>10.8808</v>
+        <v>11.746</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>1.06</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2053</v>
+        <v>0.2143</v>
       </c>
       <c r="J35" t="n">
-        <v>5.7484</v>
+        <v>6.0004</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2275</v>
+        <v>-0.2212</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.37</v>
+        <v>-6.1936</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.32</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5441</v>
+        <v>0.6004</v>
       </c>
       <c r="J37" t="n">
-        <v>15.2348</v>
+        <v>16.8112</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>0.9</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1253</v>
+        <v>-0.1401</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.5084</v>
+        <v>-3.9228</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>0.82</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2085</v>
+        <v>-0.2244</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.838</v>
+        <v>-6.2832</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.79</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2386</v>
+        <v>-0.2542</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.6808</v>
+        <v>-7.1176</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2876</v>
+        <v>-0.3023</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.0528</v>
+        <v>-8.464399999999999</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.37</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7025</v>
+        <v>0.7775</v>
       </c>
       <c r="J42" t="n">
-        <v>21.075</v>
+        <v>23.325</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.28</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5807</v>
+        <v>0.6437</v>
       </c>
       <c r="J43" t="n">
-        <v>17.421</v>
+        <v>19.311</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.11</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3314</v>
+        <v>0.3391</v>
       </c>
       <c r="J44" t="n">
-        <v>9.942</v>
+        <v>10.173</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.08</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2496</v>
+        <v>0.26</v>
       </c>
       <c r="J45" t="n">
-        <v>7.488</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>1.06</v>
       </c>
       <c r="I46" t="n">
-        <v>0.189</v>
+        <v>0.2031</v>
       </c>
       <c r="J46" t="n">
-        <v>5.67</v>
+        <v>6.093</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.26</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4787</v>
+        <v>0.5264</v>
       </c>
       <c r="J47" t="n">
-        <v>14.361</v>
+        <v>15.792</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>1.24</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4571</v>
+        <v>0.5017</v>
       </c>
       <c r="J48" t="n">
-        <v>13.713</v>
+        <v>15.051</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.75</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2786</v>
+        <v>-0.2934</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.358000000000001</v>
+        <v>-8.802</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3362</v>
+        <v>-0.3494</v>
       </c>
       <c r="J50" t="n">
-        <v>-10.086</v>
+        <v>-10.482</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.66</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3646</v>
+        <v>-0.3767</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.938</v>
+        <v>-11.301</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.54</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9314</v>
+        <v>1.0227</v>
       </c>
       <c r="J52" t="n">
-        <v>26.0792</v>
+        <v>28.6356</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3848</v>
+        <v>0.4154</v>
       </c>
       <c r="J53" t="n">
-        <v>10.7744</v>
+        <v>11.6312</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>1.08</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2558</v>
+        <v>0.2642</v>
       </c>
       <c r="J54" t="n">
-        <v>7.1624</v>
+        <v>7.3976</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>1.01</v>
       </c>
       <c r="I55" t="n">
-        <v>0.018</v>
+        <v>0.0344</v>
       </c>
       <c r="J55" t="n">
-        <v>0.504</v>
+        <v>0.9631999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0369</v>
+        <v>-0.0254</v>
       </c>
       <c r="J56" t="n">
-        <v>-1.0332</v>
+        <v>-0.7112000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5566</v>
+        <v>0.6163</v>
       </c>
       <c r="J57" t="n">
-        <v>15.5848</v>
+        <v>17.2564</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.02</v>
       </c>
       <c r="I58" t="n">
-        <v>0.078</v>
+        <v>0.0819</v>
       </c>
       <c r="J58" t="n">
-        <v>2.184</v>
+        <v>2.2932</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>0.98</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0314</v>
+        <v>-0.0393</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.8792</v>
+        <v>-1.1004</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3389</v>
+        <v>-0.3515</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.4892</v>
+        <v>-9.842000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.68</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3484</v>
+        <v>-0.3607</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.7552</v>
+        <v>-10.0996</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.56</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9771</v>
+        <v>1.0679</v>
       </c>
       <c r="J62" t="n">
-        <v>27.3588</v>
+        <v>29.9012</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.55</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9641</v>
+        <v>1.0541</v>
       </c>
       <c r="J63" t="n">
-        <v>26.9948</v>
+        <v>29.5148</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>1.14</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3914</v>
+        <v>0.4224</v>
       </c>
       <c r="J64" t="n">
-        <v>10.9592</v>
+        <v>11.8272</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.65</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0198</v>
+        <v>-0.9317</v>
       </c>
       <c r="J65" t="n">
-        <v>-28.5544</v>
+        <v>-26.0876</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.2318</v>
+        <v>-1.1137</v>
       </c>
       <c r="J66" t="n">
-        <v>-34.4904</v>
+        <v>-31.1836</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.09</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2204</v>
+        <v>0.2288</v>
       </c>
       <c r="J67" t="n">
-        <v>6.1712</v>
+        <v>6.4064</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.08</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1997</v>
+        <v>0.2087</v>
       </c>
       <c r="J68" t="n">
-        <v>5.5916</v>
+        <v>5.8436</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1349</v>
+        <v>0.1447</v>
       </c>
       <c r="J69" t="n">
-        <v>3.7772</v>
+        <v>4.0516</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>1.04</v>
       </c>
       <c r="I70" t="n">
-        <v>0.112</v>
+        <v>0.1217</v>
       </c>
       <c r="J70" t="n">
-        <v>3.136</v>
+        <v>3.4076</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1802</v>
+        <v>-0.193</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.0456</v>
+        <v>-5.404</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.05</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1835</v>
+        <v>0.18</v>
       </c>
       <c r="J72" t="n">
-        <v>4.771</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>0.95</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0599</v>
+        <v>-0.0738</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.5574</v>
+        <v>-1.9188</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>0.85</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1716</v>
+        <v>-0.1889</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.4616</v>
+        <v>-4.9114</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>0.75</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2698</v>
+        <v>-0.2865</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.0148</v>
+        <v>-7.449</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.66</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3557</v>
+        <v>-0.3698</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.248200000000001</v>
+        <v>-9.614800000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.46</v>
       </c>
       <c r="I77" t="n">
-        <v>0.821</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>21.346</v>
+        <v>23.5482</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.4</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7423</v>
+        <v>0.8208</v>
       </c>
       <c r="J78" t="n">
-        <v>19.2998</v>
+        <v>21.3408</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>1.29</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5944</v>
+        <v>0.6589</v>
       </c>
       <c r="J79" t="n">
-        <v>15.4544</v>
+        <v>17.1314</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.92</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3394</v>
+        <v>-0.322</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.824400000000001</v>
+        <v>-8.372</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.83</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5918</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.3868</v>
+        <v>-14.3494</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.23</v>
       </c>
       <c r="I82" t="n">
-        <v>0.424</v>
+        <v>0.4686</v>
       </c>
       <c r="J82" t="n">
-        <v>12.72</v>
+        <v>14.058</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.19</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3813</v>
+        <v>0.4117</v>
       </c>
       <c r="J83" t="n">
-        <v>11.439</v>
+        <v>12.351</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1.07</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1794</v>
+        <v>0.1886</v>
       </c>
       <c r="J84" t="n">
-        <v>5.382</v>
+        <v>5.658</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2212</v>
+        <v>-0.2342</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.636</v>
+        <v>-7.026</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2513</v>
+        <v>-0.2641</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.539</v>
+        <v>-7.923</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.52</v>
       </c>
       <c r="I87" t="n">
-        <v>0.912</v>
+        <v>1.0009</v>
       </c>
       <c r="J87" t="n">
-        <v>27.36</v>
+        <v>30.027</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.42</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7804</v>
+        <v>0.8597</v>
       </c>
       <c r="J88" t="n">
-        <v>23.412</v>
+        <v>25.791</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>1.1</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3167</v>
+        <v>0.3207</v>
       </c>
       <c r="J89" t="n">
-        <v>9.500999999999999</v>
+        <v>9.621</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6322</v>
+        <v>-0.5903</v>
       </c>
       <c r="J90" t="n">
-        <v>-18.966</v>
+        <v>-17.709</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6322</v>
+        <v>-0.5903</v>
       </c>
       <c r="J91" t="n">
-        <v>-18.966</v>
+        <v>-17.709</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.55</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8897</v>
+        <v>0.9885</v>
       </c>
       <c r="J92" t="n">
-        <v>19.5734</v>
+        <v>21.747</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.45</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7691</v>
+        <v>0.8578</v>
       </c>
       <c r="J93" t="n">
-        <v>16.9202</v>
+        <v>18.8716</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>1.44</v>
       </c>
       <c r="I94" t="n">
-        <v>0.757</v>
+        <v>0.8446</v>
       </c>
       <c r="J94" t="n">
-        <v>16.654</v>
+        <v>18.5812</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>1.33</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6213</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="J95" t="n">
-        <v>13.6686</v>
+        <v>15.2922</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>1.26</v>
       </c>
       <c r="I96" t="n">
-        <v>0.5278</v>
+        <v>0.5914</v>
       </c>
       <c r="J96" t="n">
-        <v>11.6116</v>
+        <v>13.0108</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3019</v>
+        <v>0.2837</v>
       </c>
       <c r="J97" t="n">
-        <v>6.6418</v>
+        <v>6.2414</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>0.78</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2301</v>
+        <v>-0.2498</v>
       </c>
       <c r="J98" t="n">
-        <v>-5.0622</v>
+        <v>-5.4956</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>0.78</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2301</v>
+        <v>-0.2498</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.0622</v>
+        <v>-5.4956</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>0.57</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4262</v>
+        <v>-0.4394</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.3764</v>
+        <v>-9.6668</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.57</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4262</v>
+        <v>-0.4394</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.3764</v>
+        <v>-9.6668</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.29</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6208</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="J102" t="n">
-        <v>17.3824</v>
+        <v>19.096</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.24</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5485</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="J103" t="n">
-        <v>15.358</v>
+        <v>16.8644</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>1.17</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4436</v>
+        <v>0.4852</v>
       </c>
       <c r="J104" t="n">
-        <v>12.4208</v>
+        <v>13.5856</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>0.8</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.6382</v>
+        <v>-0.5994</v>
       </c>
       <c r="J105" t="n">
-        <v>-17.8696</v>
+        <v>-16.7832</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.79</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.664</v>
+        <v>-0.6223</v>
       </c>
       <c r="J106" t="n">
-        <v>-18.592</v>
+        <v>-17.4244</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.31</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4989</v>
+        <v>0.5564</v>
       </c>
       <c r="J107" t="n">
-        <v>13.9692</v>
+        <v>15.5792</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.07</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1731</v>
+        <v>0.1841</v>
       </c>
       <c r="J108" t="n">
-        <v>4.8468</v>
+        <v>5.1548</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>1.06</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1522</v>
+        <v>0.1634</v>
       </c>
       <c r="J109" t="n">
-        <v>4.2616</v>
+        <v>4.5752</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0585</v>
+        <v>0.068</v>
       </c>
       <c r="J110" t="n">
-        <v>1.638</v>
+        <v>1.904</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.83</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2152</v>
+        <v>-0.2273</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.0256</v>
+        <v>-6.3644</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.75</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8591</v>
+        <v>0.8471</v>
       </c>
       <c r="J112" t="n">
-        <v>18.9002</v>
+        <v>18.6362</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.46</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5587</v>
+        <v>0.5681</v>
       </c>
       <c r="J113" t="n">
-        <v>12.2914</v>
+        <v>12.4982</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.41</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5053</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J114" t="n">
-        <v>11.1166</v>
+        <v>11.3872</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>1.15</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2055</v>
+        <v>0.2271</v>
       </c>
       <c r="J115" t="n">
-        <v>4.521</v>
+        <v>4.9962</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.87</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1992</v>
+        <v>-0.2056</v>
       </c>
       <c r="J116" t="n">
-        <v>-4.3824</v>
+        <v>-4.5232</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.12</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2849</v>
+        <v>0.2772</v>
       </c>
       <c r="J117" t="n">
-        <v>6.2678</v>
+        <v>6.0984</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.03</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1232</v>
+        <v>0.1179</v>
       </c>
       <c r="J118" t="n">
-        <v>2.7104</v>
+        <v>2.5938</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.73</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2804</v>
+        <v>-0.2986</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.1688</v>
+        <v>-6.5692</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.57</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.431</v>
+        <v>-0.4431</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.481999999999999</v>
+        <v>-9.748200000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.49</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.505</v>
+        <v>-0.513</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.11</v>
+        <v>-11.286</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>0.66</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.2648</v>
+        <v>-0.2989</v>
       </c>
       <c r="J122" t="n">
-        <v>-4.5016</v>
+        <v>-5.0813</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>0.5</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.4367</v>
+        <v>-0.4584</v>
       </c>
       <c r="J123" t="n">
-        <v>-7.4239</v>
+        <v>-7.7928</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>0.42</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.5094</v>
+        <v>-0.5261</v>
       </c>
       <c r="J124" t="n">
-        <v>-8.659800000000001</v>
+        <v>-8.9437</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>0.36</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5679</v>
+        <v>-0.5796</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.654299999999999</v>
+        <v>-9.853199999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.34</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5879</v>
+        <v>-0.5979</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.994300000000001</v>
+        <v>-10.1643</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>2.06</v>
       </c>
       <c r="I127" t="n">
-        <v>1.693</v>
+        <v>1.7053</v>
       </c>
       <c r="J127" t="n">
-        <v>28.781</v>
+        <v>28.9901</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.74</v>
       </c>
       <c r="I128" t="n">
-        <v>1.3476</v>
+        <v>1.3402</v>
       </c>
       <c r="J128" t="n">
-        <v>22.9092</v>
+        <v>22.7834</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>1.68</v>
       </c>
       <c r="I129" t="n">
-        <v>1.2829</v>
+        <v>1.2706</v>
       </c>
       <c r="J129" t="n">
-        <v>21.8093</v>
+        <v>21.6002</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>1.48</v>
       </c>
       <c r="I130" t="n">
-        <v>1.0528</v>
+        <v>1.0187</v>
       </c>
       <c r="J130" t="n">
-        <v>17.8976</v>
+        <v>17.3179</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>1.45</v>
       </c>
       <c r="I131" t="n">
-        <v>1.0113</v>
+        <v>0.9717</v>
       </c>
       <c r="J131" t="n">
-        <v>17.1921</v>
+        <v>16.5189</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.18</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4419</v>
+        <v>0.4288</v>
       </c>
       <c r="J132" t="n">
-        <v>11.4894</v>
+        <v>11.1488</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>0.86</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1652</v>
+        <v>-0.1814</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.2952</v>
+        <v>-4.7164</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>0.83</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1958</v>
+        <v>-0.2122</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.0908</v>
+        <v>-5.5172</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2159</v>
+        <v>-0.2323</v>
       </c>
       <c r="J135" t="n">
-        <v>-5.6134</v>
+        <v>-6.0398</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.78</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2457</v>
+        <v>-0.2618</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.3882</v>
+        <v>-6.8068</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.51</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1609</v>
+        <v>1.1239</v>
       </c>
       <c r="J137" t="n">
-        <v>30.1834</v>
+        <v>29.2214</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.31</v>
       </c>
       <c r="I138" t="n">
-        <v>0.8243</v>
+        <v>0.7785</v>
       </c>
       <c r="J138" t="n">
-        <v>21.4318</v>
+        <v>20.241</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1.18</v>
       </c>
       <c r="I139" t="n">
-        <v>0.5159</v>
+        <v>0.5043</v>
       </c>
       <c r="J139" t="n">
-        <v>13.4134</v>
+        <v>13.1118</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>1.12</v>
       </c>
       <c r="I140" t="n">
-        <v>0.3636</v>
+        <v>0.3651</v>
       </c>
       <c r="J140" t="n">
-        <v>9.4536</v>
+        <v>9.492599999999999</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.75</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7957</v>
+        <v>-0.7331</v>
       </c>
       <c r="J141" t="n">
-        <v>-20.6882</v>
+        <v>-19.0606</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.11</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2506</v>
+        <v>0.2479</v>
       </c>
       <c r="J142" t="n">
-        <v>6.265</v>
+        <v>6.1975</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.88</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1387</v>
+        <v>-0.1559</v>
       </c>
       <c r="J143" t="n">
-        <v>-3.4675</v>
+        <v>-3.8975</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.83</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1896</v>
+        <v>-0.2075</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.74</v>
+        <v>-5.1875</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.77</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2478</v>
+        <v>-0.2654</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.195</v>
+        <v>-6.635</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.57</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4371</v>
+        <v>-0.4479</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.9275</v>
+        <v>-11.1975</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.57</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>17.5</v>
+        <v>17.4025</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4568</v>
+        <v>0.4681</v>
       </c>
       <c r="J148" t="n">
-        <v>11.42</v>
+        <v>11.7025</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.21</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2936</v>
+        <v>0.3108</v>
       </c>
       <c r="J149" t="n">
-        <v>7.34</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.03</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0427</v>
+        <v>0.0573</v>
       </c>
       <c r="J150" t="n">
-        <v>1.0675</v>
+        <v>1.4325</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.83</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2294</v>
+        <v>-0.2385</v>
       </c>
       <c r="J151" t="n">
-        <v>-5.735</v>
+        <v>-5.9625</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.8</v>
       </c>
       <c r="I152" t="n">
-        <v>1.448</v>
+        <v>1.4406</v>
       </c>
       <c r="J152" t="n">
-        <v>31.856</v>
+        <v>31.6932</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.76</v>
       </c>
       <c r="I153" t="n">
-        <v>1.4021</v>
+        <v>1.392</v>
       </c>
       <c r="J153" t="n">
-        <v>30.8462</v>
+        <v>30.624</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>1.31</v>
       </c>
       <c r="I154" t="n">
-        <v>0.7683</v>
+        <v>0.7401</v>
       </c>
       <c r="J154" t="n">
-        <v>16.9026</v>
+        <v>16.2822</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>1.25</v>
       </c>
       <c r="I155" t="n">
-        <v>0.6299</v>
+        <v>0.6178</v>
       </c>
       <c r="J155" t="n">
-        <v>13.8578</v>
+        <v>13.5916</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>1.14</v>
       </c>
       <c r="I156" t="n">
-        <v>0.3554</v>
+        <v>0.3711</v>
       </c>
       <c r="J156" t="n">
-        <v>7.8188</v>
+        <v>8.164199999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>0.77</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.2259</v>
+        <v>-0.2487</v>
       </c>
       <c r="J157" t="n">
-        <v>-4.9698</v>
+        <v>-5.4714</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>0.73</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2661</v>
+        <v>-0.2877</v>
       </c>
       <c r="J158" t="n">
-        <v>-5.8542</v>
+        <v>-6.3294</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>0.67</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3213</v>
+        <v>-0.3414</v>
       </c>
       <c r="J159" t="n">
-        <v>-7.0686</v>
+        <v>-7.5108</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>0.64</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3483</v>
+        <v>-0.3675</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.6626</v>
+        <v>-8.085000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.57</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4132</v>
+        <v>-0.4292</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.090400000000001</v>
+        <v>-9.442399999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.42</v>
       </c>
       <c r="I162" t="n">
-        <v>1.0208</v>
+        <v>0.9697</v>
       </c>
       <c r="J162" t="n">
-        <v>25.52</v>
+        <v>24.2425</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.41</v>
       </c>
       <c r="I163" t="n">
-        <v>1.005</v>
+        <v>0.9522</v>
       </c>
       <c r="J163" t="n">
-        <v>25.125</v>
+        <v>23.805</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.34</v>
       </c>
       <c r="I164" t="n">
-        <v>0.866</v>
+        <v>0.82</v>
       </c>
       <c r="J164" t="n">
-        <v>21.65</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.27</v>
       </c>
       <c r="I165" t="n">
-        <v>0.7109</v>
+        <v>0.6828</v>
       </c>
       <c r="J165" t="n">
-        <v>17.7725</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>0.91</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3911</v>
+        <v>-0.365</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.7775</v>
+        <v>-9.125</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.04</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1824</v>
+        <v>0.173</v>
       </c>
       <c r="J167" t="n">
-        <v>4.56</v>
+        <v>4.325</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>0.9</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1109</v>
+        <v>-0.129</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.7725</v>
+        <v>-3.225</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1444</v>
+        <v>-0.163</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.61</v>
+        <v>-4.075</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.7</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3102</v>
+        <v>-0.3273</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.755</v>
+        <v>-8.182499999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.48</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5155</v>
+        <v>-0.5226</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.8875</v>
+        <v>-13.065</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.84</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4908</v>
+        <v>1.4863</v>
       </c>
       <c r="J172" t="n">
-        <v>28.3252</v>
+        <v>28.2397</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.61</v>
       </c>
       <c r="I173" t="n">
-        <v>1.2258</v>
+        <v>1.2045</v>
       </c>
       <c r="J173" t="n">
-        <v>23.2902</v>
+        <v>22.8855</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>1.33</v>
       </c>
       <c r="I174" t="n">
-        <v>0.8102</v>
+        <v>0.7775</v>
       </c>
       <c r="J174" t="n">
-        <v>15.3938</v>
+        <v>14.7725</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>1.29</v>
       </c>
       <c r="I175" t="n">
-        <v>0.7201</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="J175" t="n">
-        <v>13.6819</v>
+        <v>13.2639</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>1.26</v>
       </c>
       <c r="I176" t="n">
-        <v>0.6506</v>
+        <v>0.6367</v>
       </c>
       <c r="J176" t="n">
-        <v>12.3614</v>
+        <v>12.0973</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>0.8</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1796</v>
+        <v>-0.2064</v>
       </c>
       <c r="J177" t="n">
-        <v>-3.4124</v>
+        <v>-3.9216</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>0.75</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2336</v>
+        <v>-0.2586</v>
       </c>
       <c r="J178" t="n">
-        <v>-4.4384</v>
+        <v>-4.9134</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.73</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2544</v>
+        <v>-0.2786</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.8336</v>
+        <v>-5.2934</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.55</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4227</v>
+        <v>-0.4397</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.0313</v>
+        <v>-8.3543</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.29</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6691</v>
+        <v>-0.668</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.7129</v>
+        <v>-12.692</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.33</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4998</v>
+        <v>0.4956</v>
       </c>
       <c r="J182" t="n">
-        <v>14.4942</v>
+        <v>14.3724</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.14</v>
       </c>
       <c r="I183" t="n">
-        <v>0.241</v>
+        <v>0.2508</v>
       </c>
       <c r="J183" t="n">
-        <v>6.989</v>
+        <v>7.2732</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.11</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1965</v>
+        <v>0.2074</v>
       </c>
       <c r="J184" t="n">
-        <v>5.6985</v>
+        <v>6.0146</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>0.84</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2031</v>
+        <v>-0.2156</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.8899</v>
+        <v>-6.2524</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.79</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2538</v>
+        <v>-0.266</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.3602</v>
+        <v>-7.714</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.324</v>
+        <v>0.3364</v>
       </c>
       <c r="J187" t="n">
-        <v>9.396000000000001</v>
+        <v>9.755599999999999</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.19</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2858</v>
+        <v>0.2993</v>
       </c>
       <c r="J188" t="n">
-        <v>8.2882</v>
+        <v>8.6797</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>1.16</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2467</v>
+        <v>0.2611</v>
       </c>
       <c r="J189" t="n">
-        <v>7.1543</v>
+        <v>7.5719</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.96</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0701</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.0329</v>
+        <v>-2.2562</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2366</v>
+        <v>-0.2484</v>
       </c>
       <c r="J191" t="n">
-        <v>-6.8614</v>
+        <v>-7.2036</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.71</v>
       </c>
       <c r="I192" t="n">
-        <v>1.3939</v>
+        <v>1.3746</v>
       </c>
       <c r="J192" t="n">
-        <v>36.2414</v>
+        <v>35.7396</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>1.29</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7617</v>
+        <v>0.7266</v>
       </c>
       <c r="J193" t="n">
-        <v>19.8042</v>
+        <v>18.8916</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>1.11</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3221</v>
+        <v>0.3302</v>
       </c>
       <c r="J194" t="n">
-        <v>8.374599999999999</v>
+        <v>8.5852</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>1.07</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2062</v>
+        <v>0.2226</v>
       </c>
       <c r="J195" t="n">
-        <v>5.3612</v>
+        <v>5.7876</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>1</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.0575</v>
+        <v>-0.0398</v>
       </c>
       <c r="J196" t="n">
-        <v>-1.495</v>
+        <v>-1.0348</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.14</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3797</v>
+        <v>0.3676</v>
       </c>
       <c r="J197" t="n">
-        <v>9.872199999999999</v>
+        <v>9.557600000000001</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.08</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2521</v>
+        <v>0.2468</v>
       </c>
       <c r="J198" t="n">
-        <v>6.5546</v>
+        <v>6.4168</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>0.93</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0851</v>
+        <v>-0.1001</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.2126</v>
+        <v>-2.6026</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4492</v>
+        <v>-0.459</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.6792</v>
+        <v>-11.934</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4492</v>
+        <v>-0.459</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.6792</v>
+        <v>-11.934</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>0.93</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0381</v>
+        <v>-0.0633</v>
       </c>
       <c r="J202" t="n">
-        <v>-0.8001</v>
+        <v>-1.3293</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.91</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0639</v>
+        <v>-0.0895</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.3419</v>
+        <v>-1.8795</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.59</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3925</v>
+        <v>-0.41</v>
       </c>
       <c r="J204" t="n">
-        <v>-8.2425</v>
+        <v>-8.609999999999999</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.49</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4861</v>
+        <v>-0.4981</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.2081</v>
+        <v>-10.4601</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.4</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5708</v>
+        <v>-0.5768</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.9868</v>
+        <v>-12.1128</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.72</v>
       </c>
       <c r="I207" t="n">
-        <v>1.3546</v>
+        <v>1.3419</v>
       </c>
       <c r="J207" t="n">
-        <v>28.4466</v>
+        <v>28.1799</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.53</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1325</v>
+        <v>1.1039</v>
       </c>
       <c r="J208" t="n">
-        <v>23.7825</v>
+        <v>23.1819</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>1.44</v>
       </c>
       <c r="I209" t="n">
-        <v>1.0237</v>
+        <v>0.9792</v>
       </c>
       <c r="J209" t="n">
-        <v>21.4977</v>
+        <v>20.5632</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>1.35</v>
       </c>
       <c r="I210" t="n">
-        <v>0.8555</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="J210" t="n">
-        <v>17.9655</v>
+        <v>17.157</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>1.26</v>
       </c>
       <c r="I211" t="n">
-        <v>0.6518</v>
+        <v>0.6375</v>
       </c>
       <c r="J211" t="n">
-        <v>13.6878</v>
+        <v>13.3875</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>0.73</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.2246</v>
+        <v>-0.2552</v>
       </c>
       <c r="J212" t="n">
-        <v>-3.8182</v>
+        <v>-4.3384</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>0.65</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.3109</v>
+        <v>-0.3368</v>
       </c>
       <c r="J213" t="n">
-        <v>-5.2853</v>
+        <v>-5.7256</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.47</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4802</v>
+        <v>-0.4963</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.163399999999999</v>
+        <v>-8.437099999999999</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.43</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5183</v>
+        <v>-0.5316</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.8111</v>
+        <v>-9.0372</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.4</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5473</v>
+        <v>-0.5583</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.3041</v>
+        <v>-9.491099999999999</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>2.27</v>
       </c>
       <c r="I217" t="n">
-        <v>1.8338</v>
+        <v>1.9254</v>
       </c>
       <c r="J217" t="n">
-        <v>31.1746</v>
+        <v>32.7318</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.84</v>
       </c>
       <c r="I218" t="n">
-        <v>1.4493</v>
+        <v>1.4499</v>
       </c>
       <c r="J218" t="n">
-        <v>24.6381</v>
+        <v>24.6483</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>1.59</v>
       </c>
       <c r="I219" t="n">
-        <v>1.1768</v>
+        <v>1.1575</v>
       </c>
       <c r="J219" t="n">
-        <v>20.0056</v>
+        <v>19.6775</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>1.54</v>
       </c>
       <c r="I220" t="n">
-        <v>1.1185</v>
+        <v>1.0944</v>
       </c>
       <c r="J220" t="n">
-        <v>19.0145</v>
+        <v>18.6048</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>1.49</v>
       </c>
       <c r="I221" t="n">
-        <v>1.0586</v>
+        <v>1.027</v>
       </c>
       <c r="J221" t="n">
-        <v>17.9962</v>
+        <v>17.459</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.04</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1565</v>
+        <v>0.154</v>
       </c>
       <c r="J222" t="n">
-        <v>4.2255</v>
+        <v>4.158</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>0.95</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0609</v>
+        <v>-0.0746</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.6443</v>
+        <v>-2.0142</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>0.93</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0857</v>
+        <v>-0.1006</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.3139</v>
+        <v>-2.7162</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.73</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2899</v>
+        <v>-0.3059</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.8273</v>
+        <v>-8.2593</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.64</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3753</v>
+        <v>-0.3885</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.1331</v>
+        <v>-10.4895</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.6</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2606</v>
+        <v>1.2329</v>
       </c>
       <c r="J227" t="n">
-        <v>34.0362</v>
+        <v>33.2883</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>1.47</v>
       </c>
       <c r="I228" t="n">
-        <v>1.0966</v>
+        <v>1.0566</v>
       </c>
       <c r="J228" t="n">
-        <v>29.6082</v>
+        <v>28.5282</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>1.14</v>
       </c>
       <c r="I229" t="n">
-        <v>0.405</v>
+        <v>0.4057</v>
       </c>
       <c r="J229" t="n">
-        <v>10.935</v>
+        <v>10.9539</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.97</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.189</v>
+        <v>-0.1764</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.103</v>
+        <v>-4.7628</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.96</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.224</v>
+        <v>-0.2102</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.048</v>
+        <v>-5.6754</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>1.05</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2968</v>
+        <v>0.2638</v>
       </c>
       <c r="J232" t="n">
-        <v>5.936</v>
+        <v>5.276</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>0.88</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.1253</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.99</v>
+        <v>-2.506</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>0.53</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.4479</v>
+        <v>-0.4623</v>
       </c>
       <c r="J234" t="n">
-        <v>-8.958</v>
+        <v>-9.246</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>0.47</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5042</v>
+        <v>-0.5151</v>
       </c>
       <c r="J235" t="n">
-        <v>-10.084</v>
+        <v>-10.302</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.37</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5984</v>
+        <v>-0.6024</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.968</v>
+        <v>-12.048</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.72</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3546</v>
+        <v>1.3419</v>
       </c>
       <c r="J237" t="n">
-        <v>27.092</v>
+        <v>26.838</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.71</v>
       </c>
       <c r="I238" t="n">
-        <v>1.343</v>
+        <v>1.3296</v>
       </c>
       <c r="J238" t="n">
-        <v>26.86</v>
+        <v>26.592</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>1.53</v>
       </c>
       <c r="I239" t="n">
-        <v>1.1325</v>
+        <v>1.1039</v>
       </c>
       <c r="J239" t="n">
-        <v>22.65</v>
+        <v>22.078</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>1.35</v>
       </c>
       <c r="I240" t="n">
-        <v>0.8555</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="J240" t="n">
-        <v>17.11</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.99</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.162</v>
+        <v>-0.1344</v>
       </c>
       <c r="J241" t="n">
-        <v>-3.24</v>
+        <v>-2.688</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.31</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4178</v>
+        <v>0.4296</v>
       </c>
       <c r="J242" t="n">
-        <v>11.2806</v>
+        <v>11.5992</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3706</v>
+        <v>0.3843</v>
       </c>
       <c r="J243" t="n">
-        <v>10.0062</v>
+        <v>10.3761</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>1.21</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2981</v>
+        <v>0.3142</v>
       </c>
       <c r="J244" t="n">
-        <v>8.0487</v>
+        <v>8.4834</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>1.08</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1286</v>
+        <v>0.145</v>
       </c>
       <c r="J245" t="n">
-        <v>3.4722</v>
+        <v>3.915</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.9</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1507</v>
+        <v>-0.1598</v>
       </c>
       <c r="J246" t="n">
-        <v>-4.0689</v>
+        <v>-4.3146</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>1.07</v>
       </c>
       <c r="I247" t="n">
-        <v>0.1547</v>
+        <v>0.1606</v>
       </c>
       <c r="J247" t="n">
-        <v>4.1769</v>
+        <v>4.3362</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1</v>
       </c>
       <c r="I248" t="n">
-        <v>0.0098</v>
+        <v>0.0072</v>
       </c>
       <c r="J248" t="n">
-        <v>0.2646</v>
+        <v>0.1944</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.88</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1483</v>
+        <v>-0.1632</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.0041</v>
+        <v>-4.4064</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.86</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1694</v>
+        <v>-0.1846</v>
       </c>
       <c r="J250" t="n">
-        <v>-4.5738</v>
+        <v>-4.9842</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.84</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.1901</v>
+        <v>-0.2055</v>
       </c>
       <c r="J251" t="n">
-        <v>-5.1327</v>
+        <v>-5.5485</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.16</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3921</v>
+        <v>0.3846</v>
       </c>
       <c r="J252" t="n">
-        <v>10.5867</v>
+        <v>10.3842</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.11</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2916</v>
+        <v>0.2901</v>
       </c>
       <c r="J253" t="n">
-        <v>7.8732</v>
+        <v>7.8327</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>0.96</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0563</v>
+        <v>-0.0673</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.5201</v>
+        <v>-1.8171</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>0.84</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1887</v>
+        <v>-0.2044</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.0949</v>
+        <v>-5.5188</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.52</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4933</v>
+        <v>-0.4995</v>
       </c>
       <c r="J256" t="n">
-        <v>-13.3191</v>
+        <v>-13.4865</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.27</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7466</v>
+        <v>0.7073</v>
       </c>
       <c r="J257" t="n">
-        <v>20.1582</v>
+        <v>19.0971</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>1.27</v>
       </c>
       <c r="I258" t="n">
-        <v>0.7466</v>
+        <v>0.7073</v>
       </c>
       <c r="J258" t="n">
-        <v>20.1582</v>
+        <v>19.0971</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>1.19</v>
       </c>
       <c r="I259" t="n">
-        <v>0.5511</v>
+        <v>0.5337</v>
       </c>
       <c r="J259" t="n">
-        <v>14.8797</v>
+        <v>14.4099</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>1.15</v>
       </c>
       <c r="I260" t="n">
-        <v>0.45</v>
+        <v>0.4423</v>
       </c>
       <c r="J260" t="n">
-        <v>12.15</v>
+        <v>11.9421</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.8084</v>
+        <v>-0.7464</v>
       </c>
       <c r="J261" t="n">
-        <v>-21.8268</v>
+        <v>-20.1528</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.19</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4091</v>
+        <v>0.4084</v>
       </c>
       <c r="J262" t="n">
-        <v>16.7731</v>
+        <v>16.7444</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.06</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1548</v>
+        <v>0.1651</v>
       </c>
       <c r="J263" t="n">
-        <v>6.3468</v>
+        <v>6.7691</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.01</v>
       </c>
       <c r="I264" t="n">
-        <v>0.0331</v>
+        <v>0.0401</v>
       </c>
       <c r="J264" t="n">
-        <v>1.3571</v>
+        <v>1.6441</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.97</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0537</v>
+        <v>-0.061</v>
       </c>
       <c r="J265" t="n">
-        <v>-2.2017</v>
+        <v>-2.501</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.96</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.067</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="J266" t="n">
-        <v>-2.747</v>
+        <v>-3.0914</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.48</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1508</v>
+        <v>1.1076</v>
       </c>
       <c r="J267" t="n">
-        <v>47.1828</v>
+        <v>45.4116</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.21</v>
       </c>
       <c r="I268" t="n">
-        <v>0.6162</v>
+        <v>0.5888</v>
       </c>
       <c r="J268" t="n">
-        <v>25.2642</v>
+        <v>24.1408</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>1.02</v>
       </c>
       <c r="I269" t="n">
-        <v>0.0785</v>
+        <v>0.0893</v>
       </c>
       <c r="J269" t="n">
-        <v>3.2185</v>
+        <v>3.6613</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.86</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4833</v>
+        <v>-0.4597</v>
       </c>
       <c r="J270" t="n">
-        <v>-19.8153</v>
+        <v>-18.8477</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6171</v>
+        <v>-0.5797</v>
       </c>
       <c r="J271" t="n">
-        <v>-25.3011</v>
+        <v>-23.7677</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>1.36</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6694</v>
+        <v>0.6532</v>
       </c>
       <c r="J272" t="n">
-        <v>20.082</v>
+        <v>19.596</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>1.22</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4366</v>
+        <v>0.4394</v>
       </c>
       <c r="J273" t="n">
-        <v>13.098</v>
+        <v>13.182</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>1.14</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2972</v>
+        <v>0.3075</v>
       </c>
       <c r="J274" t="n">
-        <v>8.916</v>
+        <v>9.225</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>1.12</v>
       </c>
       <c r="I275" t="n">
-        <v>0.2603</v>
+        <v>0.2721</v>
       </c>
       <c r="J275" t="n">
-        <v>7.809</v>
+        <v>8.163</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.91</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.1391</v>
+        <v>-0.1479</v>
       </c>
       <c r="J276" t="n">
-        <v>-4.173</v>
+        <v>-4.437</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.15</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5482</v>
+        <v>0.5108</v>
       </c>
       <c r="J277" t="n">
-        <v>16.446</v>
+        <v>15.324</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>0.96</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.1339</v>
+        <v>-0.148</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.017</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>0.89</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3472</v>
+        <v>-0.3474</v>
       </c>
       <c r="J279" t="n">
-        <v>-10.416</v>
+        <v>-10.422</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.83</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5057</v>
+        <v>-0.4918</v>
       </c>
       <c r="J280" t="n">
-        <v>-15.171</v>
+        <v>-14.754</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.58</v>
       </c>
       <c r="I281" t="n">
-        <v>-1.1285</v>
+        <v>-1.0338</v>
       </c>
       <c r="J281" t="n">
-        <v>-33.855</v>
+        <v>-31.014</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>0.89</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.0675</v>
+        <v>-0.0975</v>
       </c>
       <c r="J282" t="n">
-        <v>-1.35</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>0.76</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.2182</v>
+        <v>-0.2446</v>
       </c>
       <c r="J283" t="n">
-        <v>-4.364</v>
+        <v>-4.892</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.68</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3008</v>
+        <v>-0.3239</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.016</v>
+        <v>-6.478</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.42</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.5423</v>
+        <v>-0.5518</v>
       </c>
       <c r="J285" t="n">
-        <v>-10.846</v>
+        <v>-11.036</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.29</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6669</v>
+        <v>-0.6663</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.338</v>
+        <v>-13.326</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.99</v>
       </c>
       <c r="I287" t="n">
-        <v>1.6398</v>
+        <v>1.6459</v>
       </c>
       <c r="J287" t="n">
-        <v>32.796</v>
+        <v>32.918</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.59</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1922</v>
+        <v>1.1706</v>
       </c>
       <c r="J288" t="n">
-        <v>23.844</v>
+        <v>23.412</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.49</v>
       </c>
       <c r="I289" t="n">
-        <v>1.0778</v>
+        <v>1.045</v>
       </c>
       <c r="J289" t="n">
-        <v>21.556</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>1.38</v>
       </c>
       <c r="I290" t="n">
-        <v>0.9019</v>
+        <v>0.8613</v>
       </c>
       <c r="J290" t="n">
-        <v>18.038</v>
+        <v>17.226</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>1.34</v>
       </c>
       <c r="I291" t="n">
-        <v>0.8146</v>
+        <v>0.7846</v>
       </c>
       <c r="J291" t="n">
-        <v>16.292</v>
+        <v>15.692</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.1</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3242</v>
+        <v>0.3003</v>
       </c>
       <c r="J292" t="n">
-        <v>6.484</v>
+        <v>6.006</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>0.73</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.262</v>
+        <v>-0.2846</v>
       </c>
       <c r="J293" t="n">
-        <v>-5.24</v>
+        <v>-5.692</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.61</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.3727</v>
+        <v>-0.3914</v>
       </c>
       <c r="J294" t="n">
-        <v>-7.454</v>
+        <v>-7.828</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.54</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4378</v>
+        <v>-0.453</v>
       </c>
       <c r="J295" t="n">
-        <v>-8.756</v>
+        <v>-9.06</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.3</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6639</v>
+        <v>-0.6627</v>
       </c>
       <c r="J296" t="n">
-        <v>-13.278</v>
+        <v>-13.254</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>2.27</v>
       </c>
       <c r="I297" t="n">
-        <v>1.198</v>
+        <v>1.2102</v>
       </c>
       <c r="J297" t="n">
-        <v>23.96</v>
+        <v>24.204</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.48</v>
       </c>
       <c r="I298" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5784</v>
       </c>
       <c r="J298" t="n">
-        <v>11.34</v>
+        <v>11.568</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.31</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3874</v>
+        <v>0.4068</v>
       </c>
       <c r="J299" t="n">
-        <v>7.748</v>
+        <v>8.135999999999999</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>1.16</v>
       </c>
       <c r="I300" t="n">
-        <v>0.2062</v>
+        <v>0.2305</v>
       </c>
       <c r="J300" t="n">
-        <v>4.124</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.99</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.0609</v>
+        <v>-0.0567</v>
       </c>
       <c r="J301" t="n">
-        <v>-1.218</v>
+        <v>-1.134</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>1.87</v>
       </c>
       <c r="I302" t="n">
-        <v>1.5142</v>
+        <v>1.5127</v>
       </c>
       <c r="J302" t="n">
-        <v>28.7698</v>
+        <v>28.7413</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>1.6</v>
       </c>
       <c r="I303" t="n">
-        <v>1.2073</v>
+        <v>1.1862</v>
       </c>
       <c r="J303" t="n">
-        <v>22.9387</v>
+        <v>22.5378</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>1.41</v>
       </c>
       <c r="I304" t="n">
-        <v>0.9678</v>
+        <v>0.9217</v>
       </c>
       <c r="J304" t="n">
-        <v>18.3882</v>
+        <v>17.5123</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>1.39</v>
       </c>
       <c r="I305" t="n">
-        <v>0.9295</v>
+        <v>0.885</v>
       </c>
       <c r="J305" t="n">
-        <v>17.6605</v>
+        <v>16.815</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>1.33</v>
       </c>
       <c r="I306" t="n">
-        <v>0.7997</v>
+        <v>0.7702</v>
       </c>
       <c r="J306" t="n">
-        <v>15.1943</v>
+        <v>14.6338</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>1.11</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4831</v>
+        <v>0.432</v>
       </c>
       <c r="J307" t="n">
-        <v>9.178900000000001</v>
+        <v>8.208</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>0.67</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.3132</v>
+        <v>-0.3352</v>
       </c>
       <c r="J308" t="n">
-        <v>-5.9508</v>
+        <v>-6.3688</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>0.63</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.3503</v>
+        <v>-0.3708</v>
       </c>
       <c r="J309" t="n">
-        <v>-6.6557</v>
+        <v>-7.0452</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>0.35</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.6112</v>
+        <v>-0.615</v>
       </c>
       <c r="J310" t="n">
-        <v>-11.6128</v>
+        <v>-11.685</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.34</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6208</v>
+        <v>-0.6238</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.7952</v>
+        <v>-11.8522</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.77</v>
       </c>
       <c r="I312" t="n">
-        <v>1.3963</v>
+        <v>1.389</v>
       </c>
       <c r="J312" t="n">
-        <v>26.5297</v>
+        <v>26.391</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.74</v>
       </c>
       <c r="I313" t="n">
-        <v>1.3625</v>
+        <v>1.3531</v>
       </c>
       <c r="J313" t="n">
-        <v>25.8875</v>
+        <v>25.7089</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>1.62</v>
       </c>
       <c r="I314" t="n">
-        <v>1.2266</v>
+        <v>1.2076</v>
       </c>
       <c r="J314" t="n">
-        <v>23.3054</v>
+        <v>22.9444</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>1.42</v>
       </c>
       <c r="I315" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9354</v>
       </c>
       <c r="J315" t="n">
-        <v>18.6257</v>
+        <v>17.7726</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>1.22</v>
       </c>
       <c r="I316" t="n">
-        <v>0.5376</v>
+        <v>0.5394</v>
       </c>
       <c r="J316" t="n">
-        <v>10.2144</v>
+        <v>10.2486</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>0.82</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.1378</v>
+        <v>-0.1693</v>
       </c>
       <c r="J317" t="n">
-        <v>-2.6182</v>
+        <v>-3.2167</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>0.73</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.2392</v>
+        <v>-0.2668</v>
       </c>
       <c r="J318" t="n">
-        <v>-4.5448</v>
+        <v>-5.0692</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>0.6</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.3701</v>
+        <v>-0.3911</v>
       </c>
       <c r="J319" t="n">
-        <v>-7.0319</v>
+        <v>-7.4309</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>0.42</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.5467</v>
       </c>
       <c r="J320" t="n">
-        <v>-10.1802</v>
+        <v>-10.3873</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.3</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.652</v>
+        <v>-0.6533</v>
       </c>
       <c r="J321" t="n">
-        <v>-12.388</v>
+        <v>-12.4127</v>
       </c>
     </row>
     <row r="322">
@@ -15275,10 +15275,10 @@
         <v>1.44</v>
       </c>
       <c r="I322" t="n">
-        <v>1.0622</v>
+        <v>1.0154</v>
       </c>
       <c r="J322" t="n">
-        <v>25.4928</v>
+        <v>24.3696</v>
       </c>
     </row>
     <row r="323">
@@ -15315,10 +15315,10 @@
         <v>1.37</v>
       </c>
       <c r="I323" t="n">
-        <v>0.9474</v>
+        <v>0.8902</v>
       </c>
       <c r="J323" t="n">
-        <v>22.7376</v>
+        <v>21.3648</v>
       </c>
     </row>
     <row r="324">
@@ -15355,10 +15355,10 @@
         <v>1.12</v>
       </c>
       <c r="I324" t="n">
-        <v>0.356</v>
+        <v>0.3599</v>
       </c>
       <c r="J324" t="n">
-        <v>8.544</v>
+        <v>8.637600000000001</v>
       </c>
     </row>
     <row r="325">
@@ -15395,10 +15395,10 @@
         <v>1.08</v>
       </c>
       <c r="I325" t="n">
-        <v>0.2429</v>
+        <v>0.2553</v>
       </c>
       <c r="J325" t="n">
-        <v>5.8296</v>
+        <v>6.1272</v>
       </c>
     </row>
     <row r="326">
@@ -15435,10 +15435,10 @@
         <v>1.03</v>
       </c>
       <c r="I326" t="n">
-        <v>0.0825</v>
+        <v>0.1028</v>
       </c>
       <c r="J326" t="n">
-        <v>1.98</v>
+        <v>2.4672</v>
       </c>
     </row>
     <row r="327">
@@ -15475,10 +15475,10 @@
         <v>1.26</v>
       </c>
       <c r="I327" t="n">
-        <v>0.6089</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="J327" t="n">
-        <v>14.6136</v>
+        <v>13.8984</v>
       </c>
     </row>
     <row r="328">
@@ -15515,10 +15515,10 @@
         <v>1.03</v>
       </c>
       <c r="I328" t="n">
-        <v>0.1294</v>
+        <v>0.1273</v>
       </c>
       <c r="J328" t="n">
-        <v>3.1056</v>
+        <v>3.0552</v>
       </c>
     </row>
     <row r="329">
@@ -15555,10 +15555,10 @@
         <v>0.72</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3</v>
+        <v>-0.3157</v>
       </c>
       <c r="J329" t="n">
-        <v>-7.2</v>
+        <v>-7.5768</v>
       </c>
     </row>
     <row r="330">
@@ -15595,10 +15595,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3287</v>
+        <v>-0.3435</v>
       </c>
       <c r="J330" t="n">
-        <v>-7.8888</v>
+        <v>-8.244</v>
       </c>
     </row>
     <row r="331">
@@ -15635,10 +15635,10 @@
         <v>0.61</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4039</v>
+        <v>-0.4157</v>
       </c>
       <c r="J331" t="n">
-        <v>-9.6936</v>
+        <v>-9.976800000000001</v>
       </c>
     </row>
     <row r="332">
@@ -15675,10 +15675,10 @@
         <v>1.99</v>
       </c>
       <c r="I332" t="n">
-        <v>1.6671</v>
+        <v>1.6701</v>
       </c>
       <c r="J332" t="n">
-        <v>35.0091</v>
+        <v>35.0721</v>
       </c>
     </row>
     <row r="333">
@@ -15715,10 +15715,10 @@
         <v>1.64</v>
       </c>
       <c r="I333" t="n">
-        <v>1.2655</v>
+        <v>1.2462</v>
       </c>
       <c r="J333" t="n">
-        <v>26.5755</v>
+        <v>26.1702</v>
       </c>
     </row>
     <row r="334">
@@ -15755,10 +15755,10 @@
         <v>1.44</v>
       </c>
       <c r="I334" t="n">
-        <v>1.0254</v>
+        <v>0.9807</v>
       </c>
       <c r="J334" t="n">
-        <v>21.5334</v>
+        <v>20.5947</v>
       </c>
     </row>
     <row r="335">
@@ -15795,10 +15795,10 @@
         <v>1.28</v>
       </c>
       <c r="I335" t="n">
-        <v>0.7032</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="J335" t="n">
-        <v>14.7672</v>
+        <v>14.322</v>
       </c>
     </row>
     <row r="336">
@@ -15835,10 +15835,10 @@
         <v>0.83</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.6464</v>
+        <v>-0.5904</v>
       </c>
       <c r="J336" t="n">
-        <v>-13.5744</v>
+        <v>-12.3984</v>
       </c>
     </row>
     <row r="337">
@@ -15875,10 +15875,10 @@
         <v>1.05</v>
       </c>
       <c r="I337" t="n">
-        <v>0.2823</v>
+        <v>0.253</v>
       </c>
       <c r="J337" t="n">
-        <v>5.9283</v>
+        <v>5.313</v>
       </c>
     </row>
     <row r="338">
@@ -15915,10 +15915,10 @@
         <v>0.95</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.016</v>
+        <v>-0.0394</v>
       </c>
       <c r="J338" t="n">
-        <v>-0.336</v>
+        <v>-0.8274</v>
       </c>
     </row>
     <row r="339">
@@ -15955,10 +15955,10 @@
         <v>0.49</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.4885</v>
+        <v>-0.4999</v>
       </c>
       <c r="J339" t="n">
-        <v>-10.2585</v>
+        <v>-10.4979</v>
       </c>
     </row>
     <row r="340">
@@ -15995,10 +15995,10 @@
         <v>0.47</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.5073</v>
+        <v>-0.5175</v>
       </c>
       <c r="J340" t="n">
-        <v>-10.6533</v>
+        <v>-10.8675</v>
       </c>
     </row>
     <row r="341">
@@ -16035,10 +16035,10 @@
         <v>0.43</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5448</v>
+        <v>-0.5524</v>
       </c>
       <c r="J341" t="n">
-        <v>-11.4408</v>
+        <v>-11.6004</v>
       </c>
     </row>
     <row r="342">
@@ -16075,10 +16075,10 @@
         <v>1.63</v>
       </c>
       <c r="I342" t="n">
-        <v>1.3439</v>
+        <v>1.3134</v>
       </c>
       <c r="J342" t="n">
-        <v>37.6292</v>
+        <v>36.7752</v>
       </c>
     </row>
     <row r="343">
@@ -16115,10 +16115,10 @@
         <v>1.09</v>
       </c>
       <c r="I343" t="n">
-        <v>0.2976</v>
+        <v>0.2999</v>
       </c>
       <c r="J343" t="n">
-        <v>8.332800000000001</v>
+        <v>8.3972</v>
       </c>
     </row>
     <row r="344">
@@ -16155,10 +16155,10 @@
         <v>1.02</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0761</v>
+        <v>0.0876</v>
       </c>
       <c r="J344" t="n">
-        <v>2.1308</v>
+        <v>2.4528</v>
       </c>
     </row>
     <row r="345">
@@ -16195,10 +16195,10 @@
         <v>0.99</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.074</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="J345" t="n">
-        <v>-2.072</v>
+        <v>-2.0412</v>
       </c>
     </row>
     <row r="346">
@@ -16235,10 +16235,10 @@
         <v>0.7</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.8974</v>
+        <v>-0.8258</v>
       </c>
       <c r="J346" t="n">
-        <v>-25.1272</v>
+        <v>-23.1224</v>
       </c>
     </row>
     <row r="347">
@@ -16275,10 +16275,10 @@
         <v>1.14</v>
       </c>
       <c r="I347" t="n">
-        <v>0.328</v>
+        <v>0.3297</v>
       </c>
       <c r="J347" t="n">
-        <v>9.183999999999999</v>
+        <v>9.2316</v>
       </c>
     </row>
     <row r="348">
@@ -16315,10 +16315,10 @@
         <v>1.05</v>
       </c>
       <c r="I348" t="n">
-        <v>0.141</v>
+        <v>0.1491</v>
       </c>
       <c r="J348" t="n">
-        <v>3.948</v>
+        <v>4.1748</v>
       </c>
     </row>
     <row r="349">
@@ -16355,10 +16355,10 @@
         <v>0.98</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.0354</v>
+        <v>-0.0422</v>
       </c>
       <c r="J349" t="n">
-        <v>-0.9912</v>
+        <v>-1.1816</v>
       </c>
     </row>
     <row r="350">
@@ -16395,10 +16395,10 @@
         <v>0.9</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.1334</v>
+        <v>-0.1463</v>
       </c>
       <c r="J350" t="n">
-        <v>-3.7352</v>
+        <v>-4.0964</v>
       </c>
     </row>
     <row r="351">
@@ -16435,10 +16435,10 @@
         <v>0.89</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.1444</v>
+        <v>-0.1575</v>
       </c>
       <c r="J351" t="n">
-        <v>-4.0432</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="352">
@@ -16475,10 +16475,10 @@
         <v>2.03</v>
       </c>
       <c r="I352" t="n">
-        <v>1.6845</v>
+        <v>1.6925</v>
       </c>
       <c r="J352" t="n">
-        <v>28.6365</v>
+        <v>28.7725</v>
       </c>
     </row>
     <row r="353">
@@ -16515,10 +16515,10 @@
         <v>1.63</v>
       </c>
       <c r="I353" t="n">
-        <v>1.2379</v>
+        <v>1.2199</v>
       </c>
       <c r="J353" t="n">
-        <v>21.0443</v>
+        <v>20.7383</v>
       </c>
     </row>
     <row r="354">
@@ -16555,10 +16555,10 @@
         <v>1.53</v>
       </c>
       <c r="I354" t="n">
-        <v>1.1249</v>
+        <v>1.0975</v>
       </c>
       <c r="J354" t="n">
-        <v>19.1233</v>
+        <v>18.6575</v>
       </c>
     </row>
     <row r="355">
@@ -16595,10 +16595,10 @@
         <v>1.37</v>
       </c>
       <c r="I355" t="n">
-        <v>0.8812</v>
+        <v>0.8428</v>
       </c>
       <c r="J355" t="n">
-        <v>14.9804</v>
+        <v>14.3276</v>
       </c>
     </row>
     <row r="356">
@@ -16635,10 +16635,10 @@
         <v>1.21</v>
       </c>
       <c r="I356" t="n">
-        <v>0.5132</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J356" t="n">
-        <v>8.724399999999999</v>
+        <v>8.799200000000001</v>
       </c>
     </row>
     <row r="357">
@@ -16675,10 +16675,10 @@
         <v>0.83</v>
       </c>
       <c r="I357" t="n">
-        <v>-0.1399</v>
+        <v>-0.1688</v>
       </c>
       <c r="J357" t="n">
-        <v>-2.3783</v>
+        <v>-2.8696</v>
       </c>
     </row>
     <row r="358">
@@ -16715,10 +16715,10 @@
         <v>0.74</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.2395</v>
+        <v>-0.2651</v>
       </c>
       <c r="J358" t="n">
-        <v>-4.0715</v>
+        <v>-4.5067</v>
       </c>
     </row>
     <row r="359">
@@ -16755,10 +16755,10 @@
         <v>0.61</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.3662</v>
+        <v>-0.3864</v>
       </c>
       <c r="J359" t="n">
-        <v>-6.2254</v>
+        <v>-6.5688</v>
       </c>
     </row>
     <row r="360">
@@ -16795,10 +16795,10 @@
         <v>0.55</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.4198</v>
+        <v>-0.4374</v>
       </c>
       <c r="J360" t="n">
-        <v>-7.1366</v>
+        <v>-7.4358</v>
       </c>
     </row>
     <row r="361">
@@ -16835,10 +16835,10 @@
         <v>0.31</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.6476</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="J361" t="n">
-        <v>-11.0092</v>
+        <v>-11.0279</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4979/event_4979_evp_summary.xlsx
+++ b/database/event/4979/event_4979_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.938599999999999</v>
+        <v>9.0261</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0623</v>
+        <v>2.0825</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4448</v>
+        <v>3.506</v>
       </c>
       <c r="E2" t="n">
-        <v>8.938599999999999</v>
+        <v>9.0261</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5807</v>
+        <v>4.605</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3579</v>
+        <v>4.4211</v>
       </c>
       <c r="H2" t="n">
-        <v>11.4298</v>
+        <v>11.2521</v>
       </c>
       <c r="I2" t="n">
-        <v>6.172</v>
+        <v>6.3177</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3579</v>
+        <v>4.4211</v>
       </c>
       <c r="K2" t="n">
         <v>103</v>
@@ -529,7 +529,7 @@
         <v>144</v>
       </c>
       <c r="M2" t="n">
-        <v>10.5299</v>
+        <v>10.7388</v>
       </c>
       <c r="N2" t="n">
         <v>247</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.3889</v>
+        <v>6.3695</v>
       </c>
       <c r="C3" t="n">
-        <v>1.474</v>
+        <v>1.4696</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2842</v>
+        <v>2.2958</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3889</v>
+        <v>6.3695</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9139</v>
+        <v>2.9019</v>
       </c>
       <c r="G3" t="n">
-        <v>3.475</v>
+        <v>3.4676</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7197</v>
+        <v>4.4524</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5486</v>
+        <v>2.4999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.475</v>
+        <v>3.4676</v>
       </c>
       <c r="K3" t="n">
         <v>103</v>
@@ -575,7 +575,7 @@
         <v>144</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0236</v>
+        <v>5.967499999999999</v>
       </c>
       <c r="N3" t="n">
         <v>247</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6489</v>
+        <v>4.478</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0726</v>
+        <v>1.0332</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4921</v>
+        <v>1.4342</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6489</v>
+        <v>4.478</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7665</v>
+        <v>2.8012</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8824</v>
+        <v>1.6768</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2336</v>
+        <v>4.0741</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2861</v>
+        <v>2.2875</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8824</v>
+        <v>1.6768</v>
       </c>
       <c r="K4" t="n">
         <v>142</v>
@@ -621,7 +621,7 @@
         <v>146</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1685</v>
+        <v>3.9643</v>
       </c>
       <c r="N4" t="n">
         <v>288</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5793</v>
+        <v>4.4411</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0565</v>
+        <v>1.0246</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4604</v>
+        <v>1.4173</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5793</v>
+        <v>4.4411</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6355</v>
+        <v>3.5466</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9438</v>
+        <v>0.8945</v>
       </c>
       <c r="H5" t="n">
-        <v>7.1007</v>
+        <v>6.8729</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8343</v>
+        <v>3.8589</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9438</v>
+        <v>0.8945</v>
       </c>
       <c r="K5" t="n">
         <v>142</v>
@@ -667,7 +667,7 @@
         <v>146</v>
       </c>
       <c r="M5" t="n">
-        <v>4.7781</v>
+        <v>4.7534</v>
       </c>
       <c r="N5" t="n">
         <v>288</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0047</v>
+        <v>3.8643</v>
       </c>
       <c r="C6" t="n">
-        <v>0.924</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1988</v>
+        <v>1.1546</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0047</v>
+        <v>3.8643</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5137</v>
+        <v>2.4741</v>
       </c>
       <c r="G6" t="n">
-        <v>1.491</v>
+        <v>1.3902</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7768</v>
+        <v>2.7198</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9218</v>
+        <v>2.8671</v>
       </c>
       <c r="J6" t="n">
-        <v>1.491</v>
+        <v>1.3902</v>
       </c>
       <c r="K6" t="n">
         <v>155</v>
@@ -713,7 +713,7 @@
         <v>106</v>
       </c>
       <c r="M6" t="n">
-        <v>4.412800000000001</v>
+        <v>4.257300000000001</v>
       </c>
       <c r="N6" t="n">
         <v>261</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7031</v>
+        <v>3.6876</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8544</v>
+        <v>0.8508</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0615</v>
+        <v>1.0741</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7031</v>
+        <v>3.6876</v>
       </c>
       <c r="F7" t="n">
-        <v>2.693</v>
+        <v>2.7473</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0101</v>
+        <v>0.9403</v>
       </c>
       <c r="H7" t="n">
-        <v>3.991</v>
+        <v>3.8718</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1551</v>
+        <v>2.1739</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0101</v>
+        <v>0.9403</v>
       </c>
       <c r="K7" t="n">
         <v>103</v>
@@ -759,7 +759,7 @@
         <v>144</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1652</v>
+        <v>3.1142</v>
       </c>
       <c r="N7" t="n">
         <v>247</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2354</v>
+        <v>3.2198</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.7429</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8486</v>
+        <v>0.861</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2354</v>
+        <v>3.2198</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2652</v>
+        <v>3.2388</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0298</v>
+        <v>-0.019</v>
       </c>
       <c r="H8" t="n">
-        <v>5.8788</v>
+        <v>5.7173</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1745</v>
+        <v>3.2101</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0298</v>
+        <v>-0.019</v>
       </c>
       <c r="K8" t="n">
         <v>103</v>
@@ -805,7 +805,7 @@
         <v>144</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1447</v>
+        <v>3.1911</v>
       </c>
       <c r="N8" t="n">
         <v>247</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1574</v>
+        <v>3.0906</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7285</v>
+        <v>0.7131</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8131</v>
+        <v>0.8021</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1574</v>
+        <v>3.0906</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8777</v>
+        <v>2.8425</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2797</v>
+        <v>0.2481</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5735</v>
+        <v>3.564</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9563</v>
+        <v>3.9605</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2797</v>
+        <v>0.2481</v>
       </c>
       <c r="K9" t="n">
         <v>175</v>
@@ -851,7 +851,7 @@
         <v>56</v>
       </c>
       <c r="M9" t="n">
-        <v>4.236</v>
+        <v>4.208600000000001</v>
       </c>
       <c r="N9" t="n">
         <v>231</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>xsepower</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1113</v>
+        <v>3.0169</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7178</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7921</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1113</v>
+        <v>3.0169</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9965</v>
+        <v>2.7232</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1148</v>
+        <v>0.2938</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8335</v>
+        <v>3.2905</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2442</v>
+        <v>3.5614</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1148</v>
+        <v>0.2938</v>
       </c>
       <c r="K10" t="n">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="L10" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M10" t="n">
-        <v>4.359</v>
+        <v>3.8552</v>
       </c>
       <c r="N10" t="n">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>xsepower</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1016</v>
+        <v>3.0156</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7156</v>
+        <v>0.6958</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7877</v>
+        <v>0.768</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1016</v>
+        <v>3.0156</v>
       </c>
       <c r="F11" t="n">
-        <v>2.795</v>
+        <v>2.9284</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3066</v>
+        <v>0.0872</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3924</v>
+        <v>3.761</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6615</v>
+        <v>4.1794</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3066</v>
+        <v>0.0872</v>
       </c>
       <c r="K11" t="n">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="L11" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9681</v>
+        <v>4.2666</v>
       </c>
       <c r="N11" t="n">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8898</v>
+        <v>2.9375</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6667</v>
+        <v>0.6777</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6913</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8898</v>
+        <v>2.9375</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6752</v>
+        <v>1.717</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2146</v>
+        <v>1.2205</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6752</v>
+        <v>1.717</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7627</v>
+        <v>1.81</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2146</v>
+        <v>1.2205</v>
       </c>
       <c r="K12" t="n">
         <v>155</v>
@@ -989,7 +989,7 @@
         <v>106</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9773</v>
+        <v>3.0305</v>
       </c>
       <c r="N12" t="n">
         <v>261</v>
@@ -998,35 +998,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.726</v>
+        <v>2.6218</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6289</v>
+        <v>0.6049</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6167</v>
+        <v>0.5886</v>
       </c>
       <c r="E13" t="n">
-        <v>2.726</v>
+        <v>2.6218</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1827</v>
+        <v>2.528</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5433</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3073</v>
+        <v>3.0484</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2459</v>
+        <v>1.7116</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5433</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>142</v>
@@ -1035,7 +1035,7 @@
         <v>146</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7892</v>
+        <v>1.8054</v>
       </c>
       <c r="N13" t="n">
         <v>288</v>
@@ -1044,219 +1044,219 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6253</v>
+        <v>2.5965</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6057</v>
+        <v>0.5991</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5709</v>
+        <v>0.577</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6253</v>
+        <v>2.5965</v>
       </c>
       <c r="F14" t="n">
-        <v>0.357</v>
+        <v>2.1089</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2683</v>
+        <v>0.4876</v>
       </c>
       <c r="H14" t="n">
-        <v>0.357</v>
+        <v>2.1089</v>
       </c>
       <c r="I14" t="n">
-        <v>0.357</v>
+        <v>1.1841</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2683</v>
+        <v>0.4876</v>
       </c>
       <c r="K14" t="n">
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="L14" t="n">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6253</v>
+        <v>1.6717</v>
       </c>
       <c r="N14" t="n">
-        <v>179</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5632</v>
+        <v>2.4302</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5914</v>
+        <v>0.5607</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5426</v>
+        <v>0.5013</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5632</v>
+        <v>2.4302</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4434</v>
+        <v>0.2729</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1198</v>
+        <v>2.1573</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1676</v>
+        <v>0.2729</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7105</v>
+        <v>0.2729</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1198</v>
+        <v>2.1573</v>
       </c>
       <c r="K15" t="n">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="L15" t="n">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8303</v>
+        <v>2.4302</v>
       </c>
       <c r="N15" t="n">
-        <v>288</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>Jerry</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4059</v>
+        <v>2.3015</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5551</v>
+        <v>0.531</v>
       </c>
       <c r="D16" t="n">
-        <v>0.471</v>
+        <v>0.4427</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4059</v>
+        <v>2.3015</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8142</v>
+        <v>2.9398</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5917</v>
+        <v>-0.6383</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8142</v>
+        <v>3.7871</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0085</v>
+        <v>4.0989</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5917</v>
+        <v>-0.6383</v>
       </c>
       <c r="K16" t="n">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="L16" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M16" t="n">
-        <v>2.6002</v>
+        <v>3.4606</v>
       </c>
       <c r="N16" t="n">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>facecrack</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3368</v>
+        <v>2.298</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5391</v>
+        <v>0.5302</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4396</v>
+        <v>0.4411</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3368</v>
+        <v>2.298</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9851</v>
+        <v>1.8034</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3517</v>
+        <v>0.4946</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9851</v>
+        <v>1.8034</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1425</v>
+        <v>2.0041</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3517</v>
+        <v>0.4946</v>
       </c>
       <c r="K17" t="n">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="L17" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M17" t="n">
-        <v>2.4942</v>
+        <v>2.4987</v>
       </c>
       <c r="N17" t="n">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jerry</t>
+          <t>facecrack</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3181</v>
+        <v>2.2388</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.5165</v>
       </c>
       <c r="D18" t="n">
-        <v>0.431</v>
+        <v>0.4141</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3181</v>
+        <v>2.2388</v>
       </c>
       <c r="F18" t="n">
-        <v>2.9848</v>
+        <v>1.9463</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6667</v>
+        <v>0.2925</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8078</v>
+        <v>1.9463</v>
       </c>
       <c r="I18" t="n">
-        <v>4.1098</v>
+        <v>2.1066</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6667</v>
+        <v>0.2925</v>
       </c>
       <c r="K18" t="n">
         <v>189</v>
@@ -1265,7 +1265,7 @@
         <v>50</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4431</v>
+        <v>2.3991</v>
       </c>
       <c r="N18" t="n">
         <v>239</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2574</v>
+        <v>2.1636</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5208</v>
+        <v>0.4992</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4034</v>
+        <v>0.3798</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2574</v>
+        <v>2.1636</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1532</v>
+        <v>1.0933</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1042</v>
+        <v>1.0703</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1532</v>
+        <v>1.0933</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2134</v>
+        <v>1.1525</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1042</v>
+        <v>1.0703</v>
       </c>
       <c r="K19" t="n">
         <v>155</v>
@@ -1311,7 +1311,7 @@
         <v>106</v>
       </c>
       <c r="M19" t="n">
-        <v>2.3176</v>
+        <v>2.2228</v>
       </c>
       <c r="N19" t="n">
         <v>261</v>
@@ -1320,35 +1320,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>almazer</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.2095</v>
+        <v>2.0994</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5098</v>
+        <v>0.4844</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3816</v>
+        <v>0.3506</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2095</v>
+        <v>2.0994</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2752</v>
+        <v>2.4018</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.3024</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2752</v>
+        <v>2.5541</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4557</v>
+        <v>2.7644</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.3024</v>
       </c>
       <c r="K20" t="n">
         <v>189</v>
@@ -1357,7 +1357,7 @@
         <v>50</v>
       </c>
       <c r="M20" t="n">
-        <v>2.39</v>
+        <v>2.462</v>
       </c>
       <c r="N20" t="n">
         <v>239</v>
@@ -1366,35 +1366,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>almazer</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.089</v>
+        <v>2.0766</v>
       </c>
       <c r="C21" t="n">
-        <v>0.482</v>
+        <v>0.4791</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3268</v>
+        <v>0.3402</v>
       </c>
       <c r="E21" t="n">
-        <v>2.089</v>
+        <v>2.0766</v>
       </c>
       <c r="F21" t="n">
-        <v>2.365</v>
+        <v>2.1635</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.276</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4514</v>
+        <v>2.1635</v>
       </c>
       <c r="I21" t="n">
-        <v>2.6458</v>
+        <v>2.3416</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.276</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>189</v>
@@ -1403,7 +1403,7 @@
         <v>50</v>
       </c>
       <c r="M21" t="n">
-        <v>2.3698</v>
+        <v>2.2547</v>
       </c>
       <c r="N21" t="n">
         <v>239</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0164</v>
+        <v>2.0551</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4652</v>
+        <v>0.4742</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2937</v>
+        <v>0.3304</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0164</v>
+        <v>2.0551</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1764</v>
+        <v>2.2075</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.16</v>
+        <v>-0.1524</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1764</v>
+        <v>2.2075</v>
       </c>
       <c r="I22" t="n">
-        <v>2.29</v>
+        <v>2.3271</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.16</v>
+        <v>-0.1524</v>
       </c>
       <c r="K22" t="n">
         <v>155</v>
@@ -1449,7 +1449,7 @@
         <v>106</v>
       </c>
       <c r="M22" t="n">
-        <v>2.13</v>
+        <v>2.1747</v>
       </c>
       <c r="N22" t="n">
         <v>261</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.9998</v>
+        <v>1.9981</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4614</v>
+        <v>0.461</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2861</v>
+        <v>0.3044</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9998</v>
+        <v>1.9981</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0216</v>
+        <v>0.0206</v>
       </c>
       <c r="G23" t="n">
-        <v>2.0214</v>
+        <v>1.9775</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0216</v>
+        <v>0.0206</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0227</v>
+        <v>0.0217</v>
       </c>
       <c r="J23" t="n">
-        <v>2.0214</v>
+        <v>1.9775</v>
       </c>
       <c r="K23" t="n">
         <v>162</v>
@@ -1495,7 +1495,7 @@
         <v>114</v>
       </c>
       <c r="M23" t="n">
-        <v>1.9987</v>
+        <v>1.9992</v>
       </c>
       <c r="N23" t="n">
         <v>276</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9245</v>
+        <v>1.9142</v>
       </c>
       <c r="C24" t="n">
-        <v>0.444</v>
+        <v>0.4416</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2519</v>
+        <v>0.2662</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9245</v>
+        <v>1.9142</v>
       </c>
       <c r="F24" t="n">
-        <v>2.24</v>
+        <v>2.1745</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3155</v>
+        <v>-0.2603</v>
       </c>
       <c r="H24" t="n">
-        <v>2.24</v>
+        <v>2.1745</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3569</v>
+        <v>2.2922</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3155</v>
+        <v>-0.2603</v>
       </c>
       <c r="K24" t="n">
         <v>162</v>
@@ -1541,7 +1541,7 @@
         <v>114</v>
       </c>
       <c r="M24" t="n">
-        <v>2.0414</v>
+        <v>2.0319</v>
       </c>
       <c r="N24" t="n">
         <v>276</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7082</v>
+        <v>1.6109</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3941</v>
+        <v>0.3717</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1534</v>
+        <v>0.1281</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7082</v>
+        <v>1.6109</v>
       </c>
       <c r="F25" t="n">
-        <v>2.2588</v>
+        <v>2.1238</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5506</v>
+        <v>-0.5129</v>
       </c>
       <c r="H25" t="n">
-        <v>2.2588</v>
+        <v>2.1238</v>
       </c>
       <c r="I25" t="n">
-        <v>2.5008</v>
+        <v>2.36</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5506</v>
+        <v>-0.5129</v>
       </c>
       <c r="K25" t="n">
         <v>175</v>
@@ -1587,7 +1587,7 @@
         <v>56</v>
       </c>
       <c r="M25" t="n">
-        <v>1.9502</v>
+        <v>1.8471</v>
       </c>
       <c r="N25" t="n">
         <v>231</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.591</v>
+        <v>1.5688</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3671</v>
+        <v>0.362</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1001</v>
+        <v>0.1089</v>
       </c>
       <c r="E26" t="n">
-        <v>1.591</v>
+        <v>1.5688</v>
       </c>
       <c r="F26" t="n">
-        <v>0.258</v>
+        <v>0.2794</v>
       </c>
       <c r="G26" t="n">
-        <v>1.333</v>
+        <v>1.2894</v>
       </c>
       <c r="H26" t="n">
-        <v>0.258</v>
+        <v>0.2794</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2715</v>
+        <v>0.2945</v>
       </c>
       <c r="J26" t="n">
-        <v>1.333</v>
+        <v>1.2894</v>
       </c>
       <c r="K26" t="n">
         <v>155</v>
@@ -1633,7 +1633,7 @@
         <v>106</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6045</v>
+        <v>1.5839</v>
       </c>
       <c r="N26" t="n">
         <v>261</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8012</v>
+        <v>0.6321</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1849</v>
+        <v>0.1458</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2595</v>
+        <v>-0.3178</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8012</v>
+        <v>0.6321</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8012</v>
+        <v>0.6321</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8012</v>
+        <v>0.6321</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8218</v>
+        <v>0.649</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8218</v>
+        <v>0.649</v>
       </c>
       <c r="N27" t="n">
         <v>169</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4</v>
+        <v>0.3535</v>
       </c>
       <c r="C28" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4421</v>
+        <v>-0.4448</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4</v>
+        <v>0.3535</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4</v>
+        <v>2.3535</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4</v>
+        <v>2.3935</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4103</v>
+        <v>1.3439</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="K28" t="n">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4103</v>
+        <v>-0.6560999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>169</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2306</v>
+        <v>0.2807</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0532</v>
+        <v>0.0648</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5192</v>
+        <v>-0.4779</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2306</v>
+        <v>0.2807</v>
       </c>
       <c r="F29" t="n">
-        <v>2.2306</v>
+        <v>0.2807</v>
       </c>
       <c r="G29" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.4652</v>
+        <v>0.2807</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3312</v>
+        <v>0.2883</v>
       </c>
       <c r="J29" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="L29" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6688000000000001</v>
+        <v>0.2883</v>
       </c>
       <c r="N29" t="n">
-        <v>247</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0065</v>
+        <v>-0.1317</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0015</v>
+        <v>-0.0304</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6212</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0065</v>
+        <v>-0.1317</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0065</v>
+        <v>-0.1317</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0065</v>
+        <v>-0.1317</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0067</v>
+        <v>-0.1353</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0067</v>
+        <v>-0.1353</v>
       </c>
       <c r="N30" t="n">
         <v>169</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5078</v>
+        <v>-0.5272</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1172</v>
+        <v>-0.1216</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8554</v>
+        <v>-0.846</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5078</v>
+        <v>-0.5272</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5078</v>
+        <v>-0.5272</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5078</v>
+        <v>-0.5272</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5078</v>
+        <v>-0.5272</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5078</v>
+        <v>-0.5272</v>
       </c>
       <c r="N31" t="n">
         <v>83</v>
@@ -1872,185 +1872,185 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6117</v>
+        <v>-0.5561</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1411</v>
+        <v>-0.1283</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.8591</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6117</v>
+        <v>-0.5561</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6117</v>
+        <v>-0.3336</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.2225</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6117</v>
+        <v>-0.3336</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.1873</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.2225</v>
       </c>
       <c r="K32" t="n">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.4098</v>
       </c>
       <c r="N32" t="n">
-        <v>169</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7758</v>
+        <v>-0.6914</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.179</v>
+        <v>-0.1595</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9774</v>
+        <v>-0.9208</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7758</v>
+        <v>-0.6914</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5652</v>
+        <v>-0.6914</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.2106</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5652</v>
+        <v>-0.6914</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3052</v>
+        <v>-0.7099</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.2106</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="L33" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5158</v>
+        <v>-0.7099</v>
       </c>
       <c r="N33" t="n">
-        <v>288</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7816</v>
+        <v>-0.7537</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1803</v>
+        <v>-0.1739</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.98</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7816</v>
+        <v>-0.7537</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7816</v>
+        <v>-0.8369</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.0832</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7816</v>
+        <v>-0.8369</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8017</v>
+        <v>-0.8822</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.0832</v>
       </c>
       <c r="K34" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8017</v>
+        <v>-0.7989999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>169</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8642</v>
+        <v>-0.792</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1994</v>
+        <v>-0.1827</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0176</v>
+        <v>-0.9666</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8642</v>
+        <v>-0.792</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8841</v>
+        <v>-0.792</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0199</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8841</v>
+        <v>-0.792</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9303</v>
+        <v>-0.8132</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0199</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="L35" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9104</v>
+        <v>-0.8132</v>
       </c>
       <c r="N35" t="n">
-        <v>276</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.919</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2204</v>
+        <v>-0.212</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.059</v>
+        <v>-1.0244</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.919</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.919</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.919</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.919</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.919</v>
       </c>
       <c r="N36" t="n">
         <v>83</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>B1NGO</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0339</v>
+        <v>-1.0125</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2385</v>
+        <v>-0.2336</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0949</v>
+        <v>-1.067</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0339</v>
+        <v>-1.0125</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4299</v>
+        <v>-1.0125</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.604</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4299</v>
+        <v>-1.0125</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4759</v>
+        <v>-1.0125</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.604</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>175</v>
+        <v>83</v>
       </c>
       <c r="L37" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0799</v>
+        <v>-1.0125</v>
       </c>
       <c r="N37" t="n">
-        <v>231</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B1NGO</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0684</v>
+        <v>-1.0171</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2465</v>
+        <v>-0.2347</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1106</v>
+        <v>-1.0691</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0684</v>
+        <v>-1.0171</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0684</v>
+        <v>-0.4473</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.5698</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0684</v>
+        <v>-0.4473</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0684</v>
+        <v>-0.4971</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.5698</v>
       </c>
       <c r="K38" t="n">
-        <v>83</v>
+        <v>175</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0684</v>
+        <v>-1.0669</v>
       </c>
       <c r="N38" t="n">
-        <v>83</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0724</v>
+        <v>-1.0622</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2474</v>
+        <v>-0.2451</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1124</v>
+        <v>-1.0897</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0724</v>
+        <v>-1.0622</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0724</v>
+        <v>-1.0622</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0724</v>
+        <v>-1.0622</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1</v>
+        <v>-1.0906</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1</v>
+        <v>-1.0906</v>
       </c>
       <c r="N39" t="n">
         <v>97</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4484</v>
+        <v>-1.4459</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3342</v>
+        <v>-0.3336</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2835</v>
+        <v>-1.2645</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4484</v>
+        <v>-1.4459</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2033</v>
+        <v>0.1726</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.6517</v>
+        <v>-1.6185</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2033</v>
+        <v>0.1726</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2139</v>
+        <v>0.182</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.6517</v>
+        <v>-1.6185</v>
       </c>
       <c r="K40" t="n">
         <v>162</v>
@@ -2277,7 +2277,7 @@
         <v>114</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4378</v>
+        <v>-1.4365</v>
       </c>
       <c r="N40" t="n">
         <v>276</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4855</v>
+        <v>-1.4494</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3427</v>
+        <v>-0.3344</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3004</v>
+        <v>-1.2661</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4855</v>
+        <v>-1.4494</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4855</v>
+        <v>-1.4494</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4855</v>
+        <v>-1.4494</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4855</v>
+        <v>-1.4494</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4855</v>
+        <v>-1.4494</v>
       </c>
       <c r="N41" t="n">
         <v>83</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-1.4996</v>
+        <v>-1.554</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.346</v>
+        <v>-0.3585</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.3069</v>
+        <v>-1.3137</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.4996</v>
+        <v>-1.554</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.4996</v>
+        <v>-1.554</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.4996</v>
+        <v>-1.554</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.4996</v>
+        <v>-1.554</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-1.4996</v>
+        <v>-1.554</v>
       </c>
       <c r="N42" t="n">
         <v>83</v>
@@ -2475,10 +2475,10 @@
         <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>0.772</v>
+        <v>0.8319</v>
       </c>
       <c r="J2" t="n">
-        <v>27.02</v>
+        <v>29.1165</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>1.02</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0553</v>
+        <v>0.0451</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9355</v>
+        <v>1.5785</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0019</v>
+        <v>-0.001</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0665</v>
+        <v>-0.035</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1018</v>
+        <v>-0.0844</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.563</v>
+        <v>-2.954</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.64</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4047</v>
+        <v>-0.3954</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.1645</v>
+        <v>-13.839</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4487</v>
+        <v>0.3828</v>
       </c>
       <c r="J7" t="n">
-        <v>15.7045</v>
+        <v>13.398</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.26</v>
       </c>
       <c r="I8" t="n">
-        <v>0.39</v>
+        <v>0.3272</v>
       </c>
       <c r="J8" t="n">
-        <v>13.65</v>
+        <v>11.452</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.12</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2117</v>
+        <v>0.166</v>
       </c>
       <c r="J9" t="n">
-        <v>7.4095</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>0.74</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3134</v>
+        <v>-0.2965</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.969</v>
+        <v>-10.3775</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>0.74</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3134</v>
+        <v>-0.2965</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.969</v>
+        <v>-10.3775</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.87</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7491</v>
+        <v>1.7966</v>
       </c>
       <c r="J12" t="n">
-        <v>48.9748</v>
+        <v>50.3048</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>1.01</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0365</v>
+        <v>0.0263</v>
       </c>
       <c r="J13" t="n">
-        <v>1.022</v>
+        <v>0.7364000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.99</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.083</v>
+        <v>-0.0622</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.324</v>
+        <v>-1.7416</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.93</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2866</v>
+        <v>-0.2465</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.024800000000001</v>
+        <v>-6.902</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3427</v>
+        <v>-0.301</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.595599999999999</v>
+        <v>-8.428000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.13</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3216</v>
+        <v>0.2695</v>
       </c>
       <c r="J17" t="n">
-        <v>9.004799999999999</v>
+        <v>7.546</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2635</v>
+        <v>0.2157</v>
       </c>
       <c r="J18" t="n">
-        <v>7.378</v>
+        <v>6.0396</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>0.89</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1536</v>
+        <v>-0.1344</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.3008</v>
+        <v>-3.7632</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>0.83</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2172</v>
+        <v>-0.1969</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.0816</v>
+        <v>-5.5132</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.267</v>
+        <v>-0.2476</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.476</v>
+        <v>-6.9328</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.59</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2961</v>
+        <v>1.3238</v>
       </c>
       <c r="J22" t="n">
-        <v>32.4025</v>
+        <v>33.095</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.42</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9823</v>
+        <v>0.9731</v>
       </c>
       <c r="J23" t="n">
-        <v>24.5575</v>
+        <v>24.3275</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>1.3</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7483</v>
+        <v>0.722</v>
       </c>
       <c r="J24" t="n">
-        <v>18.7075</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>1.12</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3571</v>
+        <v>0.3239</v>
       </c>
       <c r="J25" t="n">
-        <v>8.9275</v>
+        <v>8.0975</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8489</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-21.2225</v>
+        <v>-20.855</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.11</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3187</v>
+        <v>0.2713</v>
       </c>
       <c r="J27" t="n">
-        <v>7.9675</v>
+        <v>6.7825</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>0.78</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2553</v>
+        <v>-0.237</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.3825</v>
+        <v>-5.925</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2648</v>
+        <v>-0.2466</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.62</v>
+        <v>-6.165</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>0.74</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2932</v>
+        <v>-0.2755</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.33</v>
+        <v>-6.8875</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.73</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3026</v>
+        <v>-0.2852</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.565</v>
+        <v>-7.13</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.24</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5921</v>
+        <v>0.5802</v>
       </c>
       <c r="J32" t="n">
-        <v>16.5788</v>
+        <v>16.2456</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4769</v>
+        <v>0.4513</v>
       </c>
       <c r="J33" t="n">
-        <v>13.3532</v>
+        <v>12.6364</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.14</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4195</v>
+        <v>0.3815</v>
       </c>
       <c r="J34" t="n">
-        <v>11.746</v>
+        <v>10.682</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>1.06</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2143</v>
+        <v>0.1838</v>
       </c>
       <c r="J35" t="n">
-        <v>6.0004</v>
+        <v>5.1464</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2212</v>
+        <v>-0.1842</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.1936</v>
+        <v>-5.1576</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.32</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6004</v>
+        <v>0.5757</v>
       </c>
       <c r="J37" t="n">
-        <v>16.8112</v>
+        <v>16.1196</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>0.9</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1401</v>
+        <v>-0.1222</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.9228</v>
+        <v>-3.4216</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>0.82</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2244</v>
+        <v>-0.2044</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.2832</v>
+        <v>-5.7232</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.79</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2542</v>
+        <v>-0.2345</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.1176</v>
+        <v>-6.566</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3023</v>
+        <v>-0.2843</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.464399999999999</v>
+        <v>-7.9604</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.37</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7775</v>
+        <v>0.7618</v>
       </c>
       <c r="J42" t="n">
-        <v>23.325</v>
+        <v>22.854</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.28</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6437</v>
+        <v>0.6312</v>
       </c>
       <c r="J43" t="n">
-        <v>19.311</v>
+        <v>18.936</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.11</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3391</v>
+        <v>0.3051</v>
       </c>
       <c r="J44" t="n">
-        <v>10.173</v>
+        <v>9.153</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.08</v>
       </c>
       <c r="I45" t="n">
-        <v>0.26</v>
+        <v>0.2286</v>
       </c>
       <c r="J45" t="n">
-        <v>7.8</v>
+        <v>6.858</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>1.06</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2031</v>
+        <v>0.1746</v>
       </c>
       <c r="J46" t="n">
-        <v>6.093</v>
+        <v>5.238</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.26</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5264</v>
+        <v>0.4988</v>
       </c>
       <c r="J47" t="n">
-        <v>15.792</v>
+        <v>14.964</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>1.24</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5017</v>
+        <v>0.467</v>
       </c>
       <c r="J48" t="n">
-        <v>15.051</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.75</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2934</v>
+        <v>-0.275</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.802</v>
+        <v>-8.25</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3494</v>
+        <v>-0.3342</v>
       </c>
       <c r="J50" t="n">
-        <v>-10.482</v>
+        <v>-10.026</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.66</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3767</v>
+        <v>-0.3637</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.301</v>
+        <v>-10.911</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.54</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0227</v>
+        <v>1.0117</v>
       </c>
       <c r="J52" t="n">
-        <v>28.6356</v>
+        <v>28.3276</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4154</v>
+        <v>0.3794</v>
       </c>
       <c r="J53" t="n">
-        <v>11.6312</v>
+        <v>10.6232</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>1.08</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2642</v>
+        <v>0.232</v>
       </c>
       <c r="J54" t="n">
-        <v>7.3976</v>
+        <v>6.496</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>1.01</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0344</v>
+        <v>0.0243</v>
       </c>
       <c r="J55" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.6804</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0254</v>
+        <v>-0.02</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6163</v>
+        <v>0.5896</v>
       </c>
       <c r="J57" t="n">
-        <v>17.2564</v>
+        <v>16.5088</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.02</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0819</v>
+        <v>0.0583</v>
       </c>
       <c r="J58" t="n">
-        <v>2.2932</v>
+        <v>1.6324</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>0.98</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0393</v>
+        <v>-0.0306</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.1004</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3515</v>
+        <v>-0.3366</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.842000000000001</v>
+        <v>-9.424799999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.68</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3607</v>
+        <v>-0.3465</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.0996</v>
+        <v>-9.702</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.56</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0679</v>
+        <v>1.061</v>
       </c>
       <c r="J62" t="n">
-        <v>29.9012</v>
+        <v>29.708</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.55</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0541</v>
+        <v>1.0463</v>
       </c>
       <c r="J63" t="n">
-        <v>29.5148</v>
+        <v>29.2964</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>1.14</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4224</v>
+        <v>0.3836</v>
       </c>
       <c r="J64" t="n">
-        <v>11.8272</v>
+        <v>10.7408</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.65</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.9317</v>
+        <v>-0.9221</v>
       </c>
       <c r="J65" t="n">
-        <v>-26.0876</v>
+        <v>-25.8188</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.1137</v>
+        <v>-1.1279</v>
       </c>
       <c r="J66" t="n">
-        <v>-31.1836</v>
+        <v>-31.5812</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.09</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2288</v>
+        <v>0.1851</v>
       </c>
       <c r="J67" t="n">
-        <v>6.4064</v>
+        <v>5.1828</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.08</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2087</v>
+        <v>0.1673</v>
       </c>
       <c r="J68" t="n">
-        <v>5.8436</v>
+        <v>4.6844</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1447</v>
+        <v>0.1119</v>
       </c>
       <c r="J69" t="n">
-        <v>4.0516</v>
+        <v>3.1332</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>1.04</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1217</v>
+        <v>0.0925</v>
       </c>
       <c r="J70" t="n">
-        <v>3.4076</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.193</v>
+        <v>-0.1724</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.404</v>
+        <v>-4.8272</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.05</v>
       </c>
       <c r="I72" t="n">
-        <v>0.18</v>
+        <v>0.1426</v>
       </c>
       <c r="J72" t="n">
-        <v>4.68</v>
+        <v>3.7076</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>0.95</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0738</v>
+        <v>-0.0617</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.9188</v>
+        <v>-1.6042</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>0.85</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1889</v>
+        <v>-0.1707</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.9114</v>
+        <v>-4.4382</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>0.75</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2865</v>
+        <v>-0.2682</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.449</v>
+        <v>-6.9732</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.66</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3698</v>
+        <v>-0.3559</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.614800000000001</v>
+        <v>-9.253399999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.46</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.8908</v>
       </c>
       <c r="J77" t="n">
-        <v>23.5482</v>
+        <v>23.1608</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.4</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8208</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>21.3408</v>
+        <v>20.9274</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>1.29</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6589</v>
+        <v>0.6458</v>
       </c>
       <c r="J79" t="n">
-        <v>17.1314</v>
+        <v>16.7908</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.92</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.322</v>
+        <v>-0.2814</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.372</v>
+        <v>-7.3164</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.83</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.5138</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.3494</v>
+        <v>-13.3588</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.23</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4686</v>
+        <v>0.4205</v>
       </c>
       <c r="J82" t="n">
-        <v>14.058</v>
+        <v>12.615</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.19</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4117</v>
+        <v>0.3554</v>
       </c>
       <c r="J83" t="n">
-        <v>12.351</v>
+        <v>10.662</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1.07</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1886</v>
+        <v>0.1495</v>
       </c>
       <c r="J84" t="n">
-        <v>5.658</v>
+        <v>4.485</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2342</v>
+        <v>-0.2139</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.026</v>
+        <v>-6.417</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2641</v>
+        <v>-0.2447</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.923</v>
+        <v>-7.341</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.52</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0009</v>
+        <v>0.9893</v>
       </c>
       <c r="J87" t="n">
-        <v>30.027</v>
+        <v>29.679</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.42</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8597</v>
+        <v>0.844</v>
       </c>
       <c r="J88" t="n">
-        <v>25.791</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>1.1</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3207</v>
+        <v>0.2853</v>
       </c>
       <c r="J89" t="n">
-        <v>9.621</v>
+        <v>8.558999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5903</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="J90" t="n">
-        <v>-17.709</v>
+        <v>-16.587</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5903</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.709</v>
+        <v>-16.587</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.55</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9885</v>
+        <v>0.9781</v>
       </c>
       <c r="J92" t="n">
-        <v>21.747</v>
+        <v>21.5182</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.45</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8578</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="J93" t="n">
-        <v>18.8716</v>
+        <v>18.6406</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>1.44</v>
       </c>
       <c r="I94" t="n">
-        <v>0.8446</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>18.5812</v>
+        <v>18.3524</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>1.33</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="J95" t="n">
-        <v>15.2922</v>
+        <v>15.136</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>1.26</v>
       </c>
       <c r="I96" t="n">
-        <v>0.5914</v>
+        <v>0.5879</v>
       </c>
       <c r="J96" t="n">
-        <v>13.0108</v>
+        <v>12.9338</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2837</v>
+        <v>0.2447</v>
       </c>
       <c r="J97" t="n">
-        <v>6.2414</v>
+        <v>5.3834</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>0.78</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2498</v>
+        <v>-0.2338</v>
       </c>
       <c r="J98" t="n">
-        <v>-5.4956</v>
+        <v>-5.1436</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>0.78</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2498</v>
+        <v>-0.2338</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.4956</v>
+        <v>-5.1436</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>0.57</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4394</v>
+        <v>-0.4313</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.6668</v>
+        <v>-9.4886</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.57</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4394</v>
+        <v>-0.4313</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.6668</v>
+        <v>-9.4886</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.29</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="J102" t="n">
-        <v>19.096</v>
+        <v>18.6704</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.24</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.5893</v>
       </c>
       <c r="J103" t="n">
-        <v>16.8644</v>
+        <v>16.5004</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>1.17</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4852</v>
+        <v>0.4605</v>
       </c>
       <c r="J104" t="n">
-        <v>13.5856</v>
+        <v>12.894</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>0.8</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5994</v>
+        <v>-0.5611</v>
       </c>
       <c r="J105" t="n">
-        <v>-16.7832</v>
+        <v>-15.7108</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.79</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6223</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="J106" t="n">
-        <v>-17.4244</v>
+        <v>-16.3856</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.31</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5564</v>
+        <v>0.5296</v>
       </c>
       <c r="J107" t="n">
-        <v>15.5792</v>
+        <v>14.8288</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.07</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1841</v>
+        <v>0.1469</v>
       </c>
       <c r="J108" t="n">
-        <v>5.1548</v>
+        <v>4.1132</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>1.06</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1634</v>
+        <v>0.1289</v>
       </c>
       <c r="J109" t="n">
-        <v>4.5752</v>
+        <v>3.6092</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.068</v>
+        <v>0.0498</v>
       </c>
       <c r="J110" t="n">
-        <v>1.904</v>
+        <v>1.3944</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.83</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2273</v>
+        <v>-0.207</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.3644</v>
+        <v>-5.796</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.75</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8471</v>
+        <v>0.7764</v>
       </c>
       <c r="J112" t="n">
-        <v>18.6362</v>
+        <v>17.0808</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.46</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5681</v>
+        <v>0.4992</v>
       </c>
       <c r="J113" t="n">
-        <v>12.4982</v>
+        <v>10.9824</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.41</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.451</v>
       </c>
       <c r="J114" t="n">
-        <v>11.3872</v>
+        <v>9.922000000000001</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>1.15</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2271</v>
+        <v>0.1845</v>
       </c>
       <c r="J115" t="n">
-        <v>4.9962</v>
+        <v>4.059</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.87</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2056</v>
+        <v>-0.1875</v>
       </c>
       <c r="J116" t="n">
-        <v>-4.5232</v>
+        <v>-4.125</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.12</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2772</v>
+        <v>0.271</v>
       </c>
       <c r="J117" t="n">
-        <v>6.0984</v>
+        <v>5.962</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.03</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1179</v>
+        <v>0.1065</v>
       </c>
       <c r="J118" t="n">
-        <v>2.5938</v>
+        <v>2.343</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.73</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2986</v>
+        <v>-0.2817</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.5692</v>
+        <v>-6.1974</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.57</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4431</v>
+        <v>-0.4355</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.748200000000001</v>
+        <v>-9.581</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.49</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.513</v>
+        <v>-0.5137</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.286</v>
+        <v>-11.3014</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>0.66</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.2989</v>
+        <v>-0.2837</v>
       </c>
       <c r="J122" t="n">
-        <v>-5.0813</v>
+        <v>-4.8229</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>0.5</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.4584</v>
+        <v>-0.4594</v>
       </c>
       <c r="J123" t="n">
-        <v>-7.7928</v>
+        <v>-7.8098</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>0.42</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.5261</v>
+        <v>-0.5294</v>
       </c>
       <c r="J124" t="n">
-        <v>-8.9437</v>
+        <v>-8.9998</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>0.36</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5796</v>
+        <v>-0.5874</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.853199999999999</v>
+        <v>-9.985799999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.34</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5979</v>
+        <v>-0.6079</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.1643</v>
+        <v>-10.3343</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>2.06</v>
       </c>
       <c r="I127" t="n">
-        <v>1.7053</v>
+        <v>1.754</v>
       </c>
       <c r="J127" t="n">
-        <v>28.9901</v>
+        <v>29.818</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.74</v>
       </c>
       <c r="I128" t="n">
-        <v>1.3402</v>
+        <v>1.3682</v>
       </c>
       <c r="J128" t="n">
-        <v>22.7834</v>
+        <v>23.2594</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>1.68</v>
       </c>
       <c r="I129" t="n">
-        <v>1.2706</v>
+        <v>1.2968</v>
       </c>
       <c r="J129" t="n">
-        <v>21.6002</v>
+        <v>22.0456</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>1.48</v>
       </c>
       <c r="I130" t="n">
-        <v>1.0187</v>
+        <v>1.0345</v>
       </c>
       <c r="J130" t="n">
-        <v>17.3179</v>
+        <v>17.5865</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>1.45</v>
       </c>
       <c r="I131" t="n">
-        <v>0.9717</v>
+        <v>0.9809</v>
       </c>
       <c r="J131" t="n">
-        <v>16.5189</v>
+        <v>16.6753</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.18</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4288</v>
+        <v>0.374</v>
       </c>
       <c r="J132" t="n">
-        <v>11.1488</v>
+        <v>9.724</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>0.86</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1814</v>
+        <v>-0.1623</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.7164</v>
+        <v>-4.2198</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>0.83</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2122</v>
+        <v>-0.1926</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.5172</v>
+        <v>-5.0076</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2323</v>
+        <v>-0.2126</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.0398</v>
+        <v>-5.5276</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.78</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2618</v>
+        <v>-0.2425</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.8068</v>
+        <v>-6.305</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.51</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1239</v>
+        <v>1.1363</v>
       </c>
       <c r="J137" t="n">
-        <v>29.2214</v>
+        <v>29.5438</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.31</v>
       </c>
       <c r="I138" t="n">
-        <v>0.7785</v>
+        <v>0.7519</v>
       </c>
       <c r="J138" t="n">
-        <v>20.241</v>
+        <v>19.5494</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1.18</v>
       </c>
       <c r="I139" t="n">
-        <v>0.5043</v>
+        <v>0.4684</v>
       </c>
       <c r="J139" t="n">
-        <v>13.1118</v>
+        <v>12.1784</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>1.12</v>
       </c>
       <c r="I140" t="n">
-        <v>0.3651</v>
+        <v>0.3303</v>
       </c>
       <c r="J140" t="n">
-        <v>9.492599999999999</v>
+        <v>8.5878</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.75</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7331</v>
+        <v>-0.7062</v>
       </c>
       <c r="J141" t="n">
-        <v>-19.0606</v>
+        <v>-18.3612</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.11</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2479</v>
+        <v>0.2363</v>
       </c>
       <c r="J142" t="n">
-        <v>6.1975</v>
+        <v>5.9075</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.88</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1559</v>
+        <v>-0.1394</v>
       </c>
       <c r="J143" t="n">
-        <v>-3.8975</v>
+        <v>-3.485</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.83</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2075</v>
+        <v>-0.1895</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.1875</v>
+        <v>-4.7375</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.77</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2654</v>
+        <v>-0.2471</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.635</v>
+        <v>-6.1775</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.57</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4479</v>
+        <v>-0.4411</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.1975</v>
+        <v>-11.0275</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.57</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.6241</v>
       </c>
       <c r="J147" t="n">
-        <v>17.4025</v>
+        <v>15.6025</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4681</v>
+        <v>0.4017</v>
       </c>
       <c r="J148" t="n">
-        <v>11.7025</v>
+        <v>10.0425</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.21</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3108</v>
+        <v>0.2571</v>
       </c>
       <c r="J149" t="n">
-        <v>7.77</v>
+        <v>6.4275</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.03</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0573</v>
+        <v>0.0405</v>
       </c>
       <c r="J150" t="n">
-        <v>1.4325</v>
+        <v>1.0125</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.83</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2385</v>
+        <v>-0.2196</v>
       </c>
       <c r="J151" t="n">
-        <v>-5.9625</v>
+        <v>-5.49</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.8</v>
       </c>
       <c r="I152" t="n">
-        <v>1.4406</v>
+        <v>1.4682</v>
       </c>
       <c r="J152" t="n">
-        <v>31.6932</v>
+        <v>32.3004</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.76</v>
       </c>
       <c r="I153" t="n">
-        <v>1.392</v>
+        <v>1.4169</v>
       </c>
       <c r="J153" t="n">
-        <v>30.624</v>
+        <v>31.1718</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>1.31</v>
       </c>
       <c r="I154" t="n">
-        <v>0.7401</v>
+        <v>0.7234</v>
       </c>
       <c r="J154" t="n">
-        <v>16.2822</v>
+        <v>15.9148</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>1.25</v>
       </c>
       <c r="I155" t="n">
-        <v>0.6178</v>
+        <v>0.5941</v>
       </c>
       <c r="J155" t="n">
-        <v>13.5916</v>
+        <v>13.0702</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>1.14</v>
       </c>
       <c r="I156" t="n">
-        <v>0.3711</v>
+        <v>0.3387</v>
       </c>
       <c r="J156" t="n">
-        <v>8.164199999999999</v>
+        <v>7.4514</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>0.77</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.2487</v>
+        <v>-0.2346</v>
       </c>
       <c r="J157" t="n">
-        <v>-5.4714</v>
+        <v>-5.1612</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>0.73</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2877</v>
+        <v>-0.2745</v>
       </c>
       <c r="J158" t="n">
-        <v>-6.3294</v>
+        <v>-6.039</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>0.67</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3414</v>
+        <v>-0.329</v>
       </c>
       <c r="J159" t="n">
-        <v>-7.5108</v>
+        <v>-7.238</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>0.64</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3675</v>
+        <v>-0.3556</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.085000000000001</v>
+        <v>-7.8232</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.57</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4292</v>
+        <v>-0.4207</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.442399999999999</v>
+        <v>-9.2554</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.42</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9697</v>
+        <v>0.9633</v>
       </c>
       <c r="J162" t="n">
-        <v>24.2425</v>
+        <v>24.0825</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.41</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9522</v>
+        <v>0.9432</v>
       </c>
       <c r="J163" t="n">
-        <v>23.805</v>
+        <v>23.58</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.34</v>
       </c>
       <c r="I164" t="n">
-        <v>0.82</v>
+        <v>0.7998</v>
       </c>
       <c r="J164" t="n">
-        <v>20.5</v>
+        <v>19.995</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.27</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6828</v>
+        <v>0.656</v>
       </c>
       <c r="J165" t="n">
-        <v>17.07</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>0.91</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.365</v>
+        <v>-0.326</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.125</v>
+        <v>-8.15</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.04</v>
       </c>
       <c r="I167" t="n">
-        <v>0.173</v>
+        <v>0.1398</v>
       </c>
       <c r="J167" t="n">
-        <v>4.325</v>
+        <v>3.495</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>0.9</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.129</v>
+        <v>-0.1139</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.225</v>
+        <v>-2.8475</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.163</v>
+        <v>-0.1469</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.075</v>
+        <v>-3.6725</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.7</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3273</v>
+        <v>-0.3113</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.182499999999999</v>
+        <v>-7.7825</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.48</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5226</v>
+        <v>-0.5248</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.065</v>
+        <v>-13.12</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.84</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4863</v>
+        <v>1.5168</v>
       </c>
       <c r="J172" t="n">
-        <v>28.2397</v>
+        <v>28.8192</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.61</v>
       </c>
       <c r="I173" t="n">
-        <v>1.2045</v>
+        <v>1.2226</v>
       </c>
       <c r="J173" t="n">
-        <v>22.8855</v>
+        <v>23.2294</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>1.33</v>
       </c>
       <c r="I174" t="n">
-        <v>0.7775</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="J174" t="n">
-        <v>14.7725</v>
+        <v>14.5084</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>1.29</v>
       </c>
       <c r="I175" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.6792</v>
       </c>
       <c r="J175" t="n">
-        <v>13.2639</v>
+        <v>12.9048</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>1.26</v>
       </c>
       <c r="I176" t="n">
-        <v>0.6367</v>
+        <v>0.6141</v>
       </c>
       <c r="J176" t="n">
-        <v>12.0973</v>
+        <v>11.6679</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>0.8</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.2064</v>
+        <v>-0.1904</v>
       </c>
       <c r="J177" t="n">
-        <v>-3.9216</v>
+        <v>-3.6176</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>0.75</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2586</v>
+        <v>-0.2452</v>
       </c>
       <c r="J178" t="n">
-        <v>-4.9134</v>
+        <v>-4.6588</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.73</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2786</v>
+        <v>-0.2661</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.2934</v>
+        <v>-5.0559</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.55</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4397</v>
+        <v>-0.4327</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.3543</v>
+        <v>-8.221299999999999</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.29</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.668</v>
+        <v>-0.6921</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.692</v>
+        <v>-13.1499</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.33</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4956</v>
+        <v>0.5042</v>
       </c>
       <c r="J182" t="n">
-        <v>14.3724</v>
+        <v>14.6218</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.14</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2508</v>
+        <v>0.2363</v>
       </c>
       <c r="J183" t="n">
-        <v>7.2732</v>
+        <v>6.8527</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.11</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2074</v>
+        <v>0.1917</v>
       </c>
       <c r="J184" t="n">
-        <v>6.0146</v>
+        <v>5.5593</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>0.84</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2156</v>
+        <v>-0.1951</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.2524</v>
+        <v>-5.6579</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.79</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.266</v>
+        <v>-0.2468</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.714</v>
+        <v>-7.1572</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3364</v>
+        <v>0.2776</v>
       </c>
       <c r="J187" t="n">
-        <v>9.755599999999999</v>
+        <v>8.0504</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.19</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2993</v>
+        <v>0.244</v>
       </c>
       <c r="J188" t="n">
-        <v>8.6797</v>
+        <v>7.076</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>1.16</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2611</v>
+        <v>0.2098</v>
       </c>
       <c r="J189" t="n">
-        <v>7.5719</v>
+        <v>6.0842</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.96</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.07779999999999999</v>
+        <v>-0.0624</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.2562</v>
+        <v>-1.8096</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2484</v>
+        <v>-0.2287</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.2036</v>
+        <v>-6.6323</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.71</v>
       </c>
       <c r="I192" t="n">
-        <v>1.3746</v>
+        <v>1.3991</v>
       </c>
       <c r="J192" t="n">
-        <v>35.7396</v>
+        <v>36.3766</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>1.29</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7266</v>
+        <v>0.6998</v>
       </c>
       <c r="J193" t="n">
-        <v>18.8916</v>
+        <v>18.1948</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>1.11</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3302</v>
+        <v>0.2977</v>
       </c>
       <c r="J194" t="n">
-        <v>8.5852</v>
+        <v>7.7402</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>1.07</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2226</v>
+        <v>0.1933</v>
       </c>
       <c r="J195" t="n">
-        <v>5.7876</v>
+        <v>5.0258</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>1</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.0398</v>
+        <v>-0.0344</v>
       </c>
       <c r="J196" t="n">
-        <v>-1.0348</v>
+        <v>-0.8944</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.14</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3676</v>
+        <v>0.3164</v>
       </c>
       <c r="J197" t="n">
-        <v>9.557600000000001</v>
+        <v>8.2264</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.08</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2468</v>
+        <v>0.2026</v>
       </c>
       <c r="J198" t="n">
-        <v>6.4168</v>
+        <v>5.2676</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>0.93</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1001</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.6026</v>
+        <v>-2.236</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.459</v>
+        <v>-0.4536</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.934</v>
+        <v>-11.7936</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.459</v>
+        <v>-0.4536</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.934</v>
+        <v>-11.7936</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>0.93</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0633</v>
+        <v>-0.0454</v>
       </c>
       <c r="J202" t="n">
-        <v>-1.3293</v>
+        <v>-0.9534</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.91</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0895</v>
+        <v>-0.0716</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.8795</v>
+        <v>-1.5036</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.59</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.41</v>
+        <v>-0.4004</v>
       </c>
       <c r="J204" t="n">
-        <v>-8.609999999999999</v>
+        <v>-8.4084</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.49</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4981</v>
+        <v>-0.496</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.4601</v>
+        <v>-10.416</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.4</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5768</v>
+        <v>-0.5853</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.1128</v>
+        <v>-12.2913</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.72</v>
       </c>
       <c r="I207" t="n">
-        <v>1.3419</v>
+        <v>1.3643</v>
       </c>
       <c r="J207" t="n">
-        <v>28.1799</v>
+        <v>28.6503</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.53</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1039</v>
+        <v>1.1203</v>
       </c>
       <c r="J208" t="n">
-        <v>23.1819</v>
+        <v>23.5263</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>1.44</v>
       </c>
       <c r="I209" t="n">
-        <v>0.9792</v>
+        <v>0.9826</v>
       </c>
       <c r="J209" t="n">
-        <v>20.5632</v>
+        <v>20.6346</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>1.35</v>
       </c>
       <c r="I210" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8056</v>
       </c>
       <c r="J210" t="n">
-        <v>17.157</v>
+        <v>16.9176</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>1.26</v>
       </c>
       <c r="I211" t="n">
-        <v>0.6375</v>
+        <v>0.615</v>
       </c>
       <c r="J211" t="n">
-        <v>13.3875</v>
+        <v>12.915</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>0.73</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.2552</v>
+        <v>-0.2396</v>
       </c>
       <c r="J212" t="n">
-        <v>-4.3384</v>
+        <v>-4.0732</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>0.65</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.3368</v>
+        <v>-0.3281</v>
       </c>
       <c r="J213" t="n">
-        <v>-5.7256</v>
+        <v>-5.5777</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.47</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4963</v>
+        <v>-0.4952</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.437099999999999</v>
+        <v>-8.4184</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.43</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5316</v>
+        <v>-0.5335</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.0372</v>
+        <v>-9.0695</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.4</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5583</v>
+        <v>-0.5632</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.491099999999999</v>
+        <v>-9.574400000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>2.27</v>
       </c>
       <c r="I217" t="n">
-        <v>1.9254</v>
+        <v>1.9818</v>
       </c>
       <c r="J217" t="n">
-        <v>32.7318</v>
+        <v>33.6906</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.84</v>
       </c>
       <c r="I218" t="n">
-        <v>1.4499</v>
+        <v>1.484</v>
       </c>
       <c r="J218" t="n">
-        <v>24.6483</v>
+        <v>25.228</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>1.59</v>
       </c>
       <c r="I219" t="n">
-        <v>1.1575</v>
+        <v>1.1829</v>
       </c>
       <c r="J219" t="n">
-        <v>19.6775</v>
+        <v>20.1093</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>1.54</v>
       </c>
       <c r="I220" t="n">
-        <v>1.0944</v>
+        <v>1.1184</v>
       </c>
       <c r="J220" t="n">
-        <v>18.6048</v>
+        <v>19.0128</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>1.49</v>
       </c>
       <c r="I221" t="n">
-        <v>1.027</v>
+        <v>1.0449</v>
       </c>
       <c r="J221" t="n">
-        <v>17.459</v>
+        <v>17.7633</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.04</v>
       </c>
       <c r="I222" t="n">
-        <v>0.154</v>
+        <v>0.1197</v>
       </c>
       <c r="J222" t="n">
-        <v>4.158</v>
+        <v>3.2319</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>0.95</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0746</v>
+        <v>-0.0624</v>
       </c>
       <c r="J223" t="n">
-        <v>-2.0142</v>
+        <v>-1.6848</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>0.93</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1006</v>
+        <v>-0.0864</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.7162</v>
+        <v>-2.3328</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.73</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3059</v>
+        <v>-0.2884</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.2593</v>
+        <v>-7.7868</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.64</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3885</v>
+        <v>-0.3761</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.4895</v>
+        <v>-10.1547</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.6</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2329</v>
+        <v>1.2492</v>
       </c>
       <c r="J227" t="n">
-        <v>33.2883</v>
+        <v>33.7284</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>1.47</v>
       </c>
       <c r="I228" t="n">
-        <v>1.0566</v>
+        <v>1.0632</v>
       </c>
       <c r="J228" t="n">
-        <v>28.5282</v>
+        <v>28.7064</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>1.14</v>
       </c>
       <c r="I229" t="n">
-        <v>0.4057</v>
+        <v>0.3722</v>
       </c>
       <c r="J229" t="n">
-        <v>10.9539</v>
+        <v>10.0494</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.97</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1764</v>
+        <v>-0.1454</v>
       </c>
       <c r="J230" t="n">
-        <v>-4.7628</v>
+        <v>-3.9258</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.96</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2102</v>
+        <v>-0.1763</v>
       </c>
       <c r="J231" t="n">
-        <v>-5.6754</v>
+        <v>-4.7601</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>1.05</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2638</v>
+        <v>0.2428</v>
       </c>
       <c r="J232" t="n">
-        <v>5.276</v>
+        <v>4.856</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>0.88</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.1253</v>
+        <v>-0.1077</v>
       </c>
       <c r="J233" t="n">
-        <v>-2.506</v>
+        <v>-2.154</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>0.53</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.4623</v>
+        <v>-0.4566</v>
       </c>
       <c r="J234" t="n">
-        <v>-9.246</v>
+        <v>-9.132</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>0.47</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5151</v>
+        <v>-0.515</v>
       </c>
       <c r="J235" t="n">
-        <v>-10.302</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.37</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6024</v>
+        <v>-0.615</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.048</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.72</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3419</v>
+        <v>1.3643</v>
       </c>
       <c r="J237" t="n">
-        <v>26.838</v>
+        <v>27.286</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.71</v>
       </c>
       <c r="I238" t="n">
-        <v>1.3296</v>
+        <v>1.3515</v>
       </c>
       <c r="J238" t="n">
-        <v>26.592</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>1.53</v>
       </c>
       <c r="I239" t="n">
-        <v>1.1039</v>
+        <v>1.1203</v>
       </c>
       <c r="J239" t="n">
-        <v>22.078</v>
+        <v>22.406</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>1.35</v>
       </c>
       <c r="I240" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8056</v>
       </c>
       <c r="J240" t="n">
-        <v>16.34</v>
+        <v>16.112</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.99</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.1344</v>
+        <v>-0.1186</v>
       </c>
       <c r="J241" t="n">
-        <v>-2.688</v>
+        <v>-2.372</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.31</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4296</v>
+        <v>0.3649</v>
       </c>
       <c r="J242" t="n">
-        <v>11.5992</v>
+        <v>9.8523</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3843</v>
+        <v>0.3228</v>
       </c>
       <c r="J243" t="n">
-        <v>10.3761</v>
+        <v>8.7156</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>1.21</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3142</v>
+        <v>0.2589</v>
       </c>
       <c r="J244" t="n">
-        <v>8.4834</v>
+        <v>6.9903</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>1.08</v>
       </c>
       <c r="I245" t="n">
-        <v>0.145</v>
+        <v>0.112</v>
       </c>
       <c r="J245" t="n">
-        <v>3.915</v>
+        <v>3.024</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.9</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1598</v>
+        <v>-0.14</v>
       </c>
       <c r="J246" t="n">
-        <v>-4.3146</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>1.07</v>
       </c>
       <c r="I247" t="n">
-        <v>0.1606</v>
+        <v>0.1433</v>
       </c>
       <c r="J247" t="n">
-        <v>4.3362</v>
+        <v>3.8691</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1</v>
       </c>
       <c r="I248" t="n">
-        <v>0.0072</v>
+        <v>0.005</v>
       </c>
       <c r="J248" t="n">
-        <v>0.1944</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.88</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1632</v>
+        <v>-0.1439</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.4064</v>
+        <v>-3.8853</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.86</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1846</v>
+        <v>-0.1647</v>
       </c>
       <c r="J250" t="n">
-        <v>-4.9842</v>
+        <v>-4.4469</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.84</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2055</v>
+        <v>-0.1853</v>
       </c>
       <c r="J251" t="n">
-        <v>-5.5485</v>
+        <v>-5.0031</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.16</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3846</v>
+        <v>0.33</v>
       </c>
       <c r="J252" t="n">
-        <v>10.3842</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.11</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2901</v>
+        <v>0.2405</v>
       </c>
       <c r="J253" t="n">
-        <v>7.8327</v>
+        <v>6.4935</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>0.96</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0673</v>
+        <v>-0.0552</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.8171</v>
+        <v>-1.4904</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>0.84</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2044</v>
+        <v>-0.1844</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.5188</v>
+        <v>-4.9788</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.52</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4995</v>
+        <v>-0.5</v>
       </c>
       <c r="J256" t="n">
-        <v>-13.4865</v>
+        <v>-13.5</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.27</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7073</v>
+        <v>0.6751</v>
       </c>
       <c r="J257" t="n">
-        <v>19.0971</v>
+        <v>18.2277</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>1.27</v>
       </c>
       <c r="I258" t="n">
-        <v>0.7073</v>
+        <v>0.6751</v>
       </c>
       <c r="J258" t="n">
-        <v>19.0971</v>
+        <v>18.2277</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>1.19</v>
       </c>
       <c r="I259" t="n">
-        <v>0.5337</v>
+        <v>0.4955</v>
       </c>
       <c r="J259" t="n">
-        <v>14.4099</v>
+        <v>13.3785</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>1.15</v>
       </c>
       <c r="I260" t="n">
-        <v>0.4423</v>
+        <v>0.4038</v>
       </c>
       <c r="J260" t="n">
-        <v>11.9421</v>
+        <v>10.9026</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7464</v>
+        <v>-0.7192</v>
       </c>
       <c r="J261" t="n">
-        <v>-20.1528</v>
+        <v>-19.4184</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.19</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4084</v>
+        <v>0.3519</v>
       </c>
       <c r="J262" t="n">
-        <v>16.7444</v>
+        <v>14.4279</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.06</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1651</v>
+        <v>0.1297</v>
       </c>
       <c r="J263" t="n">
-        <v>6.7691</v>
+        <v>5.3177</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.01</v>
       </c>
       <c r="I264" t="n">
-        <v>0.0401</v>
+        <v>0.0279</v>
       </c>
       <c r="J264" t="n">
-        <v>1.6441</v>
+        <v>1.1439</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.97</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.061</v>
+        <v>-0.0476</v>
       </c>
       <c r="J265" t="n">
-        <v>-2.501</v>
+        <v>-1.9516</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.96</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0604</v>
       </c>
       <c r="J266" t="n">
-        <v>-3.0914</v>
+        <v>-2.4764</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.48</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1076</v>
+        <v>1.1212</v>
       </c>
       <c r="J267" t="n">
-        <v>45.4116</v>
+        <v>45.9692</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.21</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5888</v>
+        <v>0.5502</v>
       </c>
       <c r="J268" t="n">
-        <v>24.1408</v>
+        <v>22.5582</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>1.02</v>
       </c>
       <c r="I269" t="n">
-        <v>0.0893</v>
+        <v>0.0706</v>
       </c>
       <c r="J269" t="n">
-        <v>3.6613</v>
+        <v>2.8946</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.86</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4597</v>
+        <v>-0.4171</v>
       </c>
       <c r="J270" t="n">
-        <v>-18.8477</v>
+        <v>-17.1011</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5797</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="J271" t="n">
-        <v>-23.7677</v>
+        <v>-22.1728</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>1.36</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6532</v>
+        <v>0.594</v>
       </c>
       <c r="J272" t="n">
-        <v>19.596</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>1.22</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4394</v>
+        <v>0.3839</v>
       </c>
       <c r="J273" t="n">
-        <v>13.182</v>
+        <v>11.517</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>1.14</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3075</v>
+        <v>0.2606</v>
       </c>
       <c r="J274" t="n">
-        <v>9.225</v>
+        <v>7.818</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>1.12</v>
       </c>
       <c r="I275" t="n">
-        <v>0.2721</v>
+        <v>0.2283</v>
       </c>
       <c r="J275" t="n">
-        <v>8.163</v>
+        <v>6.849</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.91</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.1479</v>
+        <v>-0.1284</v>
       </c>
       <c r="J276" t="n">
-        <v>-4.437</v>
+        <v>-3.852</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.15</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5108</v>
+        <v>0.4722</v>
       </c>
       <c r="J277" t="n">
-        <v>15.324</v>
+        <v>14.166</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>0.96</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.148</v>
+        <v>-0.1234</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.44</v>
+        <v>-3.702</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>0.89</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3474</v>
+        <v>-0.3106</v>
       </c>
       <c r="J279" t="n">
-        <v>-10.422</v>
+        <v>-9.318</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.83</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4918</v>
+        <v>-0.4523</v>
       </c>
       <c r="J280" t="n">
-        <v>-14.754</v>
+        <v>-13.569</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.58</v>
       </c>
       <c r="I281" t="n">
-        <v>-1.0338</v>
+        <v>-1.031</v>
       </c>
       <c r="J281" t="n">
-        <v>-31.014</v>
+        <v>-30.93</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>0.89</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.0975</v>
+        <v>-0.0755</v>
       </c>
       <c r="J282" t="n">
-        <v>-1.95</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>0.76</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.2446</v>
+        <v>-0.2303</v>
       </c>
       <c r="J283" t="n">
-        <v>-4.892</v>
+        <v>-4.606</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.68</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3239</v>
+        <v>-0.3135</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.478</v>
+        <v>-6.27</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.42</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.5518</v>
+        <v>-0.5561</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.036</v>
+        <v>-11.122</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.29</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6663</v>
+        <v>-0.6896</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.326</v>
+        <v>-13.792</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.99</v>
       </c>
       <c r="I287" t="n">
-        <v>1.6459</v>
+        <v>1.6888</v>
       </c>
       <c r="J287" t="n">
-        <v>32.918</v>
+        <v>33.776</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.59</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1706</v>
+        <v>1.191</v>
       </c>
       <c r="J288" t="n">
-        <v>23.412</v>
+        <v>23.82</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.49</v>
       </c>
       <c r="I289" t="n">
-        <v>1.045</v>
+        <v>1.0607</v>
       </c>
       <c r="J289" t="n">
-        <v>20.9</v>
+        <v>21.214</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>1.38</v>
       </c>
       <c r="I290" t="n">
-        <v>0.8613</v>
+        <v>0.8558</v>
       </c>
       <c r="J290" t="n">
-        <v>17.226</v>
+        <v>17.116</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>1.34</v>
       </c>
       <c r="I291" t="n">
-        <v>0.7846</v>
+        <v>0.7731</v>
       </c>
       <c r="J291" t="n">
-        <v>15.692</v>
+        <v>15.462</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.1</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3003</v>
+        <v>0.316</v>
       </c>
       <c r="J292" t="n">
-        <v>6.006</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>0.73</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.2846</v>
+        <v>-0.2718</v>
       </c>
       <c r="J293" t="n">
-        <v>-5.692</v>
+        <v>-5.436</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.61</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.3914</v>
+        <v>-0.3811</v>
       </c>
       <c r="J294" t="n">
-        <v>-7.828</v>
+        <v>-7.622</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.54</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.453</v>
+        <v>-0.4465</v>
       </c>
       <c r="J295" t="n">
-        <v>-9.06</v>
+        <v>-8.93</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.3</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6627</v>
+        <v>-0.6863</v>
       </c>
       <c r="J296" t="n">
-        <v>-13.254</v>
+        <v>-13.726</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>2.27</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2102</v>
+        <v>1.1763</v>
       </c>
       <c r="J297" t="n">
-        <v>24.204</v>
+        <v>23.526</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.48</v>
       </c>
       <c r="I298" t="n">
-        <v>0.5784</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="J298" t="n">
-        <v>11.568</v>
+        <v>10.232</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.31</v>
       </c>
       <c r="I299" t="n">
-        <v>0.4068</v>
+        <v>0.3497</v>
       </c>
       <c r="J299" t="n">
-        <v>8.135999999999999</v>
+        <v>6.994</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>1.16</v>
       </c>
       <c r="I300" t="n">
-        <v>0.2305</v>
+        <v>0.1877</v>
       </c>
       <c r="J300" t="n">
-        <v>4.61</v>
+        <v>3.754</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.99</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.0567</v>
+        <v>-0.049</v>
       </c>
       <c r="J301" t="n">
-        <v>-1.134</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>1.87</v>
       </c>
       <c r="I302" t="n">
-        <v>1.5127</v>
+        <v>1.5454</v>
       </c>
       <c r="J302" t="n">
-        <v>28.7413</v>
+        <v>29.3626</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>1.6</v>
       </c>
       <c r="I303" t="n">
-        <v>1.1862</v>
+        <v>1.2054</v>
       </c>
       <c r="J303" t="n">
-        <v>22.5378</v>
+        <v>22.9026</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>1.41</v>
       </c>
       <c r="I304" t="n">
-        <v>0.9217</v>
+        <v>0.9206</v>
       </c>
       <c r="J304" t="n">
-        <v>17.5123</v>
+        <v>17.4914</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>1.39</v>
       </c>
       <c r="I305" t="n">
-        <v>0.885</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="J305" t="n">
-        <v>16.815</v>
+        <v>16.7295</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>1.33</v>
       </c>
       <c r="I306" t="n">
-        <v>0.7702</v>
+        <v>0.757</v>
       </c>
       <c r="J306" t="n">
-        <v>14.6338</v>
+        <v>14.383</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>1.11</v>
       </c>
       <c r="I307" t="n">
-        <v>0.432</v>
+        <v>0.4189</v>
       </c>
       <c r="J307" t="n">
-        <v>8.208</v>
+        <v>7.9591</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>0.67</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.3352</v>
+        <v>-0.3249</v>
       </c>
       <c r="J308" t="n">
-        <v>-6.3688</v>
+        <v>-6.1731</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>0.63</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.3708</v>
+        <v>-0.3614</v>
       </c>
       <c r="J309" t="n">
-        <v>-7.0452</v>
+        <v>-6.8666</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>0.35</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.615</v>
+        <v>-0.6291</v>
       </c>
       <c r="J310" t="n">
-        <v>-11.685</v>
+        <v>-11.9529</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.34</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6238</v>
+        <v>-0.6394</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.8522</v>
+        <v>-12.1486</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.77</v>
       </c>
       <c r="I312" t="n">
-        <v>1.389</v>
+        <v>1.4153</v>
       </c>
       <c r="J312" t="n">
-        <v>26.391</v>
+        <v>26.8907</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.74</v>
       </c>
       <c r="I313" t="n">
-        <v>1.3531</v>
+        <v>1.3779</v>
       </c>
       <c r="J313" t="n">
-        <v>25.7089</v>
+        <v>26.1801</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>1.62</v>
       </c>
       <c r="I314" t="n">
-        <v>1.2076</v>
+        <v>1.2284</v>
       </c>
       <c r="J314" t="n">
-        <v>22.9444</v>
+        <v>23.3396</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>1.42</v>
       </c>
       <c r="I315" t="n">
-        <v>0.9354</v>
+        <v>0.9369</v>
       </c>
       <c r="J315" t="n">
-        <v>17.7726</v>
+        <v>17.8011</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>1.22</v>
       </c>
       <c r="I316" t="n">
-        <v>0.5394</v>
+        <v>0.512</v>
       </c>
       <c r="J316" t="n">
-        <v>10.2486</v>
+        <v>9.728</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>0.82</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.1693</v>
+        <v>-0.1486</v>
       </c>
       <c r="J317" t="n">
-        <v>-3.2167</v>
+        <v>-2.8234</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>0.73</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.2668</v>
+        <v>-0.2533</v>
       </c>
       <c r="J318" t="n">
-        <v>-5.0692</v>
+        <v>-4.8127</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>0.6</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.3911</v>
+        <v>-0.3843</v>
       </c>
       <c r="J319" t="n">
-        <v>-7.4309</v>
+        <v>-7.3017</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>0.42</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5467</v>
+        <v>-0.5502</v>
       </c>
       <c r="J320" t="n">
-        <v>-10.3873</v>
+        <v>-10.4538</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.3</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.6533</v>
+        <v>-0.6736</v>
       </c>
       <c r="J321" t="n">
-        <v>-12.4127</v>
+        <v>-12.7984</v>
       </c>
     </row>
     <row r="322">
@@ -15275,10 +15275,10 @@
         <v>1.44</v>
       </c>
       <c r="I322" t="n">
-        <v>1.0154</v>
+        <v>1.0152</v>
       </c>
       <c r="J322" t="n">
-        <v>24.3696</v>
+        <v>24.3648</v>
       </c>
     </row>
     <row r="323">
@@ -15315,10 +15315,10 @@
         <v>1.37</v>
       </c>
       <c r="I323" t="n">
-        <v>0.8902</v>
+        <v>0.8726</v>
       </c>
       <c r="J323" t="n">
-        <v>21.3648</v>
+        <v>20.9424</v>
       </c>
     </row>
     <row r="324">
@@ -15355,10 +15355,10 @@
         <v>1.12</v>
       </c>
       <c r="I324" t="n">
-        <v>0.3599</v>
+        <v>0.3263</v>
       </c>
       <c r="J324" t="n">
-        <v>8.637600000000001</v>
+        <v>7.8312</v>
       </c>
     </row>
     <row r="325">
@@ -15395,10 +15395,10 @@
         <v>1.08</v>
       </c>
       <c r="I325" t="n">
-        <v>0.2553</v>
+        <v>0.2245</v>
       </c>
       <c r="J325" t="n">
-        <v>6.1272</v>
+        <v>5.388</v>
       </c>
     </row>
     <row r="326">
@@ -15435,10 +15435,10 @@
         <v>1.03</v>
       </c>
       <c r="I326" t="n">
-        <v>0.1028</v>
+        <v>0.0823</v>
       </c>
       <c r="J326" t="n">
-        <v>2.4672</v>
+        <v>1.9752</v>
       </c>
     </row>
     <row r="327">
@@ -15475,10 +15475,10 @@
         <v>1.26</v>
       </c>
       <c r="I327" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.527</v>
       </c>
       <c r="J327" t="n">
-        <v>13.8984</v>
+        <v>12.648</v>
       </c>
     </row>
     <row r="328">
@@ -15515,10 +15515,10 @@
         <v>1.03</v>
       </c>
       <c r="I328" t="n">
-        <v>0.1273</v>
+        <v>0.0968</v>
       </c>
       <c r="J328" t="n">
-        <v>3.0552</v>
+        <v>2.3232</v>
       </c>
     </row>
     <row r="329">
@@ -15555,10 +15555,10 @@
         <v>0.72</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3157</v>
+        <v>-0.2985</v>
       </c>
       <c r="J329" t="n">
-        <v>-7.5768</v>
+        <v>-7.164</v>
       </c>
     </row>
     <row r="330">
@@ -15595,10 +15595,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3435</v>
+        <v>-0.3278</v>
       </c>
       <c r="J330" t="n">
-        <v>-8.244</v>
+        <v>-7.8672</v>
       </c>
     </row>
     <row r="331">
@@ -15635,10 +15635,10 @@
         <v>0.61</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4157</v>
+        <v>-0.4058</v>
       </c>
       <c r="J331" t="n">
-        <v>-9.976800000000001</v>
+        <v>-9.7392</v>
       </c>
     </row>
     <row r="332">
@@ -15675,10 +15675,10 @@
         <v>1.99</v>
       </c>
       <c r="I332" t="n">
-        <v>1.6701</v>
+        <v>1.7156</v>
       </c>
       <c r="J332" t="n">
-        <v>35.0721</v>
+        <v>36.0276</v>
       </c>
     </row>
     <row r="333">
@@ -15715,10 +15715,10 @@
         <v>1.64</v>
       </c>
       <c r="I333" t="n">
-        <v>1.2462</v>
+        <v>1.2646</v>
       </c>
       <c r="J333" t="n">
-        <v>26.1702</v>
+        <v>26.5566</v>
       </c>
     </row>
     <row r="334">
@@ -15755,10 +15755,10 @@
         <v>1.44</v>
       </c>
       <c r="I334" t="n">
-        <v>0.9807</v>
+        <v>0.9833</v>
       </c>
       <c r="J334" t="n">
-        <v>20.5947</v>
+        <v>20.6493</v>
       </c>
     </row>
     <row r="335">
@@ -15795,10 +15795,10 @@
         <v>1.28</v>
       </c>
       <c r="I335" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6615</v>
       </c>
       <c r="J335" t="n">
-        <v>14.322</v>
+        <v>13.8915</v>
       </c>
     </row>
     <row r="336">
@@ -15835,10 +15835,10 @@
         <v>0.83</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5904</v>
+        <v>-0.5617</v>
       </c>
       <c r="J336" t="n">
-        <v>-12.3984</v>
+        <v>-11.7957</v>
       </c>
     </row>
     <row r="337">
@@ -15875,10 +15875,10 @@
         <v>1.05</v>
       </c>
       <c r="I337" t="n">
-        <v>0.253</v>
+        <v>0.2287</v>
       </c>
       <c r="J337" t="n">
-        <v>5.313</v>
+        <v>4.8027</v>
       </c>
     </row>
     <row r="338">
@@ -15915,10 +15915,10 @@
         <v>0.95</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.0394</v>
+        <v>-0.0232</v>
       </c>
       <c r="J338" t="n">
-        <v>-0.8274</v>
+        <v>-0.4872</v>
       </c>
     </row>
     <row r="339">
@@ -15955,10 +15955,10 @@
         <v>0.49</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.4999</v>
+        <v>-0.4981</v>
       </c>
       <c r="J339" t="n">
-        <v>-10.4979</v>
+        <v>-10.4601</v>
       </c>
     </row>
     <row r="340">
@@ -15995,10 +15995,10 @@
         <v>0.47</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.5175</v>
+        <v>-0.5177</v>
       </c>
       <c r="J340" t="n">
-        <v>-10.8675</v>
+        <v>-10.8717</v>
       </c>
     </row>
     <row r="341">
@@ -16035,10 +16035,10 @@
         <v>0.43</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5524</v>
+        <v>-0.5574</v>
       </c>
       <c r="J341" t="n">
-        <v>-11.6004</v>
+        <v>-11.7054</v>
       </c>
     </row>
     <row r="342">
@@ -16075,10 +16075,10 @@
         <v>1.63</v>
       </c>
       <c r="I342" t="n">
-        <v>1.3134</v>
+        <v>1.3391</v>
       </c>
       <c r="J342" t="n">
-        <v>36.7752</v>
+        <v>37.4948</v>
       </c>
     </row>
     <row r="343">
@@ -16115,10 +16115,10 @@
         <v>1.09</v>
       </c>
       <c r="I343" t="n">
-        <v>0.2999</v>
+        <v>0.2632</v>
       </c>
       <c r="J343" t="n">
-        <v>8.3972</v>
+        <v>7.3696</v>
       </c>
     </row>
     <row r="344">
@@ -16155,10 +16155,10 @@
         <v>1.02</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0876</v>
+        <v>0.0693</v>
       </c>
       <c r="J344" t="n">
-        <v>2.4528</v>
+        <v>1.9404</v>
       </c>
     </row>
     <row r="345">
@@ -16195,10 +16195,10 @@
         <v>0.99</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.053</v>
       </c>
       <c r="J345" t="n">
-        <v>-2.0412</v>
+        <v>-1.484</v>
       </c>
     </row>
     <row r="346">
@@ -16235,10 +16235,10 @@
         <v>0.7</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.8258</v>
+        <v>-0.8047</v>
       </c>
       <c r="J346" t="n">
-        <v>-23.1224</v>
+        <v>-22.5316</v>
       </c>
     </row>
     <row r="347">
@@ -16275,10 +16275,10 @@
         <v>1.14</v>
       </c>
       <c r="I347" t="n">
-        <v>0.3297</v>
+        <v>0.277</v>
       </c>
       <c r="J347" t="n">
-        <v>9.2316</v>
+        <v>7.756</v>
       </c>
     </row>
     <row r="348">
@@ -16315,10 +16315,10 @@
         <v>1.05</v>
       </c>
       <c r="I348" t="n">
-        <v>0.1491</v>
+        <v>0.1147</v>
       </c>
       <c r="J348" t="n">
-        <v>4.1748</v>
+        <v>3.2116</v>
       </c>
     </row>
     <row r="349">
@@ -16355,10 +16355,10 @@
         <v>0.98</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.0422</v>
+        <v>-0.0322</v>
       </c>
       <c r="J349" t="n">
-        <v>-1.1816</v>
+        <v>-0.9016</v>
       </c>
     </row>
     <row r="350">
@@ -16395,10 +16395,10 @@
         <v>0.9</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.1463</v>
+        <v>-0.1267</v>
       </c>
       <c r="J350" t="n">
-        <v>-4.0964</v>
+        <v>-3.5476</v>
       </c>
     </row>
     <row r="351">
@@ -16435,10 +16435,10 @@
         <v>0.89</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.1575</v>
+        <v>-0.1376</v>
       </c>
       <c r="J351" t="n">
-        <v>-4.41</v>
+        <v>-3.8528</v>
       </c>
     </row>
     <row r="352">
@@ -16475,10 +16475,10 @@
         <v>2.03</v>
       </c>
       <c r="I352" t="n">
-        <v>1.6925</v>
+        <v>1.7393</v>
       </c>
       <c r="J352" t="n">
-        <v>28.7725</v>
+        <v>29.5681</v>
       </c>
     </row>
     <row r="353">
@@ -16515,10 +16515,10 @@
         <v>1.63</v>
       </c>
       <c r="I353" t="n">
-        <v>1.2199</v>
+        <v>1.2408</v>
       </c>
       <c r="J353" t="n">
-        <v>20.7383</v>
+        <v>21.0936</v>
       </c>
     </row>
     <row r="354">
@@ -16555,10 +16555,10 @@
         <v>1.53</v>
       </c>
       <c r="I354" t="n">
-        <v>1.0975</v>
+        <v>1.1168</v>
       </c>
       <c r="J354" t="n">
-        <v>18.6575</v>
+        <v>18.9856</v>
       </c>
     </row>
     <row r="355">
@@ -16595,10 +16595,10 @@
         <v>1.37</v>
       </c>
       <c r="I355" t="n">
-        <v>0.8428</v>
+        <v>0.8358</v>
       </c>
       <c r="J355" t="n">
-        <v>14.3276</v>
+        <v>14.2086</v>
       </c>
     </row>
     <row r="356">
@@ -16635,10 +16635,10 @@
         <v>1.21</v>
       </c>
       <c r="I356" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4892</v>
       </c>
       <c r="J356" t="n">
-        <v>8.799200000000001</v>
+        <v>8.3164</v>
       </c>
     </row>
     <row r="357">
@@ -16675,10 +16675,10 @@
         <v>0.83</v>
       </c>
       <c r="I357" t="n">
-        <v>-0.1688</v>
+        <v>-0.1502</v>
       </c>
       <c r="J357" t="n">
-        <v>-2.8696</v>
+        <v>-2.5534</v>
       </c>
     </row>
     <row r="358">
@@ -16715,10 +16715,10 @@
         <v>0.74</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.2651</v>
+        <v>-0.252</v>
       </c>
       <c r="J358" t="n">
-        <v>-4.5067</v>
+        <v>-4.284</v>
       </c>
     </row>
     <row r="359">
@@ -16755,10 +16755,10 @@
         <v>0.61</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.3864</v>
+        <v>-0.3779</v>
       </c>
       <c r="J359" t="n">
-        <v>-6.5688</v>
+        <v>-6.4243</v>
       </c>
     </row>
     <row r="360">
@@ -16795,10 +16795,10 @@
         <v>0.55</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.4374</v>
+        <v>-0.4307</v>
       </c>
       <c r="J360" t="n">
-        <v>-7.4358</v>
+        <v>-7.3219</v>
       </c>
     </row>
     <row r="361">
@@ -16835,10 +16835,10 @@
         <v>0.31</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.6687</v>
       </c>
       <c r="J361" t="n">
-        <v>-11.0279</v>
+        <v>-11.3679</v>
       </c>
     </row>
   </sheetData>
